--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rf2968f5fb2b640dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rdebd48563fd04954"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +23,7 @@
   </x:si>
   <x:si>
     <x:t>.NET
- 9.0.10 </x:t>
+ 9.0.15 </x:t>
   </x:si>
   <x:si>
     <x:t>wregex
@@ -71,7 +71,7 @@
   </x:si>
   <x:si>
     <x:t>Rust
- 1.90.0 </x:t>
+ 1.95.0 </x:t>
   </x:si>
   <x:si>
     <x:t>Java
@@ -91,7 +91,7 @@
   </x:si>
   <x:si>
     <x:t>Fortran (IFX)
- 2025.1.0 </x:t>
+ 2025.3.0 </x:t>
   </x:si>
   <x:si>
     <x:t>TRE
@@ -4437,11 +4437,11 @@
       <x:c r="AZ16" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="BA16" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB16" t="s">
-        <x:v>1</x:v>
+      <x:c r="BA16" s="6" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="BB16" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BC16" s="6" t="s">
         <x:v>79</x:v>
@@ -11186,8 +11186,8 @@
       <x:c r="C50" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D50" t="s">
-        <x:v>1</x:v>
+      <x:c r="D50" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E50" t="s">
         <x:v>1</x:v>
@@ -12700,8 +12700,8 @@
       <x:c r="F57" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G57" t="s">
-        <x:v>1</x:v>
+      <x:c r="G57" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H57" t="s">
         <x:v>1</x:v>
@@ -12915,8 +12915,8 @@
       <x:c r="F58" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G58" t="s">
-        <x:v>1</x:v>
+      <x:c r="G58" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H58" t="s">
         <x:v>1</x:v>
@@ -17573,8 +17573,8 @@
       <x:c r="AY80" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ80" t="s">
-        <x:v>1</x:v>
+      <x:c r="AZ80" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BA80" t="s">
         <x:v>1</x:v>
@@ -18003,8 +18003,8 @@
       <x:c r="AY82" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ82" t="s">
-        <x:v>1</x:v>
+      <x:c r="AZ82" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BA82" t="s">
         <x:v>1</x:v>
@@ -28126,14 +28126,14 @@
       <x:c r="AW132" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX132" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY132" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ132" t="s">
-        <x:v>1</x:v>
+      <x:c r="AX132" s="6" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="AY132" s="6" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="AZ132" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BA132" t="s">
         <x:v>1</x:v>
@@ -30508,11 +30508,11 @@
       <x:c r="AZ144" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="BA144" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB144" t="s">
-        <x:v>1</x:v>
+      <x:c r="BA144" s="6" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="BB144" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BC144" t="s">
         <x:v>1</x:v>
@@ -32440,8 +32440,8 @@
       <x:c r="AY153" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ153" t="s">
-        <x:v>1</x:v>
+      <x:c r="AZ153" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BA153" t="s">
         <x:v>1</x:v>
@@ -32870,8 +32870,8 @@
       <x:c r="AY155" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ155" t="s">
-        <x:v>1</x:v>
+      <x:c r="AZ155" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BA155" t="s">
         <x:v>1</x:v>
@@ -33300,8 +33300,8 @@
       <x:c r="AY157" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ157" t="s">
-        <x:v>1</x:v>
+      <x:c r="AZ157" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BA157" t="s">
         <x:v>1</x:v>
@@ -35673,8 +35673,8 @@
       <x:c r="AY169" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ169" t="s">
-        <x:v>1</x:v>
+      <x:c r="AZ169" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BA169" s="6" t="s">
         <x:v>79</x:v>
@@ -36318,8 +36318,8 @@
       <x:c r="AY172" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ172" t="s">
-        <x:v>1</x:v>
+      <x:c r="AZ172" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BA172" s="6" t="s">
         <x:v>79</x:v>
@@ -37393,8 +37393,8 @@
       <x:c r="AY177" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ177" t="s">
-        <x:v>1</x:v>
+      <x:c r="AZ177" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BA177" t="s">
         <x:v>1</x:v>
@@ -38476,8 +38476,8 @@
       <x:c r="AY183" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ183" t="s">
-        <x:v>1</x:v>
+      <x:c r="AZ183" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BA183" t="s">
         <x:v>1</x:v>
@@ -42800,8 +42800,8 @@
       <x:c r="AY206" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ206" t="s">
-        <x:v>1</x:v>
+      <x:c r="AZ206" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BA206" t="s">
         <x:v>1</x:v>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rdebd48563fd04954"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R79e52b8b2bc34ea0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -75,7 +75,7 @@
   </x:si>
   <x:si>
     <x:t>Java
- 25.0.1 </x:t>
+ 26.0.1 </x:t>
   </x:si>
   <x:si>
     <x:t>Python
@@ -83,7 +83,7 @@
   </x:si>
   <x:si>
     <x:t>D
- 2.111 </x:t>
+ 2.112 </x:t>
   </x:si>
   <x:si>
     <x:t>Perl
@@ -35222,8 +35222,8 @@
       <x:c r="AR167" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="AS167" t="s">
-        <x:v>1</x:v>
+      <x:c r="AS167" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AT167" t="s">
         <x:v>1</x:v>
@@ -35437,8 +35437,8 @@
       <x:c r="AR168" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="AS168" t="s">
-        <x:v>1</x:v>
+      <x:c r="AS168" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AT168" t="s">
         <x:v>1</x:v>
@@ -35652,8 +35652,8 @@
       <x:c r="AR169" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="AS169" t="s">
-        <x:v>1</x:v>
+      <x:c r="AS169" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AT169" t="s">
         <x:v>1</x:v>
@@ -35867,8 +35867,8 @@
       <x:c r="AR170" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="AS170" t="s">
-        <x:v>1</x:v>
+      <x:c r="AS170" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AT170" t="s">
         <x:v>1</x:v>
@@ -36082,8 +36082,8 @@
       <x:c r="AR171" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="AS171" t="s">
-        <x:v>1</x:v>
+      <x:c r="AS171" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AT171" t="s">
         <x:v>1</x:v>
@@ -36297,8 +36297,8 @@
       <x:c r="AR172" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="AS172" t="s">
-        <x:v>1</x:v>
+      <x:c r="AS172" s="6" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AT172" t="s">
         <x:v>1</x:v>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R79e52b8b2bc34ea0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R9e87c771b89d48a5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -91,7 +91,7 @@
   </x:si>
   <x:si>
     <x:t>Fortran (IFX)
- 2025.3.0 </x:t>
+ 2026.0.0 </x:t>
   </x:si>
   <x:si>
     <x:t>TRE
@@ -1000,7 +1000,7 @@
     <x:t>(?P=name)</x:t>
   </x:si>
   <x:si>
-    <x:t>Grouping</x:t>
+    <x:t>Grouping and Lookaround</x:t>
   </x:si>
   <x:si>
     <x:t>(?:…)</x:t>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rde96327c53be477b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rd7de7708dc794e7f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1265,7 +1265,7 @@
     <x:t>Approximate matching using special patterns or parameters</x:t>
   </x:si>
   <x:si>
-    <x:t>No hang</x:t>
+    <x:t>No hang, no ReDoS</x:t>
   </x:si>
   <x:si>
     <x:t>No catastrophic infinite matching, no timeout errors</x:t>
@@ -38618,8 +38618,8 @@
       <x:c r="BS181" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BT181" t="s">
-        <x:v>1</x:v>
+      <x:c r="BT181" s="6" t="s">
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="182">

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R4a308b82503f4765"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R31f2c3925c674661"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -79,7 +79,7 @@
   </x:si>
   <x:si>
     <x:t>Python
- 3.13.6 </x:t>
+ 3.14.5 </x:t>
   </x:si>
   <x:si>
     <x:t>D
@@ -32678,14 +32678,14 @@
       <x:c r="BE136" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BF136" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG136" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH136" t="s">
-        <x:v>1</x:v>
+      <x:c r="BF136" s="6" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="BG136" s="6" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="BH136" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BI136" t="s">
         <x:v>1</x:v>
@@ -41795,14 +41795,14 @@
       <x:c r="BQ175" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BR175" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BR175" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BS175" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BT175" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BT175" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BU175" s="6" t="s">
         <x:v>92</x:v>
@@ -42530,14 +42530,14 @@
       <x:c r="BQ178" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BR178" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BR178" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BS178" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BT178" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BT178" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BU178" s="6" t="s">
         <x:v>92</x:v>
@@ -42787,8 +42787,8 @@
       <x:c r="BU179" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BV179" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BV179" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BW179" t="s">
         <x:v>1</x:v>
@@ -44465,11 +44465,11 @@
       <x:c r="BF187" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BG187" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH187" t="s">
-        <x:v>1</x:v>
+      <x:c r="BG187" s="6" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="BH187" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BI187" t="s">
         <x:v>1</x:v>
@@ -50908,14 +50908,14 @@
       <x:c r="BY215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BZ215" t="s">
-        <x:v>1</x:v>
+      <x:c r="BZ215" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="CA215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CB215" t="s">
-        <x:v>1</x:v>
+      <x:c r="CB215" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="CC215" t="s">
         <x:v>1</x:v>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R31f2c3925c674661"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R14563641f65e468f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -248,10 +248,10 @@
     <x:t>fancy_regex (“u” flag)</x:t>
   </x:si>
   <x:si>
-    <x:t>regress (“u” flag)</x:t>
+    <x:t>regress (“uv” flags)</x:t>
   </x:si>
   <x:si>
-    <x:t>regress (“uv” flags)</x:t>
+    <x:t>resharp (“Full” mode)</x:t>
   </x:si>
   <x:si>
     <x:t>regex</x:t>
@@ -1534,8 +1534,8 @@
     <x:col min="51" max="51" width="13.791" customWidth="1"/>
     <x:col min="52" max="52" width="9.796" customWidth="1"/>
     <x:col min="53" max="53" width="19.089" customWidth="1"/>
-    <x:col min="54" max="54" width="15.288" customWidth="1"/>
-    <x:col min="55" max="55" width="17.087" customWidth="1"/>
+    <x:col min="54" max="54" width="17.087" customWidth="1"/>
+    <x:col min="55" max="55" width="18.884" customWidth="1"/>
     <x:col min="56" max="56" width="6.498" customWidth="1"/>
     <x:col min="57" max="57" width="4.998" customWidth="1"/>
     <x:col min="58" max="58" width="3.599" customWidth="1"/>
@@ -3948,8 +3948,8 @@
       <x:c r="BB12" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC12" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC12" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD12" s="6" t="s">
         <x:v>92</x:v>
@@ -4438,8 +4438,8 @@
       <x:c r="BB14" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC14" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC14" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD14" s="6" t="s">
         <x:v>92</x:v>
@@ -4683,8 +4683,8 @@
       <x:c r="BB15" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC15" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC15" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD15" s="6" t="s">
         <x:v>92</x:v>
@@ -5663,8 +5663,8 @@
       <x:c r="BB19" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC19" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC19" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD19" s="6" t="s">
         <x:v>92</x:v>
@@ -6640,11 +6640,11 @@
       <x:c r="BA23" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB23" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC23" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BB23" s="6" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="BC23" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD23" t="s">
         <x:v>1</x:v>
@@ -8856,8 +8856,8 @@
       <x:c r="BB33" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BC33" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BC33" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD33" s="6" t="s">
         <x:v>92</x:v>
@@ -9109,8 +9109,8 @@
       <x:c r="BB35" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC35" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC35" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD35" s="6" t="s">
         <x:v>92</x:v>
@@ -12294,8 +12294,8 @@
       <x:c r="BB48" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC48" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC48" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD48" s="6" t="s">
         <x:v>92</x:v>
@@ -12784,8 +12784,8 @@
       <x:c r="BB50" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC50" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC50" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD50" t="s">
         <x:v>1</x:v>
@@ -13274,8 +13274,8 @@
       <x:c r="BB52" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC52" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC52" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD52" t="s">
         <x:v>1</x:v>
@@ -13519,8 +13519,8 @@
       <x:c r="BB53" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BC53" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BC53" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD53" s="6" t="s">
         <x:v>92</x:v>
@@ -14752,8 +14752,8 @@
       <x:c r="BB59" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC59" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC59" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD59" s="6" t="s">
         <x:v>92</x:v>
@@ -14994,8 +14994,8 @@
       <x:c r="BA60" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BB60" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BB60" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BC60" t="s">
         <x:v>1</x:v>
@@ -17937,8 +17937,8 @@
       <x:c r="BB72" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC72" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC72" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD72" s="6" t="s">
         <x:v>92</x:v>
@@ -18427,8 +18427,8 @@
       <x:c r="BB74" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC74" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC74" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD74" t="s">
         <x:v>1</x:v>
@@ -18917,8 +18917,8 @@
       <x:c r="BB76" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC76" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC76" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD76" t="s">
         <x:v>1</x:v>
@@ -19162,8 +19162,8 @@
       <x:c r="BB77" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BC77" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BC77" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD77" s="6" t="s">
         <x:v>92</x:v>
@@ -24315,8 +24315,8 @@
       <x:c r="BB99" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC99" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC99" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD99" s="6" t="s">
         <x:v>92</x:v>
@@ -27508,8 +27508,8 @@
       <x:c r="BB113" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC113" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC113" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD113" s="6" t="s">
         <x:v>92</x:v>
@@ -27998,8 +27998,8 @@
       <x:c r="BB115" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC115" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC115" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD115" t="s">
         <x:v>1</x:v>
@@ -28738,11 +28738,11 @@
       <x:c r="BA119" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BB119" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC119" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BB119" s="6" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="BC119" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD119" s="6" t="s">
         <x:v>92</x:v>
@@ -30698,11 +30698,11 @@
       <x:c r="BA127" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BB127" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC127" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BB127" s="6" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="BC127" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD127" s="6" t="s">
         <x:v>92</x:v>
@@ -31188,11 +31188,11 @@
       <x:c r="BA129" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BB129" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC129" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BB129" s="6" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="BC129" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD129" t="s">
         <x:v>1</x:v>
@@ -32179,8 +32179,8 @@
       <x:c r="BB134" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC134" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC134" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD134" s="6" t="s">
         <x:v>92</x:v>
@@ -32669,8 +32669,8 @@
       <x:c r="BB136" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC136" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC136" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD136" s="6" t="s">
         <x:v>92</x:v>
@@ -35617,8 +35617,8 @@
       <x:c r="BB149" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC149" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC149" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD149" t="s">
         <x:v>1</x:v>
@@ -36107,8 +36107,8 @@
       <x:c r="BB151" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BC151" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BC151" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD151" t="s">
         <x:v>1</x:v>
@@ -36352,8 +36352,8 @@
       <x:c r="BB152" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BC152" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BC152" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD152" s="6" t="s">
         <x:v>92</x:v>
@@ -36597,8 +36597,8 @@
       <x:c r="BB153" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BC153" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BC153" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD153" s="6" t="s">
         <x:v>92</x:v>
@@ -37087,8 +37087,8 @@
       <x:c r="BB155" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BC155" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BC155" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD155" s="6" t="s">
         <x:v>92</x:v>
@@ -41505,8 +41505,8 @@
       <x:c r="BB174" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BC174" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BC174" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD174" s="6" t="s">
         <x:v>92</x:v>
@@ -41750,8 +41750,8 @@
       <x:c r="BB175" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BC175" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BC175" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD175" s="6" t="s">
         <x:v>92</x:v>
@@ -41995,8 +41995,8 @@
       <x:c r="BB176" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BC176" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BC176" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD176" s="6" t="s">
         <x:v>92</x:v>
@@ -42240,8 +42240,8 @@
       <x:c r="BB177" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BC177" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BC177" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD177" s="6" t="s">
         <x:v>92</x:v>
@@ -42485,8 +42485,8 @@
       <x:c r="BB178" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BC178" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BC178" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD178" s="6" t="s">
         <x:v>92</x:v>
@@ -42730,8 +42730,8 @@
       <x:c r="BB179" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BC179" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BC179" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD179" s="6" t="s">
         <x:v>92</x:v>
@@ -49124,8 +49124,8 @@
       <x:c r="BB208" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BC208" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BC208" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD208" t="s">
         <x:v>1</x:v>
@@ -49369,8 +49369,8 @@
       <x:c r="BB209" s="6" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BC209" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="BC209" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD209" t="s">
         <x:v>1</x:v>
@@ -50349,8 +50349,8 @@
       <x:c r="BB213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC213" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC213" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD213" s="6" t="s">
         <x:v>92</x:v>
@@ -52072,8 +52072,8 @@
       <x:c r="BB221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC221" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC221" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD221" t="s">
         <x:v>1</x:v>
@@ -52317,8 +52317,8 @@
       <x:c r="BB222" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC222" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC222" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD222" t="s">
         <x:v>1</x:v>
@@ -52562,8 +52562,8 @@
       <x:c r="BB223" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC223" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC223" s="6" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BD223" t="s">
         <x:v>1</x:v>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R3dd2a09574474215"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rd5219d3dd367459b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rd5219d3dd367459b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R4e6c79aab5344f2a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1360,6 +1360,9 @@
   <x:si>
     <x:t>Complement (pattern must not match)</x:t>
   </x:si>
+  <x:si>
+    <x:t>Also supports alternative syntax</x:t>
+  </x:si>
 </x:sst>
 </file>
 
@@ -36773,8 +36776,8 @@
       <x:c r="AZ152" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BA152" t="s">
-        <x:v>1</x:v>
+      <x:c r="BA152" s="6" t="s">
+        <x:v>93</x:v>
       </x:c>
       <x:c r="BB152" s="6" t="s">
         <x:v>93</x:v>
@@ -37021,8 +37024,8 @@
       <x:c r="AZ153" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BA153" t="s">
-        <x:v>1</x:v>
+      <x:c r="BA153" s="6" t="s">
+        <x:v>93</x:v>
       </x:c>
       <x:c r="BB153" s="6" t="s">
         <x:v>93</x:v>
@@ -48124,8 +48127,8 @@
       <x:c r="Y201" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z201" t="s">
-        <x:v>1</x:v>
+      <x:c r="Z201" s="6" t="s">
+        <x:v>93</x:v>
       </x:c>
       <x:c r="AA201" t="s">
         <x:v>1</x:v>
@@ -48151,8 +48154,8 @@
       <x:c r="AH201" s="6" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="AI201" t="s">
-        <x:v>1</x:v>
+      <x:c r="AI201" s="6" t="s">
+        <x:v>93</x:v>
       </x:c>
       <x:c r="AJ201" t="s">
         <x:v>1</x:v>
@@ -48175,8 +48178,8 @@
       <x:c r="AP201" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AQ201" t="s">
-        <x:v>1</x:v>
+      <x:c r="AQ201" s="6" t="s">
+        <x:v>93</x:v>
       </x:c>
       <x:c r="AR201" t="s">
         <x:v>1</x:v>
@@ -48196,8 +48199,8 @@
       <x:c r="AW201" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX201" t="s">
-        <x:v>1</x:v>
+      <x:c r="AX201" s="6" t="s">
+        <x:v>93</x:v>
       </x:c>
       <x:c r="AY201" t="s">
         <x:v>1</x:v>
@@ -53273,250 +53276,498 @@
       </x:c>
     </x:row>
     <x:row r="224">
-      <x:c r="A224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC224" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD224" s="7" t="s">
+      <x:c r="A224" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B224" s="5" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="C224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA224" s="6" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="BB224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC225" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD225" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R346721d248a4419d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R2bad27b84ce24ab6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1371,6 +1371,9 @@
     <x:t>Complement (pattern must not match)</x:t>
   </x:si>
   <x:si>
+    <x:t>Get all captures matched by group</x:t>
+  </x:si>
+  <x:si>
     <x:t>Also supports alternative syntax</x:t>
   </x:si>
 </x:sst>
@@ -53087,8 +53090,8 @@
       <x:c r="Y218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z218" s="6" t="s">
-        <x:v>96</x:v>
+      <x:c r="Z218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AA218" t="s">
         <x:v>1</x:v>
@@ -54542,8 +54545,8 @@
       <x:c r="B224" s="5" t="s">
         <x:v>444</x:v>
       </x:c>
-      <x:c r="C224" t="s">
-        <x:v>1</x:v>
+      <x:c r="C224" s="6" t="s">
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D224" t="s">
         <x:v>1</x:v>
@@ -54584,11 +54587,11 @@
       <x:c r="P224" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q224" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R224" t="s">
-        <x:v>1</x:v>
+      <x:c r="Q224" s="6" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="R224" s="6" t="s">
+        <x:v>96</x:v>
       </x:c>
       <x:c r="S224" t="s">
         <x:v>1</x:v>
@@ -54608,11 +54611,11 @@
       <x:c r="X224" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Y224" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z224" t="s">
-        <x:v>1</x:v>
+      <x:c r="Y224" s="6" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="Z224" s="6" t="s">
+        <x:v>96</x:v>
       </x:c>
       <x:c r="AA224" t="s">
         <x:v>1</x:v>
@@ -54629,20 +54632,20 @@
       <x:c r="AE224" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AF224" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG224" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH224" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI224" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ224" t="s">
-        <x:v>1</x:v>
+      <x:c r="AF224" s="6" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="AG224" s="6" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="AH224" s="6" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="AI224" s="6" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="AJ224" s="6" t="s">
+        <x:v>96</x:v>
       </x:c>
       <x:c r="AK224" t="s">
         <x:v>1</x:v>
@@ -54692,8 +54695,8 @@
       <x:c r="AZ224" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BA224" s="6" t="s">
-        <x:v>96</x:v>
+      <x:c r="BA224" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BB224" t="s">
         <x:v>1</x:v>
@@ -54704,14 +54707,14 @@
       <x:c r="BD224" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE224" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF224" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG224" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE224" s="6" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="BF224" s="6" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="BG224" s="6" t="s">
+        <x:v>96</x:v>
       </x:c>
       <x:c r="BH224" t="s">
         <x:v>1</x:v>
@@ -54790,256 +54793,510 @@
       </x:c>
     </x:row>
     <x:row r="225">
-      <x:c r="A225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE225" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF225" s="7" t="s">
+      <x:c r="A225" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B225" s="5" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="C225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA225" s="6" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="BB225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF225" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE226" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF226" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rcbd899580e6742f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R6a90f30c270d4547"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1303,6 +1303,18 @@
     <x:t>Supports Unicode characters, not just ASCII</x:t>
   </x:si>
   <x:si>
+    <x:t>[Unicode]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Supports Unicode characters inside sets</x:t>
+  </x:si>
+  <x:si>
+    <x:t>é=É</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Supports Unicode case folding</x:t>
+  </x:si>
+  <x:si>
     <x:t>Surrogates</x:t>
   </x:si>
   <x:si>
@@ -52082,35 +52094,35 @@
       <x:c r="B211" s="5" t="s">
         <x:v>422</x:v>
       </x:c>
-      <x:c r="C211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L211" t="s">
-        <x:v>1</x:v>
+      <x:c r="C211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="I211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="J211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="K211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="L211" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M211" s="6" t="s">
         <x:v>97</x:v>
@@ -52121,35 +52133,35 @@
       <x:c r="O211" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y211" t="s">
-        <x:v>1</x:v>
+      <x:c r="P211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Q211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="R211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="S211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="T211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="U211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="V211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="W211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="X211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Y211" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="Z211" s="6" t="s">
         <x:v>97</x:v>
@@ -52184,8 +52196,8 @@
       <x:c r="AJ211" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AK211" t="s">
-        <x:v>1</x:v>
+      <x:c r="AK211" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AL211" s="6" t="s">
         <x:v>97</x:v>
@@ -52205,8 +52217,8 @@
       <x:c r="AQ211" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AR211" t="s">
-        <x:v>1</x:v>
+      <x:c r="AR211" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AS211" s="6" t="s">
         <x:v>97</x:v>
@@ -52268,11 +52280,11 @@
       <x:c r="BL211" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BM211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN211" t="s">
-        <x:v>1</x:v>
+      <x:c r="BM211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BN211" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BO211" t="s">
         <x:v>1</x:v>
@@ -52286,11 +52298,11 @@
       <x:c r="BR211" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BS211" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT211" t="s">
-        <x:v>1</x:v>
+      <x:c r="BS211" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BT211" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BU211" t="s">
         <x:v>1</x:v>
@@ -52301,8 +52313,8 @@
       <x:c r="BW211" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BX211" t="s">
-        <x:v>1</x:v>
+      <x:c r="BX211" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BY211" s="6" t="s">
         <x:v>97</x:v>
@@ -52322,14 +52334,14 @@
       <x:c r="CD211" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="CE211" t="s">
-        <x:v>1</x:v>
+      <x:c r="CE211" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="CF211" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="CG211" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="CG211" t="s">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -52339,8 +52351,8 @@
       <x:c r="B212" s="5" t="s">
         <x:v>424</x:v>
       </x:c>
-      <x:c r="C212" t="s">
-        <x:v>1</x:v>
+      <x:c r="C212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D212" t="s">
         <x:v>1</x:v>
@@ -52363,143 +52375,143 @@
       <x:c r="J212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N212" t="s">
-        <x:v>1</x:v>
+      <x:c r="K212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="L212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="M212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="N212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="O212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR212" t="s">
-        <x:v>1</x:v>
+      <x:c r="P212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Q212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="R212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="S212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="T212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="U212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="V212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="W212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="X212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Y212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Z212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AA212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AB212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AC212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AD212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AE212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AF212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AG212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AH212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AI212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AJ212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AK212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AL212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AM212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AN212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AO212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AP212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AQ212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AR212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AS212" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AT212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV212" t="s">
-        <x:v>1</x:v>
+      <x:c r="AT212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AU212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AV212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AW212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ212" t="s">
-        <x:v>1</x:v>
+      <x:c r="AX212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AY212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AZ212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BA212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD212" t="s">
-        <x:v>1</x:v>
+      <x:c r="BB212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BC212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BD212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BE212" s="6" t="s">
         <x:v>97</x:v>
@@ -52510,11 +52522,11 @@
       <x:c r="BG212" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BH212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI212" t="s">
-        <x:v>1</x:v>
+      <x:c r="BH212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BI212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BJ212" t="s">
         <x:v>1</x:v>
@@ -52525,11 +52537,11 @@
       <x:c r="BL212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BM212" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BN212" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BM212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BO212" t="s">
         <x:v>1</x:v>
@@ -52537,11 +52549,11 @@
       <x:c r="BP212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BQ212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR212" t="s">
-        <x:v>1</x:v>
+      <x:c r="BQ212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BR212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BS212" t="s">
         <x:v>1</x:v>
@@ -52558,32 +52570,32 @@
       <x:c r="BW212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BX212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY212" t="s">
-        <x:v>1</x:v>
+      <x:c r="BX212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BY212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BZ212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CA212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF212" t="s">
-        <x:v>1</x:v>
+      <x:c r="CA212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CB212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CC212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CD212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CE212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CF212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="CG212" t="s">
         <x:v>1</x:v>
@@ -52635,8 +52647,8 @@
       <x:c r="O213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P213" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="P213" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q213" t="s">
         <x:v>1</x:v>
@@ -52701,14 +52713,14 @@
       <x:c r="AK213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AL213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN213" t="s">
-        <x:v>1</x:v>
+      <x:c r="AL213" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AM213" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AN213" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AO213" s="6" t="s">
         <x:v>97</x:v>
@@ -52716,8 +52728,8 @@
       <x:c r="AP213" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AQ213" t="s">
-        <x:v>1</x:v>
+      <x:c r="AQ213" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AR213" t="s">
         <x:v>1</x:v>
@@ -52728,8 +52740,8 @@
       <x:c r="AT213" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AU213" t="s">
-        <x:v>1</x:v>
+      <x:c r="AU213" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AV213" s="6" t="s">
         <x:v>97</x:v>
@@ -52740,14 +52752,14 @@
       <x:c r="AX213" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AY213" t="s">
-        <x:v>1</x:v>
+      <x:c r="AY213" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AZ213" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BA213" t="s">
-        <x:v>1</x:v>
+      <x:c r="BA213" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BB213" s="6" t="s">
         <x:v>97</x:v>
@@ -52755,8 +52767,8 @@
       <x:c r="BC213" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BD213" t="s">
-        <x:v>1</x:v>
+      <x:c r="BD213" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BE213" s="6" t="s">
         <x:v>97</x:v>
@@ -52779,17 +52791,17 @@
       <x:c r="BK213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BL213" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BM213" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BN213" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BO213" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BL213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO213" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BP213" t="s">
         <x:v>1</x:v>
@@ -52800,8 +52812,8 @@
       <x:c r="BR213" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BS213" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BS213" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BT213" t="s">
         <x:v>1</x:v>
@@ -52809,14 +52821,14 @@
       <x:c r="BU213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BV213" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BW213" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BX213" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BV213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX213" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BY213" s="6" t="s">
         <x:v>97</x:v>
@@ -52824,8 +52836,8 @@
       <x:c r="BZ213" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="CA213" t="s">
-        <x:v>1</x:v>
+      <x:c r="CA213" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="CB213" s="6" t="s">
         <x:v>97</x:v>
@@ -52839,8 +52851,8 @@
       <x:c r="CE213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CF213" t="s">
-        <x:v>1</x:v>
+      <x:c r="CF213" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="CG213" s="6" t="s">
         <x:v>97</x:v>
@@ -52856,32 +52868,32 @@
       <x:c r="C214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D214" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="E214" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F214" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G214" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H214" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="I214" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="D214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K214" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="L214" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="K214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M214" t="s">
         <x:v>1</x:v>
@@ -52889,38 +52901,38 @@
       <x:c r="N214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O214" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="O214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="P214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q214" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="R214" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="S214" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="T214" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="U214" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="V214" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="W214" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="X214" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="Y214" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="Q214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Z214" t="s">
         <x:v>1</x:v>
@@ -52979,8 +52991,8 @@
       <x:c r="AR214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AS214" t="s">
-        <x:v>1</x:v>
+      <x:c r="AS214" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AT214" t="s">
         <x:v>1</x:v>
@@ -53015,14 +53027,14 @@
       <x:c r="BD214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG214" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BF214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BG214" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BH214" t="s">
         <x:v>1</x:v>
@@ -53039,11 +53051,11 @@
       <x:c r="BL214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BM214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN214" t="s">
-        <x:v>1</x:v>
+      <x:c r="BM214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BN214" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BO214" t="s">
         <x:v>1</x:v>
@@ -53063,8 +53075,8 @@
       <x:c r="BT214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BU214" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BU214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BV214" t="s">
         <x:v>1</x:v>
@@ -53134,11 +53146,11 @@
       <x:c r="J215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="L215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="K215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M215" s="6" t="s">
         <x:v>97</x:v>
@@ -53149,8 +53161,8 @@
       <x:c r="O215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P215" t="s">
-        <x:v>1</x:v>
+      <x:c r="P215" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="Q215" t="s">
         <x:v>1</x:v>
@@ -53212,17 +53224,17 @@
       <x:c r="AJ215" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AK215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AL215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AM215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AN215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AK215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AO215" s="6" t="s">
         <x:v>97</x:v>
@@ -53230,8 +53242,8 @@
       <x:c r="AP215" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AQ215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AQ215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AR215" t="s">
         <x:v>1</x:v>
@@ -53242,20 +53254,20 @@
       <x:c r="AT215" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AU215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AU215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AV215" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AW215" t="s">
-        <x:v>1</x:v>
+      <x:c r="AW215" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AX215" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AY215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AY215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AZ215" s="6" t="s">
         <x:v>97</x:v>
@@ -53269,8 +53281,8 @@
       <x:c r="BC215" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BD215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BD215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BE215" s="6" t="s">
         <x:v>97</x:v>
@@ -53287,23 +53299,23 @@
       <x:c r="BI215" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BJ215" t="s">
-        <x:v>1</x:v>
+      <x:c r="BJ215" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BK215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BL215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO215" t="s">
-        <x:v>1</x:v>
+      <x:c r="BL215" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BM215" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BN215" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BO215" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BP215" t="s">
         <x:v>1</x:v>
@@ -53314,8 +53326,8 @@
       <x:c r="BR215" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BS215" t="s">
-        <x:v>1</x:v>
+      <x:c r="BS215" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BT215" t="s">
         <x:v>1</x:v>
@@ -53323,26 +53335,26 @@
       <x:c r="BU215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BV215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX215" t="s">
-        <x:v>1</x:v>
+      <x:c r="BV215" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BW215" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BX215" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BY215" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BZ215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="CB215" t="s">
-        <x:v>1</x:v>
+      <x:c r="BZ215" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CA215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB215" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="CC215" s="6" t="s">
         <x:v>97</x:v>
@@ -53350,19 +53362,268 @@
       <x:c r="CD215" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="CE215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="CF215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="CG215" t="s">
-        <x:v>1</x:v>
+      <x:c r="CE215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG215" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
-      <x:c r="A216" s="3" t="s">
+      <x:c r="A216" s="4" t="s">
         <x:v>431</x:v>
+      </x:c>
+      <x:c r="B216" s="5" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="C216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="I216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="J216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="L216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="M216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="P216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="R216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="S216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="T216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="U216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="V216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="W216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="X216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Y216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Z216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BV216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CG216" t="s">
         <x:v>1</x:v>
@@ -53370,10 +53631,10 @@
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="4" t="s">
-        <x:v>432</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B217" s="5" t="s">
-        <x:v>433</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="C217" t="s">
         <x:v>1</x:v>
@@ -53399,23 +53660,23 @@
       <x:c r="J217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N217" t="s">
-        <x:v>1</x:v>
+      <x:c r="K217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="L217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="M217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="N217" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="O217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P217" t="s">
-        <x:v>1</x:v>
+      <x:c r="P217" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="Q217" t="s">
         <x:v>1</x:v>
@@ -53444,113 +53705,113 @@
       <x:c r="Y217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ217" t="s">
-        <x:v>1</x:v>
+      <x:c r="Z217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AA217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AB217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AC217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AD217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AE217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AF217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AG217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AH217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AI217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AJ217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AK217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AL217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AM217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AN217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AO217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AP217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AQ217" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AR217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AS217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT217" t="s">
-        <x:v>1</x:v>
+      <x:c r="AS217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AT217" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AU217" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AV217" t="s">
-        <x:v>1</x:v>
+      <x:c r="AV217" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AW217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ217" t="s">
-        <x:v>1</x:v>
+      <x:c r="AX217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AY217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AZ217" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BA217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI217" t="s">
-        <x:v>1</x:v>
+      <x:c r="BB217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BC217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BD217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BE217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BF217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BG217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BH217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BI217" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BJ217" t="s">
         <x:v>1</x:v>
@@ -53573,11 +53834,11 @@
       <x:c r="BP217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BQ217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR217" t="s">
-        <x:v>1</x:v>
+      <x:c r="BQ217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BR217" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BS217" t="s">
         <x:v>1</x:v>
@@ -53597,286 +53858,37 @@
       <x:c r="BX217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BY217" t="s">
-        <x:v>1</x:v>
+      <x:c r="BY217" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BZ217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CA217" t="s">
-        <x:v>1</x:v>
+      <x:c r="CA217" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="CB217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CC217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF217" t="s">
-        <x:v>1</x:v>
+      <x:c r="CC217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CD217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CE217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CF217" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="CG217" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
-      <x:c r="A218" s="4" t="s">
-        <x:v>434</x:v>
-      </x:c>
-      <x:c r="B218" s="5" t="s">
+      <x:c r="A218" s="3" t="s">
         <x:v>435</x:v>
-      </x:c>
-      <x:c r="C218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF218" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="CG218" t="s">
         <x:v>1</x:v>
@@ -53925,8 +53937,8 @@
       <x:c r="N219" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O219" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="O219" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="P219" t="s">
         <x:v>1</x:v>
@@ -54021,8 +54033,8 @@
       <x:c r="AT219" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AU219" t="s">
-        <x:v>1</x:v>
+      <x:c r="AU219" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AV219" t="s">
         <x:v>1</x:v>
@@ -54144,7 +54156,7 @@
         <x:v>438</x:v>
       </x:c>
       <x:c r="B220" s="5" t="s">
-        <x:v>110</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="C220" t="s">
         <x:v>1</x:v>
@@ -54329,8 +54341,8 @@
       <x:c r="BK220" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BL220" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BL220" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BM220" t="s">
         <x:v>1</x:v>
@@ -54398,10 +54410,10 @@
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="4" t="s">
-        <x:v>439</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B221" s="5" t="s">
-        <x:v>440</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="C221" t="s">
         <x:v>1</x:v>
@@ -54439,8 +54451,8 @@
       <x:c r="N221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O221" t="s">
-        <x:v>1</x:v>
+      <x:c r="O221" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="P221" t="s">
         <x:v>1</x:v>
@@ -54550,8 +54562,8 @@
       <x:c r="AY221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ221" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AZ221" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BA221" t="s">
         <x:v>1</x:v>
@@ -54622,8 +54634,8 @@
       <x:c r="BW221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BX221" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BX221" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BY221" t="s">
         <x:v>1</x:v>
@@ -54655,10 +54667,10 @@
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="4" t="s">
-        <x:v>441</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B222" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C222" t="s">
         <x:v>1</x:v>
@@ -54807,8 +54819,8 @@
       <x:c r="AY222" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ222" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AZ222" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BA222" t="s">
         <x:v>1</x:v>
@@ -54843,8 +54855,8 @@
       <x:c r="BK222" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BL222" t="s">
-        <x:v>1</x:v>
+      <x:c r="BL222" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BM222" t="s">
         <x:v>1</x:v>
@@ -54879,8 +54891,8 @@
       <x:c r="BW222" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BX222" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BX222" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BY222" t="s">
         <x:v>1</x:v>
@@ -55169,13 +55181,13 @@
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B224" s="5" t="s">
-        <x:v>445</x:v>
-      </x:c>
-      <x:c r="C224" s="6" t="s">
-        <x:v>97</x:v>
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="C224" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D224" t="s">
         <x:v>1</x:v>
@@ -55216,11 +55228,11 @@
       <x:c r="P224" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q224" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="R224" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="Q224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R224" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="S224" t="s">
         <x:v>1</x:v>
@@ -55240,11 +55252,11 @@
       <x:c r="X224" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Y224" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="Z224" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="Y224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z224" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AA224" t="s">
         <x:v>1</x:v>
@@ -55261,20 +55273,20 @@
       <x:c r="AE224" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AF224" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AG224" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AH224" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AI224" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AJ224" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AF224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ224" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AK224" t="s">
         <x:v>1</x:v>
@@ -55321,8 +55333,8 @@
       <x:c r="AY224" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ224" t="s">
-        <x:v>1</x:v>
+      <x:c r="AZ224" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BA224" t="s">
         <x:v>1</x:v>
@@ -55336,14 +55348,14 @@
       <x:c r="BD224" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE224" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BF224" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BG224" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BE224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG224" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH224" t="s">
         <x:v>1</x:v>
@@ -55393,8 +55405,8 @@
       <x:c r="BW224" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BX224" t="s">
-        <x:v>1</x:v>
+      <x:c r="BX224" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BY224" t="s">
         <x:v>1</x:v>
@@ -55426,10 +55438,10 @@
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B225" s="5" t="s">
-        <x:v>446</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="C225" t="s">
         <x:v>1</x:v>
@@ -55578,11 +55590,11 @@
       <x:c r="AY225" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ225" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA225" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AZ225" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BA225" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BB225" t="s">
         <x:v>1</x:v>
@@ -55650,8 +55662,8 @@
       <x:c r="BW225" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BX225" t="s">
-        <x:v>1</x:v>
+      <x:c r="BX225" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BY225" t="s">
         <x:v>1</x:v>
@@ -55682,259 +55694,773 @@
       </x:c>
     </x:row>
     <x:row r="226">
-      <x:c r="A226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF226" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CG226" s="7" t="s">
+      <x:c r="A226" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B226" s="5" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="C226" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q226" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="R226" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="S226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y226" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Z226" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AA226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF226" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AG226" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AH226" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AI226" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AJ226" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AK226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE226" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BF226" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BG226" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BH226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B227" s="5" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="C227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA227" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BB227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF228" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG228" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -55986,7 +56512,7 @@
     <x:mergeCell ref="A185:CG185"/>
     <x:mergeCell ref="A192:CG192"/>
     <x:mergeCell ref="A203:CG203"/>
-    <x:mergeCell ref="A216:CG216"/>
+    <x:mergeCell ref="A218:CG218"/>
   </x:mergeCells>
 </x:worksheet>
 </file>
--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R6a90f30c270d4547"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R684a899600e54427"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -79,7 +79,7 @@
   </x:si>
   <x:si>
     <x:t>Python
- 3.14.5 </x:t>
+ 3.14.6 </x:t>
   </x:si>
   <x:si>
     <x:t>D
@@ -265,13 +265,13 @@
     <x:t>re</x:t>
   </x:si>
   <x:si>
-    <x:t>regex V0</x:t>
-  </x:si>
-  <x:si>
     <x:t>regex V1</x:t>
   </x:si>
   <x:si>
     <x:t>regex V1 (posix)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>real-regex</x:t>
   </x:si>
   <x:si>
     <x:t>Forgex</x:t>
@@ -1573,8 +1573,8 @@
     <x:col min="55" max="55" width="4.998" customWidth="1"/>
     <x:col min="56" max="56" width="3.599" customWidth="1"/>
     <x:col min="57" max="57" width="9.197" customWidth="1"/>
-    <x:col min="58" max="58" width="9.197" customWidth="1"/>
-    <x:col min="59" max="59" width="15.091" customWidth="1"/>
+    <x:col min="58" max="58" width="15.091" customWidth="1"/>
+    <x:col min="59" max="59" width="10.094" customWidth="1"/>
     <x:col min="60" max="60" width="7.5" customWidth="1"/>
     <x:col min="61" max="61" width="8" customWidth="1"/>
     <x:col min="62" max="62" width="7.597" customWidth="1"/>
@@ -5135,8 +5135,8 @@
       <x:c r="BF16" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG16" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG16" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH16" t="s">
         <x:v>1</x:v>
@@ -9252,11 +9252,11 @@
       <x:c r="BE33" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BF33" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BG33" t="s">
-        <x:v>1</x:v>
+      <x:c r="BF33" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG33" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BH33" s="6" t="s">
         <x:v>97</x:v>
@@ -14917,8 +14917,8 @@
       <x:c r="BF56" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG56" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG56" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH56" t="s">
         <x:v>1</x:v>
@@ -17495,8 +17495,8 @@
       <x:c r="BF67" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG67" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG67" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH67" t="s">
         <x:v>1</x:v>
@@ -17752,8 +17752,8 @@
       <x:c r="BF68" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG68" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG68" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH68" t="s">
         <x:v>1</x:v>
@@ -20836,8 +20836,8 @@
       <x:c r="BF80" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG80" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG80" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH80" t="s">
         <x:v>1</x:v>
@@ -23671,8 +23671,8 @@
       <x:c r="BF92" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG92" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG92" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH92" t="s">
         <x:v>1</x:v>
@@ -25213,8 +25213,8 @@
       <x:c r="BF98" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG98" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG98" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH98" t="s">
         <x:v>1</x:v>
@@ -25470,8 +25470,8 @@
       <x:c r="BF99" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG99" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG99" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH99" s="6" t="s">
         <x:v>97</x:v>
@@ -25727,8 +25727,8 @@
       <x:c r="BF100" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG100" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG100" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH100" s="6" t="s">
         <x:v>97</x:v>
@@ -27277,8 +27277,8 @@
       <x:c r="BF107" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG107" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG107" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH107" s="6" t="s">
         <x:v>97</x:v>
@@ -28819,8 +28819,8 @@
       <x:c r="BF113" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG113" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG113" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH113" s="6" t="s">
         <x:v>97</x:v>
@@ -29076,8 +29076,8 @@
       <x:c r="BF114" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG114" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG114" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH114" s="6" t="s">
         <x:v>97</x:v>
@@ -29333,8 +29333,8 @@
       <x:c r="BF115" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG115" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG115" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH115" t="s">
         <x:v>1</x:v>
@@ -30106,14 +30106,14 @@
       <x:c r="BD119" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE119" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE119" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BF119" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG119" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG119" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH119" s="6" t="s">
         <x:v>97</x:v>
@@ -32162,14 +32162,14 @@
       <x:c r="BD127" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE127" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE127" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BF127" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG127" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG127" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH127" s="6" t="s">
         <x:v>97</x:v>
@@ -32419,14 +32419,14 @@
       <x:c r="BD128" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE128" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE128" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BF128" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG128" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG128" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH128" s="6" t="s">
         <x:v>97</x:v>
@@ -32676,14 +32676,14 @@
       <x:c r="BD129" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE129" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE129" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BF129" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG129" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG129" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH129" s="6" t="s">
         <x:v>97</x:v>
@@ -32933,14 +32933,14 @@
       <x:c r="BD130" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE130" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE130" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BF130" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG130" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG130" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH130" s="6" t="s">
         <x:v>97</x:v>
@@ -34232,8 +34232,8 @@
       <x:c r="BF136" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG136" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG136" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH136" t="s">
         <x:v>1</x:v>
@@ -34489,8 +34489,8 @@
       <x:c r="BF137" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG137" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG137" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH137" t="s">
         <x:v>1</x:v>
@@ -35517,8 +35517,8 @@
       <x:c r="BF141" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG141" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG141" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH141" t="s">
         <x:v>1</x:v>
@@ -35774,8 +35774,8 @@
       <x:c r="BF142" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG142" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG142" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH142" t="s">
         <x:v>1</x:v>
@@ -36031,8 +36031,8 @@
       <x:c r="BF143" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BG143" t="s">
-        <x:v>1</x:v>
+      <x:c r="BG143" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BH143" t="s">
         <x:v>1</x:v>
@@ -37838,8 +37838,8 @@
       <x:c r="BF151" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG151" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG151" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH151" s="6" t="s">
         <x:v>97</x:v>
@@ -38095,8 +38095,8 @@
       <x:c r="BF152" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG152" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG152" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH152" s="6" t="s">
         <x:v>97</x:v>
@@ -38352,8 +38352,8 @@
       <x:c r="BF153" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG153" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG153" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH153" s="6" t="s">
         <x:v>97</x:v>
@@ -40408,8 +40408,8 @@
       <x:c r="BF161" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG161" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG161" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH161" t="s">
         <x:v>1</x:v>
@@ -42464,8 +42464,8 @@
       <x:c r="BF169" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG169" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG169" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH169" t="s">
         <x:v>1</x:v>
@@ -44014,8 +44014,8 @@
       <x:c r="BF176" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG176" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG176" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH176" s="6" t="s">
         <x:v>97</x:v>
@@ -44785,8 +44785,8 @@
       <x:c r="BF179" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG179" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG179" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH179" s="6" t="s">
         <x:v>97</x:v>
@@ -45042,8 +45042,8 @@
       <x:c r="BF180" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG180" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG180" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH180" t="s">
         <x:v>1</x:v>
@@ -45299,8 +45299,8 @@
       <x:c r="BF181" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG181" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG181" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH181" t="s">
         <x:v>1</x:v>
@@ -46335,8 +46335,8 @@
       <x:c r="BF186" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG186" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG186" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH186" t="s">
         <x:v>1</x:v>
@@ -46592,8 +46592,8 @@
       <x:c r="BF187" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG187" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG187" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH187" t="s">
         <x:v>1</x:v>
@@ -46849,8 +46849,8 @@
       <x:c r="BF188" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG188" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG188" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH188" t="s">
         <x:v>1</x:v>
@@ -47106,8 +47106,8 @@
       <x:c r="BF189" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG189" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG189" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH189" t="s">
         <x:v>1</x:v>
@@ -47363,8 +47363,8 @@
       <x:c r="BF190" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG190" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG190" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH190" t="s">
         <x:v>1</x:v>
@@ -47885,8 +47885,8 @@
       <x:c r="BF193" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG193" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG193" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH193" t="s">
         <x:v>1</x:v>
@@ -48142,8 +48142,8 @@
       <x:c r="BF194" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG194" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG194" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH194" t="s">
         <x:v>1</x:v>
@@ -48399,8 +48399,8 @@
       <x:c r="BF195" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG195" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG195" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH195" t="s">
         <x:v>1</x:v>
@@ -49941,8 +49941,8 @@
       <x:c r="BF201" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG201" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG201" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH201" t="s">
         <x:v>1</x:v>
@@ -50463,8 +50463,8 @@
       <x:c r="BF204" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG204" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG204" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH204" t="s">
         <x:v>1</x:v>
@@ -51234,8 +51234,8 @@
       <x:c r="BF207" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG207" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG207" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH207" t="s">
         <x:v>1</x:v>
@@ -52262,8 +52262,8 @@
       <x:c r="BF211" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG211" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG211" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH211" s="6" t="s">
         <x:v>97</x:v>
@@ -52519,8 +52519,8 @@
       <x:c r="BF212" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG212" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH212" s="6" t="s">
         <x:v>97</x:v>
@@ -53033,8 +53033,8 @@
       <x:c r="BF214" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG214" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH214" t="s">
         <x:v>1</x:v>
@@ -53804,8 +53804,8 @@
       <x:c r="BF217" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG217" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH217" s="6" t="s">
         <x:v>97</x:v>
@@ -55868,8 +55868,8 @@
       <x:c r="BF226" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG226" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG226" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH226" t="s">
         <x:v>1</x:v>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R684a899600e54427"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R18bb6aefb12f482d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.6.21 </x:t>
+ 2026.7.2 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>
@@ -1600,7 +1600,7 @@
     <x:col min="82" max="82" width="14.292" customWidth="1"/>
     <x:col min="83" max="83" width="8.396" customWidth="1"/>
     <x:col min="84" max="84" width="16.391" customWidth="1"/>
-    <x:col min="85" max="85" width="11" customWidth="1"/>
+    <x:col min="85" max="85" width="10" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="49" customHeight="1">
@@ -52262,8 +52262,8 @@
       <x:c r="BF211" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG211" t="s">
-        <x:v>1</x:v>
+      <x:c r="BG211" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BH211" s="6" t="s">
         <x:v>97</x:v>
@@ -52340,8 +52340,8 @@
       <x:c r="CF211" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="CG211" t="s">
-        <x:v>1</x:v>
+      <x:c r="CG211" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -52519,8 +52519,8 @@
       <x:c r="BF212" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG212" t="s">
-        <x:v>1</x:v>
+      <x:c r="BG212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BH212" s="6" t="s">
         <x:v>97</x:v>
@@ -52597,8 +52597,8 @@
       <x:c r="CF212" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="CG212" t="s">
-        <x:v>1</x:v>
+      <x:c r="CG212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -53804,8 +53804,8 @@
       <x:c r="BF217" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG217" t="s">
-        <x:v>1</x:v>
+      <x:c r="BG217" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BH217" s="6" t="s">
         <x:v>97</x:v>
@@ -53882,8 +53882,8 @@
       <x:c r="CF217" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="CG217" t="s">
-        <x:v>1</x:v>
+      <x:c r="CG217" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="218">

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R18bb6aefb12f482d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R56c98883c66c45d2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1135,6 +1135,12 @@
     <x:t>Negative lookbehind, variable-length</x:t>
   </x:si>
   <x:si>
+    <x:t>(?=…(?=…))</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nested lookarounds</x:t>
+  </x:si>
+  <x:si>
     <x:t>(?&gt;…)</x:t>
   </x:si>
   <x:si>
@@ -44877,8 +44883,8 @@
       <x:c r="C180" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="D180" t="s">
-        <x:v>1</x:v>
+      <x:c r="D180" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E180" t="s">
         <x:v>1</x:v>
@@ -44895,14 +44901,14 @@
       <x:c r="I180" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J180" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K180" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L180" t="s">
-        <x:v>1</x:v>
+      <x:c r="J180" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="K180" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="L180" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M180" t="s">
         <x:v>1</x:v>
@@ -44910,8 +44916,8 @@
       <x:c r="N180" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O180" t="s">
-        <x:v>1</x:v>
+      <x:c r="O180" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="P180" s="6" t="s">
         <x:v>97</x:v>
@@ -44976,20 +44982,20 @@
       <x:c r="AJ180" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AK180" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL180" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM180" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN180" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO180" t="s">
-        <x:v>1</x:v>
+      <x:c r="AK180" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AL180" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AM180" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AN180" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AO180" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AP180" t="s">
         <x:v>1</x:v>
@@ -44997,8 +45003,8 @@
       <x:c r="AQ180" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AR180" t="s">
-        <x:v>1</x:v>
+      <x:c r="AR180" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AS180" t="s">
         <x:v>1</x:v>
@@ -45018,14 +45024,14 @@
       <x:c r="AX180" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AY180" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ180" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA180" t="s">
-        <x:v>1</x:v>
+      <x:c r="AY180" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AZ180" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BA180" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BB180" s="6" t="s">
         <x:v>97</x:v>
@@ -45045,8 +45051,8 @@
       <x:c r="BG180" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BH180" t="s">
-        <x:v>1</x:v>
+      <x:c r="BH180" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BI180" s="6" t="s">
         <x:v>97</x:v>
@@ -45084,8 +45090,8 @@
       <x:c r="BT180" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BU180" t="s">
-        <x:v>1</x:v>
+      <x:c r="BU180" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BV180" t="s">
         <x:v>1</x:v>
@@ -45105,8 +45111,8 @@
       <x:c r="CA180" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="CB180" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="CB180" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CC180" t="s">
         <x:v>1</x:v>
@@ -45114,11 +45120,11 @@
       <x:c r="CD180" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CE180" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF180" t="s">
-        <x:v>1</x:v>
+      <x:c r="CE180" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CF180" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="CG180" t="s">
         <x:v>1</x:v>
@@ -45131,8 +45137,8 @@
       <x:c r="B181" s="5" t="s">
         <x:v>368</x:v>
       </x:c>
-      <x:c r="C181" t="s">
-        <x:v>1</x:v>
+      <x:c r="C181" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D181" t="s">
         <x:v>1</x:v>
@@ -45200,8 +45206,8 @@
       <x:c r="Y181" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="Z181" t="s">
-        <x:v>1</x:v>
+      <x:c r="Z181" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AA181" t="s">
         <x:v>1</x:v>
@@ -45209,8 +45215,8 @@
       <x:c r="AB181" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AC181" t="s">
-        <x:v>1</x:v>
+      <x:c r="AC181" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AD181" t="s">
         <x:v>1</x:v>
@@ -45218,20 +45224,20 @@
       <x:c r="AE181" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AF181" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG181" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH181" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI181" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ181" t="s">
-        <x:v>1</x:v>
+      <x:c r="AF181" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AG181" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AH181" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AI181" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AJ181" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AK181" t="s">
         <x:v>1</x:v>
@@ -45251,8 +45257,8 @@
       <x:c r="AP181" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AQ181" t="s">
-        <x:v>1</x:v>
+      <x:c r="AQ181" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AR181" t="s">
         <x:v>1</x:v>
@@ -45263,8 +45269,8 @@
       <x:c r="AT181" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AU181" t="s">
-        <x:v>1</x:v>
+      <x:c r="AU181" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AV181" t="s">
         <x:v>1</x:v>
@@ -45272,8 +45278,8 @@
       <x:c r="AW181" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX181" t="s">
-        <x:v>1</x:v>
+      <x:c r="AX181" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AY181" t="s">
         <x:v>1</x:v>
@@ -45284,14 +45290,14 @@
       <x:c r="BA181" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB181" t="s">
-        <x:v>1</x:v>
+      <x:c r="BB181" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BC181" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BD181" t="s">
-        <x:v>1</x:v>
+      <x:c r="BD181" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BE181" s="6" t="s">
         <x:v>97</x:v>
@@ -45335,11 +45341,11 @@
       <x:c r="BR181" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BS181" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT181" t="s">
-        <x:v>1</x:v>
+      <x:c r="BS181" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BT181" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BU181" t="s">
         <x:v>1</x:v>
@@ -45359,11 +45365,11 @@
       <x:c r="BZ181" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CA181" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB181" t="s">
-        <x:v>1</x:v>
+      <x:c r="CA181" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CB181" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="CC181" t="s">
         <x:v>1</x:v>
@@ -45430,11 +45436,11 @@
       <x:c r="P182" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="Q182" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R182" t="s">
-        <x:v>1</x:v>
+      <x:c r="Q182" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="R182" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="S182" t="s">
         <x:v>1</x:v>
@@ -45454,8 +45460,8 @@
       <x:c r="X182" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Y182" t="s">
-        <x:v>1</x:v>
+      <x:c r="Y182" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="Z182" t="s">
         <x:v>1</x:v>
@@ -45517,8 +45523,8 @@
       <x:c r="AS182" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AT182" t="s">
-        <x:v>1</x:v>
+      <x:c r="AT182" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AU182" t="s">
         <x:v>1</x:v>
@@ -45550,11 +45556,11 @@
       <x:c r="BD182" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE182" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF182" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE182" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BF182" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BG182" t="s">
         <x:v>1</x:v>
@@ -45562,8 +45568,8 @@
       <x:c r="BH182" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BI182" t="s">
-        <x:v>1</x:v>
+      <x:c r="BI182" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BJ182" t="s">
         <x:v>1</x:v>
@@ -45586,8 +45592,8 @@
       <x:c r="BP182" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BQ182" t="s">
-        <x:v>1</x:v>
+      <x:c r="BQ182" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BR182" s="6" t="s">
         <x:v>97</x:v>
@@ -45941,8 +45947,8 @@
       <x:c r="O184" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P184" t="s">
-        <x:v>1</x:v>
+      <x:c r="P184" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="Q184" t="s">
         <x:v>1</x:v>
@@ -45971,8 +45977,8 @@
       <x:c r="Y184" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z184" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="Z184" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AA184" t="s">
         <x:v>1</x:v>
@@ -45992,14 +45998,14 @@
       <x:c r="AF184" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AG184" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AH184" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AI184" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AG184" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH184" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI184" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AJ184" t="s">
         <x:v>1</x:v>
@@ -46043,8 +46049,8 @@
       <x:c r="AW184" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX184" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AX184" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AY184" t="s">
         <x:v>1</x:v>
@@ -46103,8 +46109,8 @@
       <x:c r="BQ184" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BR184" t="s">
-        <x:v>1</x:v>
+      <x:c r="BR184" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BS184" t="s">
         <x:v>1</x:v>
@@ -46153,265 +46159,265 @@
       </x:c>
     </x:row>
     <x:row r="185">
-      <x:c r="A185" s="3" t="s">
+      <x:c r="A185" s="4" t="s">
         <x:v>375</x:v>
+      </x:c>
+      <x:c r="B185" s="5" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="C185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z185" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AA185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG185" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AH185" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AI185" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AJ185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX185" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AY185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE185" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF185" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CG185" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
-      <x:c r="A186" s="4" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="B186" s="5" t="s">
+      <x:c r="A186" s="3" t="s">
         <x:v>377</x:v>
-      </x:c>
-      <x:c r="C186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P186" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="Q186" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="R186" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="S186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH186" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AI186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT186" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AU186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE186" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BF186" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BG186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI186" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BJ186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ186" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BR186" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BS186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE186" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF186" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="CG186" t="s">
         <x:v>1</x:v>
@@ -46490,8 +46496,8 @@
       <x:c r="X187" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Y187" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="Y187" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Z187" t="s">
         <x:v>1</x:v>
@@ -46747,8 +46753,8 @@
       <x:c r="X188" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Y188" t="s">
-        <x:v>1</x:v>
+      <x:c r="Y188" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="Z188" t="s">
         <x:v>1</x:v>
@@ -46774,8 +46780,8 @@
       <x:c r="AG188" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH188" t="s">
-        <x:v>1</x:v>
+      <x:c r="AH188" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AI188" t="s">
         <x:v>1</x:v>
@@ -46888,8 +46894,8 @@
       <x:c r="BS188" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BT188" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BT188" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BU188" t="s">
         <x:v>1</x:v>
@@ -47031,8 +47037,8 @@
       <x:c r="AG189" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH189" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AH189" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AI189" t="s">
         <x:v>1</x:v>
@@ -47145,8 +47151,8 @@
       <x:c r="BS189" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BT189" t="s">
-        <x:v>1</x:v>
+      <x:c r="BT189" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BU189" t="s">
         <x:v>1</x:v>
@@ -47193,7 +47199,7 @@
         <x:v>384</x:v>
       </x:c>
       <x:c r="B190" s="5" t="s">
-        <x:v>383</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="C190" t="s">
         <x:v>1</x:v>
@@ -47237,11 +47243,11 @@
       <x:c r="P190" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="Q190" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R190" t="s">
-        <x:v>1</x:v>
+      <x:c r="Q190" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="R190" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="S190" t="s">
         <x:v>1</x:v>
@@ -47288,14 +47294,14 @@
       <x:c r="AG190" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH190" t="s">
-        <x:v>1</x:v>
+      <x:c r="AH190" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AI190" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AJ190" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AJ190" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AK190" t="s">
         <x:v>1</x:v>
@@ -47336,8 +47342,8 @@
       <x:c r="AW190" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX190" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AX190" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AY190" t="s">
         <x:v>1</x:v>
@@ -47447,11 +47453,11 @@
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="4" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="B191" s="5" t="s">
         <x:v>385</x:v>
       </x:c>
-      <x:c r="B191" s="5" t="s">
-        <x:v>386</x:v>
-      </x:c>
       <x:c r="C191" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -47551,8 +47557,8 @@
       <x:c r="AI191" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AJ191" t="s">
-        <x:v>1</x:v>
+      <x:c r="AJ191" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AK191" t="s">
         <x:v>1</x:v>
@@ -47581,8 +47587,8 @@
       <x:c r="AS191" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AT191" t="s">
-        <x:v>1</x:v>
+      <x:c r="AT191" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AU191" t="s">
         <x:v>1</x:v>
@@ -47593,8 +47599,8 @@
       <x:c r="AW191" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX191" t="s">
-        <x:v>1</x:v>
+      <x:c r="AX191" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AY191" t="s">
         <x:v>1</x:v>
@@ -47614,11 +47620,11 @@
       <x:c r="BD191" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE191" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF191" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE191" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BF191" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BG191" t="s">
         <x:v>1</x:v>
@@ -47626,8 +47632,8 @@
       <x:c r="BH191" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BI191" t="s">
-        <x:v>1</x:v>
+      <x:c r="BI191" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BJ191" t="s">
         <x:v>1</x:v>
@@ -47650,11 +47656,11 @@
       <x:c r="BP191" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BQ191" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR191" t="s">
-        <x:v>1</x:v>
+      <x:c r="BQ191" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BR191" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BS191" t="s">
         <x:v>1</x:v>
@@ -47703,265 +47709,265 @@
       </x:c>
     </x:row>
     <x:row r="192">
-      <x:c r="A192" s="3" t="s">
+      <x:c r="A192" s="4" t="s">
         <x:v>387</x:v>
+      </x:c>
+      <x:c r="B192" s="5" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="C192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P192" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Q192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE192" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF192" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CG192" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
-      <x:c r="A193" s="4" t="s">
-        <x:v>388</x:v>
-      </x:c>
-      <x:c r="B193" s="5" t="s">
+      <x:c r="A193" s="3" t="s">
         <x:v>389</x:v>
-      </x:c>
-      <x:c r="C193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="Q193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="R193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="S193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AA193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AH193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AI193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AJ193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AK193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AU193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AY193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BE193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BF193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BG193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BJ193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BR193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BS193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BU193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA193" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="CB193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE193" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF193" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="CG193" t="s">
         <x:v>1</x:v>
@@ -48016,11 +48022,11 @@
       <x:c r="P194" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="Q194" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R194" t="s">
-        <x:v>1</x:v>
+      <x:c r="Q194" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="R194" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="S194" t="s">
         <x:v>1</x:v>
@@ -48043,8 +48049,8 @@
       <x:c r="Y194" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z194" t="s">
-        <x:v>1</x:v>
+      <x:c r="Z194" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AA194" t="s">
         <x:v>1</x:v>
@@ -48064,17 +48070,17 @@
       <x:c r="AF194" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AG194" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH194" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI194" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ194" t="s">
-        <x:v>1</x:v>
+      <x:c r="AG194" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AH194" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AI194" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AJ194" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AK194" t="s">
         <x:v>1</x:v>
@@ -48115,8 +48121,8 @@
       <x:c r="AW194" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX194" t="s">
-        <x:v>1</x:v>
+      <x:c r="AX194" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AY194" t="s">
         <x:v>1</x:v>
@@ -48148,8 +48154,8 @@
       <x:c r="BH194" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BI194" t="s">
-        <x:v>1</x:v>
+      <x:c r="BI194" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BJ194" t="s">
         <x:v>1</x:v>
@@ -48181,8 +48187,8 @@
       <x:c r="BS194" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BT194" t="s">
-        <x:v>1</x:v>
+      <x:c r="BT194" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BU194" t="s">
         <x:v>1</x:v>
@@ -48273,11 +48279,11 @@
       <x:c r="P195" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="Q195" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="R195" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="Q195" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R195" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="S195" t="s">
         <x:v>1</x:v>
@@ -48300,8 +48306,8 @@
       <x:c r="Y195" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z195" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="Z195" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AA195" t="s">
         <x:v>1</x:v>
@@ -48321,17 +48327,17 @@
       <x:c r="AF195" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AG195" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AH195" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AI195" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AJ195" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AG195" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH195" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI195" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ195" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AK195" t="s">
         <x:v>1</x:v>
@@ -48372,8 +48378,8 @@
       <x:c r="AW195" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX195" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AX195" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AY195" t="s">
         <x:v>1</x:v>
@@ -48390,8 +48396,8 @@
       <x:c r="BC195" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BD195" t="s">
-        <x:v>1</x:v>
+      <x:c r="BD195" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BE195" s="6" t="s">
         <x:v>97</x:v>
@@ -48405,8 +48411,8 @@
       <x:c r="BH195" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BI195" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BI195" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BJ195" t="s">
         <x:v>1</x:v>
@@ -48438,8 +48444,8 @@
       <x:c r="BS195" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BT195" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BT195" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BU195" t="s">
         <x:v>1</x:v>
@@ -48527,14 +48533,14 @@
       <x:c r="O196" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P196" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q196" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R196" t="s">
-        <x:v>1</x:v>
+      <x:c r="P196" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Q196" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="R196" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="S196" t="s">
         <x:v>1</x:v>
@@ -48557,8 +48563,8 @@
       <x:c r="Y196" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z196" t="s">
-        <x:v>1</x:v>
+      <x:c r="Z196" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AA196" t="s">
         <x:v>1</x:v>
@@ -48578,17 +48584,17 @@
       <x:c r="AF196" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AG196" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH196" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI196" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ196" t="s">
-        <x:v>1</x:v>
+      <x:c r="AG196" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AH196" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AI196" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AJ196" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AK196" t="s">
         <x:v>1</x:v>
@@ -48617,8 +48623,8 @@
       <x:c r="AS196" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AT196" t="s">
-        <x:v>1</x:v>
+      <x:c r="AT196" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AU196" t="s">
         <x:v>1</x:v>
@@ -48629,8 +48635,8 @@
       <x:c r="AW196" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX196" t="s">
-        <x:v>1</x:v>
+      <x:c r="AX196" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AY196" t="s">
         <x:v>1</x:v>
@@ -48650,11 +48656,11 @@
       <x:c r="BD196" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE196" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF196" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE196" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BF196" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BG196" t="s">
         <x:v>1</x:v>
@@ -48662,8 +48668,8 @@
       <x:c r="BH196" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BI196" t="s">
-        <x:v>1</x:v>
+      <x:c r="BI196" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BJ196" t="s">
         <x:v>1</x:v>
@@ -48686,17 +48692,17 @@
       <x:c r="BP196" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BQ196" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR196" t="s">
-        <x:v>1</x:v>
+      <x:c r="BQ196" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BR196" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BS196" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BT196" t="s">
-        <x:v>1</x:v>
+      <x:c r="BT196" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BU196" t="s">
         <x:v>1</x:v>
@@ -48743,10 +48749,10 @@
         <x:v>396</x:v>
       </x:c>
       <x:c r="B197" s="5" t="s">
-        <x:v>391</x:v>
-      </x:c>
-      <x:c r="C197" t="s">
-        <x:v>1</x:v>
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="C197" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D197" t="s">
         <x:v>1</x:v>
@@ -48784,14 +48790,14 @@
       <x:c r="O197" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P197" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="Q197" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="R197" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="P197" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q197" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R197" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="S197" t="s">
         <x:v>1</x:v>
@@ -48814,8 +48820,8 @@
       <x:c r="Y197" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z197" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="Z197" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AA197" t="s">
         <x:v>1</x:v>
@@ -48838,11 +48844,11 @@
       <x:c r="AG197" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH197" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AI197" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AH197" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI197" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AJ197" t="s">
         <x:v>1</x:v>
@@ -48874,8 +48880,8 @@
       <x:c r="AS197" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AT197" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AT197" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AU197" t="s">
         <x:v>1</x:v>
@@ -48886,8 +48892,8 @@
       <x:c r="AW197" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX197" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AX197" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AY197" t="s">
         <x:v>1</x:v>
@@ -48919,8 +48925,8 @@
       <x:c r="BH197" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BI197" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BI197" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BJ197" t="s">
         <x:v>1</x:v>
@@ -48943,11 +48949,11 @@
       <x:c r="BP197" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BQ197" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BR197" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BQ197" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR197" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BS197" t="s">
         <x:v>1</x:v>
@@ -48973,8 +48979,8 @@
       <x:c r="BZ197" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CA197" t="s">
-        <x:v>1</x:v>
+      <x:c r="CA197" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="CB197" t="s">
         <x:v>1</x:v>
@@ -48997,10 +49003,10 @@
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="4" t="s">
-        <x:v>397</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B198" s="5" t="s">
-        <x:v>391</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="C198" t="s">
         <x:v>1</x:v>
@@ -49101,8 +49107,8 @@
       <x:c r="AI198" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AJ198" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AJ198" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AK198" t="s">
         <x:v>1</x:v>
@@ -49254,10 +49260,10 @@
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="4" t="s">
-        <x:v>398</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B199" s="5" t="s">
-        <x:v>399</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="C199" t="s">
         <x:v>1</x:v>
@@ -49328,8 +49334,8 @@
       <x:c r="Y199" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z199" t="s">
-        <x:v>1</x:v>
+      <x:c r="Z199" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AA199" t="s">
         <x:v>1</x:v>
@@ -49352,14 +49358,14 @@
       <x:c r="AG199" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH199" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI199" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ199" t="s">
-        <x:v>1</x:v>
+      <x:c r="AH199" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AI199" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AJ199" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AK199" t="s">
         <x:v>1</x:v>
@@ -49400,8 +49406,8 @@
       <x:c r="AW199" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX199" t="s">
-        <x:v>1</x:v>
+      <x:c r="AX199" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AY199" t="s">
         <x:v>1</x:v>
@@ -49842,8 +49848,8 @@
       <x:c r="Y201" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z201" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="Z201" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AA201" t="s">
         <x:v>1</x:v>
@@ -49866,11 +49872,11 @@
       <x:c r="AG201" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH201" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AI201" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AH201" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI201" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AJ201" t="s">
         <x:v>1</x:v>
@@ -49893,8 +49899,8 @@
       <x:c r="AP201" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AQ201" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AQ201" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AR201" t="s">
         <x:v>1</x:v>
@@ -49914,8 +49920,8 @@
       <x:c r="AW201" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX201" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AX201" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AY201" t="s">
         <x:v>1</x:v>
@@ -49935,11 +49941,11 @@
       <x:c r="BD201" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE201" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BF201" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BE201" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF201" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BG201" t="s">
         <x:v>1</x:v>
@@ -50072,11 +50078,11 @@
       <x:c r="P202" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="Q202" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R202" t="s">
-        <x:v>1</x:v>
+      <x:c r="Q202" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="R202" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="S202" t="s">
         <x:v>1</x:v>
@@ -50099,8 +50105,8 @@
       <x:c r="Y202" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z202" t="s">
-        <x:v>1</x:v>
+      <x:c r="Z202" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AA202" t="s">
         <x:v>1</x:v>
@@ -50123,11 +50129,11 @@
       <x:c r="AG202" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH202" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI202" t="s">
-        <x:v>1</x:v>
+      <x:c r="AH202" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AI202" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AJ202" t="s">
         <x:v>1</x:v>
@@ -50150,8 +50156,8 @@
       <x:c r="AP202" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AQ202" t="s">
-        <x:v>1</x:v>
+      <x:c r="AQ202" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AR202" t="s">
         <x:v>1</x:v>
@@ -50159,8 +50165,8 @@
       <x:c r="AS202" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AT202" t="s">
-        <x:v>1</x:v>
+      <x:c r="AT202" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AU202" t="s">
         <x:v>1</x:v>
@@ -50171,8 +50177,8 @@
       <x:c r="AW202" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX202" t="s">
-        <x:v>1</x:v>
+      <x:c r="AX202" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AY202" t="s">
         <x:v>1</x:v>
@@ -50192,11 +50198,11 @@
       <x:c r="BD202" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE202" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF202" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE202" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BF202" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BG202" t="s">
         <x:v>1</x:v>
@@ -50204,8 +50210,8 @@
       <x:c r="BH202" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BI202" t="s">
-        <x:v>1</x:v>
+      <x:c r="BI202" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BJ202" t="s">
         <x:v>1</x:v>
@@ -50228,8 +50234,8 @@
       <x:c r="BP202" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BQ202" t="s">
-        <x:v>1</x:v>
+      <x:c r="BQ202" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BR202" s="6" t="s">
         <x:v>97</x:v>
@@ -50281,265 +50287,265 @@
       </x:c>
     </x:row>
     <x:row r="203">
-      <x:c r="A203" s="3" t="s">
+      <x:c r="A203" s="4" t="s">
         <x:v>406</x:v>
+      </x:c>
+      <x:c r="B203" s="5" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="C203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P203" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Q203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR203" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BS203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE203" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF203" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CG203" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
-      <x:c r="A204" s="4" t="s">
-        <x:v>407</x:v>
-      </x:c>
-      <x:c r="B204" s="5" t="s">
+      <x:c r="A204" s="3" t="s">
         <x:v>408</x:v>
-      </x:c>
-      <x:c r="C204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P204" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="Q204" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="R204" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="S204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z204" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AA204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG204" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AH204" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AI204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ204" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AK204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS204" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AT204" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AU204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX204" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AY204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE204" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BF204" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BG204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI204" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BJ204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ204" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BR204" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BS204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE204" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF204" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="CG204" t="s">
         <x:v>1</x:v>
@@ -50594,11 +50600,11 @@
       <x:c r="P205" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="Q205" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R205" t="s">
-        <x:v>1</x:v>
+      <x:c r="Q205" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="R205" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="S205" t="s">
         <x:v>1</x:v>
@@ -50621,8 +50627,8 @@
       <x:c r="Y205" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z205" t="s">
-        <x:v>1</x:v>
+      <x:c r="Z205" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AA205" t="s">
         <x:v>1</x:v>
@@ -50642,17 +50648,17 @@
       <x:c r="AF205" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AG205" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH205" t="s">
-        <x:v>1</x:v>
+      <x:c r="AG205" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AH205" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AI205" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AJ205" t="s">
-        <x:v>1</x:v>
+      <x:c r="AJ205" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AK205" t="s">
         <x:v>1</x:v>
@@ -50678,11 +50684,11 @@
       <x:c r="AR205" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AS205" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT205" t="s">
-        <x:v>1</x:v>
+      <x:c r="AS205" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AT205" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AU205" t="s">
         <x:v>1</x:v>
@@ -50693,8 +50699,8 @@
       <x:c r="AW205" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX205" t="s">
-        <x:v>1</x:v>
+      <x:c r="AX205" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AY205" t="s">
         <x:v>1</x:v>
@@ -50714,11 +50720,11 @@
       <x:c r="BD205" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE205" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF205" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE205" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BF205" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BG205" t="s">
         <x:v>1</x:v>
@@ -50750,8 +50756,8 @@
       <x:c r="BP205" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BQ205" t="s">
-        <x:v>1</x:v>
+      <x:c r="BQ205" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BR205" s="6" t="s">
         <x:v>97</x:v>
@@ -50878,8 +50884,8 @@
       <x:c r="Y206" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z206" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="Z206" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AA206" t="s">
         <x:v>1</x:v>
@@ -50899,17 +50905,17 @@
       <x:c r="AF206" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AG206" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AH206" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AG206" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH206" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AI206" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AJ206" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AJ206" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AK206" t="s">
         <x:v>1</x:v>
@@ -50983,8 +50989,8 @@
       <x:c r="BH206" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BI206" t="s">
-        <x:v>1</x:v>
+      <x:c r="BI206" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BJ206" t="s">
         <x:v>1</x:v>
@@ -51010,8 +51016,8 @@
       <x:c r="BQ206" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BR206" t="s">
-        <x:v>1</x:v>
+      <x:c r="BR206" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BS206" t="s">
         <x:v>1</x:v>
@@ -51096,8 +51102,8 @@
       <x:c r="L207" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M207" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="M207" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N207" t="s">
         <x:v>1</x:v>
@@ -51135,8 +51141,8 @@
       <x:c r="Y207" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z207" t="s">
-        <x:v>1</x:v>
+      <x:c r="Z207" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AA207" t="s">
         <x:v>1</x:v>
@@ -51156,17 +51162,17 @@
       <x:c r="AF207" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AG207" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH207" t="s">
-        <x:v>1</x:v>
+      <x:c r="AG207" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AH207" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AI207" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AJ207" t="s">
-        <x:v>1</x:v>
+      <x:c r="AJ207" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AK207" t="s">
         <x:v>1</x:v>
@@ -51183,8 +51189,8 @@
       <x:c r="AO207" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AP207" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AP207" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AQ207" t="s">
         <x:v>1</x:v>
@@ -51192,11 +51198,11 @@
       <x:c r="AR207" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AS207" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AT207" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AS207" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT207" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AU207" t="s">
         <x:v>1</x:v>
@@ -51219,20 +51225,20 @@
       <x:c r="BA207" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB207" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BC207" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BB207" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC207" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD207" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE207" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BF207" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BE207" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF207" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BG207" t="s">
         <x:v>1</x:v>
@@ -51240,8 +51246,8 @@
       <x:c r="BH207" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BI207" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BI207" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BJ207" t="s">
         <x:v>1</x:v>
@@ -51255,8 +51261,8 @@
       <x:c r="BM207" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BN207" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BN207" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BO207" t="s">
         <x:v>1</x:v>
@@ -51264,23 +51270,23 @@
       <x:c r="BP207" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BQ207" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BR207" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BQ207" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR207" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BS207" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BT207" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BT207" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BU207" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BV207" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BV207" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BW207" t="s">
         <x:v>1</x:v>
@@ -51288,8 +51294,8 @@
       <x:c r="BX207" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BY207" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BY207" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BZ207" t="s">
         <x:v>1</x:v>
@@ -51300,11 +51306,11 @@
       <x:c r="CB207" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CC207" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="CD207" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="CC207" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD207" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CE207" t="s">
         <x:v>1</x:v>
@@ -51326,8 +51332,8 @@
       <x:c r="C208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D208" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="D208" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E208" t="s">
         <x:v>1</x:v>
@@ -51344,17 +51350,17 @@
       <x:c r="I208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J208" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="K208" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="L208" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="M208" t="s">
-        <x:v>1</x:v>
+      <x:c r="J208" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K208" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L208" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M208" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N208" t="s">
         <x:v>1</x:v>
@@ -51425,35 +51431,35 @@
       <x:c r="AJ208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AK208" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AL208" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AM208" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AN208" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AO208" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AP208" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ208" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AK208" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL208" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM208" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN208" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO208" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP208" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AQ208" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AR208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AS208" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT208" t="s">
-        <x:v>1</x:v>
+      <x:c r="AS208" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AT208" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AU208" t="s">
         <x:v>1</x:v>
@@ -51467,29 +51473,29 @@
       <x:c r="AX208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AY208" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AY208" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AZ208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BA208" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BB208" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC208" t="s">
-        <x:v>1</x:v>
+      <x:c r="BA208" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB208" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BC208" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BD208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE208" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF208" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE208" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BF208" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BG208" t="s">
         <x:v>1</x:v>
@@ -51497,14 +51503,14 @@
       <x:c r="BH208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BI208" t="s">
-        <x:v>1</x:v>
+      <x:c r="BI208" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BJ208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BK208" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BK208" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BL208" t="s">
         <x:v>1</x:v>
@@ -51512,29 +51518,29 @@
       <x:c r="BM208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BN208" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO208" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BN208" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BO208" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BP208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BQ208" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR208" t="s">
-        <x:v>1</x:v>
+      <x:c r="BQ208" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BR208" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BS208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BT208" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU208" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BT208" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BU208" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BV208" s="6" t="s">
         <x:v>97</x:v>
@@ -51545,8 +51551,8 @@
       <x:c r="BX208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BY208" t="s">
-        <x:v>1</x:v>
+      <x:c r="BY208" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BZ208" t="s">
         <x:v>1</x:v>
@@ -51554,20 +51560,20 @@
       <x:c r="CA208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CB208" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="CC208" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD208" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE208" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="CF208" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="CB208" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC208" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CD208" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CE208" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF208" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CG208" t="s">
         <x:v>1</x:v>
@@ -51784,8 +51790,8 @@
       <x:c r="BR209" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BS209" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BS209" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BT209" t="s">
         <x:v>1</x:v>
@@ -51837,26 +51843,26 @@
       <x:c r="B210" s="5" t="s">
         <x:v>420</x:v>
       </x:c>
-      <x:c r="C210" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="C210" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D210" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="E210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="I210" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="E210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I210" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J210" s="6" t="s">
         <x:v>97</x:v>
@@ -51867,11 +51873,11 @@
       <x:c r="L210" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="M210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="N210" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="M210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N210" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O210" t="s">
         <x:v>1</x:v>
@@ -51879,65 +51885,65 @@
       <x:c r="P210" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="Q210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="R210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="S210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="T210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="U210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="V210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="W210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="X210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="Y210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="Z210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AA210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AB210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AC210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AD210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AE210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AF210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AG210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AH210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AI210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AJ210" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="Q210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ210" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AK210" s="6" t="s">
         <x:v>97</x:v>
@@ -51954,128 +51960,128 @@
       <x:c r="AO210" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AP210" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AP210" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AQ210" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AR210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AS210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AT210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AU210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AV210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AW210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AX210" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AR210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX210" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AY210" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AZ210" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AZ210" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BA210" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BB210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BC210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BD210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BE210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BF210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BG210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BH210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BI210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BJ210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BK210" t="s">
-        <x:v>1</x:v>
+      <x:c r="BB210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK210" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BL210" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BM210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BN210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BO210" t="s">
-        <x:v>1</x:v>
+      <x:c r="BM210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO210" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BP210" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BQ210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BR210" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BQ210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR210" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BS210" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BT210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BU210" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV210" t="s">
-        <x:v>1</x:v>
+      <x:c r="BT210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU210" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BV210" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BW210" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BX210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BY210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BZ210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="CA210" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BX210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA210" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CB210" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="CC210" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="CD210" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="CC210" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD210" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CE210" s="6" t="s">
         <x:v>97</x:v>
@@ -52083,8 +52089,8 @@
       <x:c r="CF210" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="CG210" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="CG210" t="s">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -52354,26 +52360,26 @@
       <x:c r="C212" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="D212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J212" t="s">
-        <x:v>1</x:v>
+      <x:c r="D212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="I212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="J212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K212" s="6" t="s">
         <x:v>97</x:v>
@@ -52489,8 +52495,8 @@
       <x:c r="AV212" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AW212" t="s">
-        <x:v>1</x:v>
+      <x:c r="AW212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AX212" s="6" t="s">
         <x:v>97</x:v>
@@ -52501,8 +52507,8 @@
       <x:c r="AZ212" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BA212" t="s">
-        <x:v>1</x:v>
+      <x:c r="BA212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BB212" s="6" t="s">
         <x:v>97</x:v>
@@ -52528,8 +52534,8 @@
       <x:c r="BI212" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BJ212" t="s">
-        <x:v>1</x:v>
+      <x:c r="BJ212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BK212" t="s">
         <x:v>1</x:v>
@@ -52537,11 +52543,11 @@
       <x:c r="BL212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BM212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN212" t="s">
-        <x:v>1</x:v>
+      <x:c r="BM212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BN212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BO212" t="s">
         <x:v>1</x:v>
@@ -52555,11 +52561,11 @@
       <x:c r="BR212" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BS212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT212" t="s">
-        <x:v>1</x:v>
+      <x:c r="BS212" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BT212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BU212" t="s">
         <x:v>1</x:v>
@@ -52576,8 +52582,8 @@
       <x:c r="BY212" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BZ212" t="s">
-        <x:v>1</x:v>
+      <x:c r="BZ212" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="CA212" s="6" t="s">
         <x:v>97</x:v>
@@ -52608,8 +52614,8 @@
       <x:c r="B213" s="5" t="s">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="C213" t="s">
-        <x:v>1</x:v>
+      <x:c r="C213" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D213" t="s">
         <x:v>1</x:v>
@@ -52632,11 +52638,11 @@
       <x:c r="J213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L213" t="s">
-        <x:v>1</x:v>
+      <x:c r="K213" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="L213" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M213" s="6" t="s">
         <x:v>97</x:v>
@@ -52647,35 +52653,35 @@
       <x:c r="O213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y213" t="s">
-        <x:v>1</x:v>
+      <x:c r="P213" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Q213" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="R213" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="S213" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="T213" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="U213" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="V213" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="W213" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="X213" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Y213" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="Z213" s="6" t="s">
         <x:v>97</x:v>
@@ -52710,8 +52716,8 @@
       <x:c r="AJ213" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AK213" t="s">
-        <x:v>1</x:v>
+      <x:c r="AK213" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AL213" s="6" t="s">
         <x:v>97</x:v>
@@ -52731,8 +52737,8 @@
       <x:c r="AQ213" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AR213" t="s">
-        <x:v>1</x:v>
+      <x:c r="AR213" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AS213" s="6" t="s">
         <x:v>97</x:v>
@@ -52746,8 +52752,8 @@
       <x:c r="AV213" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AW213" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AW213" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AX213" s="6" t="s">
         <x:v>97</x:v>
@@ -52758,8 +52764,8 @@
       <x:c r="AZ213" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BA213" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BA213" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BB213" s="6" t="s">
         <x:v>97</x:v>
@@ -52785,8 +52791,8 @@
       <x:c r="BI213" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BJ213" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BJ213" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BK213" t="s">
         <x:v>1</x:v>
@@ -52827,14 +52833,14 @@
       <x:c r="BW213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BX213" t="s">
-        <x:v>1</x:v>
+      <x:c r="BX213" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BY213" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BZ213" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BZ213" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CA213" s="6" t="s">
         <x:v>97</x:v>
@@ -52848,8 +52854,8 @@
       <x:c r="CD213" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="CE213" t="s">
-        <x:v>1</x:v>
+      <x:c r="CE213" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="CF213" s="6" t="s">
         <x:v>97</x:v>
@@ -52895,11 +52901,11 @@
       <x:c r="L214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N214" t="s">
-        <x:v>1</x:v>
+      <x:c r="M214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="N214" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="O214" t="s">
         <x:v>1</x:v>
@@ -52934,59 +52940,59 @@
       <x:c r="Y214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ214" t="s">
-        <x:v>1</x:v>
+      <x:c r="Z214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AA214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AB214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AC214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AD214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AE214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AF214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AG214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AH214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AI214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AJ214" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AK214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AL214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ214" t="s">
-        <x:v>1</x:v>
+      <x:c r="AL214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AM214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AN214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AO214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AP214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AQ214" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AR214" t="s">
         <x:v>1</x:v>
@@ -52994,38 +53000,38 @@
       <x:c r="AS214" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AT214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD214" t="s">
-        <x:v>1</x:v>
+      <x:c r="AT214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AU214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AV214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AW214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AX214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AY214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AZ214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BA214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BB214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BC214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BD214" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BE214" s="6" t="s">
         <x:v>97</x:v>
@@ -53033,17 +53039,17 @@
       <x:c r="BF214" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ214" t="s">
-        <x:v>1</x:v>
+      <x:c r="BG214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BH214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BI214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BJ214" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BK214" t="s">
         <x:v>1</x:v>
@@ -53051,11 +53057,11 @@
       <x:c r="BL214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BM214" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BN214" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BM214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BO214" t="s">
         <x:v>1</x:v>
@@ -53063,11 +53069,11 @@
       <x:c r="BP214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BQ214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR214" t="s">
-        <x:v>1</x:v>
+      <x:c r="BQ214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BR214" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BS214" t="s">
         <x:v>1</x:v>
@@ -53087,32 +53093,32 @@
       <x:c r="BX214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BY214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD214" t="s">
-        <x:v>1</x:v>
+      <x:c r="BY214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BZ214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CA214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CB214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CC214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CD214" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="CE214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CF214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CG214" t="s">
-        <x:v>1</x:v>
+      <x:c r="CF214" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CG214" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -53152,17 +53158,17 @@
       <x:c r="L215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="N215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="M215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="P215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q215" t="s">
         <x:v>1</x:v>
@@ -53191,38 +53197,38 @@
       <x:c r="Y215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AA215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AB215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AC215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AD215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AE215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AF215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AG215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AH215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AI215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AJ215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="Z215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AK215" t="s">
         <x:v>1</x:v>
@@ -53236,11 +53242,11 @@
       <x:c r="AN215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AP215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AO215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AQ215" t="s">
         <x:v>1</x:v>
@@ -53251,35 +53257,35 @@
       <x:c r="AS215" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="AT215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AT215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AU215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AV215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AW215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AX215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AV215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AY215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AZ215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BA215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BC215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BB215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD215" t="s">
         <x:v>1</x:v>
@@ -53290,23 +53296,23 @@
       <x:c r="BF215" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BH215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BI215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BJ215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BG215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BK215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BL215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BL215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BM215" s="6" t="s">
         <x:v>97</x:v>
@@ -53314,20 +53320,20 @@
       <x:c r="BN215" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BO215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BO215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BP215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BQ215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BR215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BS215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BQ215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BT215" t="s">
         <x:v>1</x:v>
@@ -53335,32 +53341,32 @@
       <x:c r="BU215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BV215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BW215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BX215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BY215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BZ215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BV215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CA215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CB215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="CC215" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="CD215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="CB215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CE215" t="s">
         <x:v>1</x:v>
@@ -53368,8 +53374,8 @@
       <x:c r="CF215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CG215" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="CG215" t="s">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -53382,104 +53388,104 @@
       <x:c r="C216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D216" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="E216" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F216" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G216" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H216" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="I216" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="D216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K216" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="L216" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="M216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O216" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="P216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q216" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="R216" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="S216" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="T216" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="U216" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="V216" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="W216" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="X216" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="Y216" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="Z216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ216" t="s">
-        <x:v>1</x:v>
+      <x:c r="K216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="N216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="O216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Q216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AA216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AB216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AC216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AD216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AE216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AF216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AG216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AH216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AI216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AJ216" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AK216" t="s">
         <x:v>1</x:v>
@@ -53493,11 +53499,11 @@
       <x:c r="AN216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP216" t="s">
-        <x:v>1</x:v>
+      <x:c r="AO216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AP216" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AQ216" t="s">
         <x:v>1</x:v>
@@ -53505,119 +53511,119 @@
       <x:c r="AR216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AS216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT216" t="s">
-        <x:v>1</x:v>
+      <x:c r="AS216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AT216" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AU216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AV216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX216" t="s">
-        <x:v>1</x:v>
+      <x:c r="AV216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AW216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AX216" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AY216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ216" t="s">
-        <x:v>1</x:v>
+      <x:c r="AZ216" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BA216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC216" t="s">
-        <x:v>1</x:v>
+      <x:c r="BB216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BC216" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BD216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ216" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BF216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BG216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BH216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BI216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BJ216" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BK216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BL216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO216" t="s">
-        <x:v>1</x:v>
+      <x:c r="BL216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BM216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BN216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BO216" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BP216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BQ216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS216" t="s">
-        <x:v>1</x:v>
+      <x:c r="BQ216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BR216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BS216" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BT216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BU216" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BV216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ216" t="s">
-        <x:v>1</x:v>
+      <x:c r="BU216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BW216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BX216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BY216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BZ216" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="CA216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CB216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD216" t="s">
-        <x:v>1</x:v>
+      <x:c r="CB216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CC216" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CD216" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="CE216" t="s">
         <x:v>1</x:v>
@@ -53625,8 +53631,8 @@
       <x:c r="CF216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CG216" t="s">
-        <x:v>1</x:v>
+      <x:c r="CG216" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
@@ -53639,23 +53645,23 @@
       <x:c r="C217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I217" t="s">
-        <x:v>1</x:v>
+      <x:c r="D217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="I217" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="J217" t="s">
         <x:v>1</x:v>
@@ -53666,152 +53672,152 @@
       <x:c r="L217" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="M217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="N217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="O217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="Q217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AA217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AB217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AC217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AD217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AE217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AF217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AG217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AH217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AI217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AJ217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AK217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AL217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AM217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AN217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AO217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AP217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AQ217" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="M217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="P217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="R217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="S217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="T217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="U217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="V217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="W217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="X217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Y217" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Z217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AR217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AS217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AT217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AU217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AV217" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AS217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AW217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AY217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AZ217" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AX217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BA217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BC217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BD217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BE217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BF217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BG217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BH217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BI217" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BB217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BJ217" t="s">
         <x:v>1</x:v>
@@ -53834,11 +53840,11 @@
       <x:c r="BP217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BQ217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BR217" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BQ217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BS217" t="s">
         <x:v>1</x:v>
@@ -53846,8 +53852,8 @@
       <x:c r="BT217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BU217" t="s">
-        <x:v>1</x:v>
+      <x:c r="BU217" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BV217" t="s">
         <x:v>1</x:v>
@@ -53858,294 +53864,294 @@
       <x:c r="BX217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BY217" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BY217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BZ217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CA217" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="CA217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CB217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CC217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="CD217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="CE217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="CF217" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="CG217" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="CC217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG217" t="s">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
-      <x:c r="A218" s="3" t="s">
+      <x:c r="A218" s="4" t="s">
         <x:v>435</x:v>
       </x:c>
-      <x:c r="CG218" t="s">
-        <x:v>1</x:v>
+      <x:c r="B218" s="5" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="C218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="L218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="M218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="N218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="O218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Q218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AA218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AB218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AC218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AD218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AE218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AF218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AG218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AH218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AI218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AJ218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AK218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AL218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AM218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AN218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AO218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AP218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AQ218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AR218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AT218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AU218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AV218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AW218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AY218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AZ218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BA218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BC218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BD218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BE218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BF218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BG218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BH218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BI218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BJ218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BR218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BS218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BZ218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CB218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CD218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CE218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CF218" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="CG218" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
-      <x:c r="A219" s="4" t="s">
-        <x:v>436</x:v>
-      </x:c>
-      <x:c r="B219" s="5" t="s">
+      <x:c r="A219" s="3" t="s">
         <x:v>437</x:v>
-      </x:c>
-      <x:c r="C219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU219" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AV219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF219" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="CG219" t="s">
         <x:v>1</x:v>
@@ -54290,8 +54296,8 @@
       <x:c r="AT220" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AU220" t="s">
-        <x:v>1</x:v>
+      <x:c r="AU220" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AV220" t="s">
         <x:v>1</x:v>
@@ -54451,8 +54457,8 @@
       <x:c r="N221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O221" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="O221" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="P221" t="s">
         <x:v>1</x:v>
@@ -54670,7 +54676,7 @@
         <x:v>442</x:v>
       </x:c>
       <x:c r="B222" s="5" t="s">
-        <x:v>110</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="C222" t="s">
         <x:v>1</x:v>
@@ -54708,8 +54714,8 @@
       <x:c r="N222" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O222" t="s">
-        <x:v>1</x:v>
+      <x:c r="O222" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="P222" t="s">
         <x:v>1</x:v>
@@ -54855,8 +54861,8 @@
       <x:c r="BK222" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BL222" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BL222" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BM222" t="s">
         <x:v>1</x:v>
@@ -54924,10 +54930,10 @@
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="4" t="s">
-        <x:v>443</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B223" s="5" t="s">
-        <x:v>444</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C223" t="s">
         <x:v>1</x:v>
@@ -55076,8 +55082,8 @@
       <x:c r="AY223" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ223" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AZ223" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BA223" t="s">
         <x:v>1</x:v>
@@ -55112,8 +55118,8 @@
       <x:c r="BK223" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BL223" t="s">
-        <x:v>1</x:v>
+      <x:c r="BL223" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BM223" t="s">
         <x:v>1</x:v>
@@ -55148,8 +55154,8 @@
       <x:c r="BW223" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BX223" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BX223" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BY223" t="s">
         <x:v>1</x:v>
@@ -55695,13 +55701,13 @@
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B226" s="5" t="s">
-        <x:v>449</x:v>
-      </x:c>
-      <x:c r="C226" s="6" t="s">
-        <x:v>97</x:v>
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="C226" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D226" t="s">
         <x:v>1</x:v>
@@ -55742,11 +55748,11 @@
       <x:c r="P226" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q226" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="R226" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="Q226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R226" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="S226" t="s">
         <x:v>1</x:v>
@@ -55766,11 +55772,11 @@
       <x:c r="X226" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Y226" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="Z226" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="Y226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z226" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AA226" t="s">
         <x:v>1</x:v>
@@ -55787,20 +55793,20 @@
       <x:c r="AE226" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AF226" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AG226" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AH226" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AI226" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AJ226" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="AF226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ226" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AK226" t="s">
         <x:v>1</x:v>
@@ -55847,8 +55853,8 @@
       <x:c r="AY226" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ226" t="s">
-        <x:v>1</x:v>
+      <x:c r="AZ226" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BA226" t="s">
         <x:v>1</x:v>
@@ -55862,11 +55868,11 @@
       <x:c r="BD226" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE226" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BF226" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BE226" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF226" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BG226" t="s">
         <x:v>1</x:v>
@@ -55919,8 +55925,8 @@
       <x:c r="BW226" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BX226" t="s">
-        <x:v>1</x:v>
+      <x:c r="BX226" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BY226" t="s">
         <x:v>1</x:v>
@@ -55955,10 +55961,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B227" s="5" t="s">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="C227" t="s">
-        <x:v>1</x:v>
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="C227" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D227" t="s">
         <x:v>1</x:v>
@@ -55999,11 +56005,11 @@
       <x:c r="P227" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q227" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R227" t="s">
-        <x:v>1</x:v>
+      <x:c r="Q227" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="R227" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="S227" t="s">
         <x:v>1</x:v>
@@ -56023,11 +56029,11 @@
       <x:c r="X227" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Y227" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z227" t="s">
-        <x:v>1</x:v>
+      <x:c r="Y227" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Z227" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AA227" t="s">
         <x:v>1</x:v>
@@ -56044,20 +56050,20 @@
       <x:c r="AE227" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AF227" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG227" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH227" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI227" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ227" t="s">
-        <x:v>1</x:v>
+      <x:c r="AF227" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AG227" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AH227" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AI227" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AJ227" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AK227" t="s">
         <x:v>1</x:v>
@@ -56107,8 +56113,8 @@
       <x:c r="AZ227" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BA227" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="BA227" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BB227" t="s">
         <x:v>1</x:v>
@@ -56119,11 +56125,11 @@
       <x:c r="BD227" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE227" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF227" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE227" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BF227" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BG227" t="s">
         <x:v>1</x:v>
@@ -56208,259 +56214,516 @@
       </x:c>
     </x:row>
     <x:row r="228">
-      <x:c r="A228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF228" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CG228" s="7" t="s">
+      <x:c r="A228" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B228" s="5" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="C228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA228" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BB228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG228" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF229" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG229" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -56509,10 +56772,10 @@
     <x:mergeCell ref="A131:CG131"/>
     <x:mergeCell ref="A146:CG146"/>
     <x:mergeCell ref="A170:CG170"/>
-    <x:mergeCell ref="A185:CG185"/>
-    <x:mergeCell ref="A192:CG192"/>
-    <x:mergeCell ref="A203:CG203"/>
-    <x:mergeCell ref="A218:CG218"/>
+    <x:mergeCell ref="A186:CG186"/>
+    <x:mergeCell ref="A193:CG193"/>
+    <x:mergeCell ref="A204:CG204"/>
+    <x:mergeCell ref="A219:CG219"/>
   </x:mergeCells>
 </x:worksheet>
 </file>
--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R56c98883c66c45d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rcd9aabf843854d38"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.7.2 </x:t>
+ 2026.7.3 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>
@@ -27283,8 +27283,8 @@
       <x:c r="BF107" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG107" t="s">
-        <x:v>1</x:v>
+      <x:c r="BG107" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BH107" s="6" t="s">
         <x:v>97</x:v>
@@ -27361,8 +27361,8 @@
       <x:c r="CF107" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="CG107" t="s">
-        <x:v>1</x:v>
+      <x:c r="CG107" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="108">

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rcd9aabf843854d38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R2f77761af6c54fc8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R2f77761af6c54fc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R567d64d94c3f45b1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.7.3 </x:t>
+ 2026.7.8 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>
@@ -5141,8 +5141,8 @@
       <x:c r="BF16" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG16" t="s">
-        <x:v>1</x:v>
+      <x:c r="BG16" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BH16" t="s">
         <x:v>1</x:v>
@@ -5219,8 +5219,8 @@
       <x:c r="CF16" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="CG16" t="s">
-        <x:v>1</x:v>
+      <x:c r="CG16" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -14923,8 +14923,8 @@
       <x:c r="BF56" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG56" t="s">
-        <x:v>1</x:v>
+      <x:c r="BG56" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BH56" t="s">
         <x:v>1</x:v>
@@ -15001,8 +15001,8 @@
       <x:c r="CF56" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CG56" t="s">
-        <x:v>1</x:v>
+      <x:c r="CG56" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -17501,8 +17501,8 @@
       <x:c r="BF67" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG67" t="s">
-        <x:v>1</x:v>
+      <x:c r="BG67" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BH67" t="s">
         <x:v>1</x:v>
@@ -17579,8 +17579,8 @@
       <x:c r="CF67" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CG67" t="s">
-        <x:v>1</x:v>
+      <x:c r="CG67" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -17758,8 +17758,8 @@
       <x:c r="BF68" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG68" t="s">
-        <x:v>1</x:v>
+      <x:c r="BG68" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BH68" t="s">
         <x:v>1</x:v>
@@ -17836,8 +17836,8 @@
       <x:c r="CF68" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CG68" t="s">
-        <x:v>1</x:v>
+      <x:c r="CG68" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -20842,8 +20842,8 @@
       <x:c r="BF80" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG80" t="s">
-        <x:v>1</x:v>
+      <x:c r="BG80" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BH80" t="s">
         <x:v>1</x:v>
@@ -20920,8 +20920,8 @@
       <x:c r="CF80" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CG80" t="s">
-        <x:v>1</x:v>
+      <x:c r="CG80" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -34238,8 +34238,8 @@
       <x:c r="BF136" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BG136" t="s">
-        <x:v>1</x:v>
+      <x:c r="BG136" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BH136" t="s">
         <x:v>1</x:v>
@@ -34316,8 +34316,8 @@
       <x:c r="CF136" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CG136" t="s">
-        <x:v>1</x:v>
+      <x:c r="CG136" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="137">

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R567d64d94c3f45b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R73b7c57dbab74ed4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -127,7 +127,7 @@
   </x:si>
   <x:si>
     <x:t>RE#
- 1.0.3 </x:t>
+ 1.0.4 </x:t>
   </x:si>
   <x:si>
     <x:t>Go
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.7.8 </x:t>
+ 2026.7.19 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>
@@ -1606,7 +1606,7 @@
     <x:col min="82" max="82" width="14.292" customWidth="1"/>
     <x:col min="83" max="83" width="8.396" customWidth="1"/>
     <x:col min="84" max="84" width="16.391" customWidth="1"/>
-    <x:col min="85" max="85" width="10" customWidth="1"/>
+    <x:col min="85" max="85" width="11" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="49" customHeight="1">

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Ref08a4a068424e99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R53155b3bc2554f0c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.7.19 </x:t>
+ 2026.7.21 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R53155b3bc2554f0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rc75ce961ede14db9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15113,8 +15113,8 @@
       <x:c r="BR56" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BS56" t="s">
-        <x:v>1</x:v>
+      <x:c r="BS56" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BT56" t="s">
         <x:v>1</x:v>
@@ -21101,8 +21101,8 @@
       <x:c r="BR80" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BS80" t="s">
-        <x:v>1</x:v>
+      <x:c r="BS80" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BT80" t="s">
         <x:v>1</x:v>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rc75ce961ede14db9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R79afd2ead30442d5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.7.21 </x:t>
+ 2026.7.23 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>
@@ -25738,8 +25738,8 @@
       <x:c r="BA99" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB99" t="s">
-        <x:v>1</x:v>
+      <x:c r="BB99" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BC99" s="6" t="s">
         <x:v>97</x:v>
@@ -25756,8 +25756,8 @@
       <x:c r="BG99" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BH99" t="s">
-        <x:v>1</x:v>
+      <x:c r="BH99" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BI99" s="6" t="s">
         <x:v>97</x:v>
@@ -25834,8 +25834,8 @@
       <x:c r="CG99" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CH99" t="s">
-        <x:v>1</x:v>
+      <x:c r="CH99" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -25998,8 +25998,8 @@
       <x:c r="BA100" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB100" t="s">
-        <x:v>1</x:v>
+      <x:c r="BB100" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BC100" s="6" t="s">
         <x:v>97</x:v>
@@ -26016,8 +26016,8 @@
       <x:c r="BG100" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BH100" t="s">
-        <x:v>1</x:v>
+      <x:c r="BH100" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BI100" s="6" t="s">
         <x:v>97</x:v>
@@ -26094,8 +26094,8 @@
       <x:c r="CG100" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="CH100" t="s">
-        <x:v>1</x:v>
+      <x:c r="CH100" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -29126,8 +29126,8 @@
       <x:c r="BA113" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB113" t="s">
-        <x:v>1</x:v>
+      <x:c r="BB113" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BC113" s="6" t="s">
         <x:v>97</x:v>
@@ -29144,8 +29144,8 @@
       <x:c r="BG113" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BH113" t="s">
-        <x:v>1</x:v>
+      <x:c r="BH113" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BI113" s="6" t="s">
         <x:v>97</x:v>
@@ -29222,8 +29222,8 @@
       <x:c r="CG113" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CH113" t="s">
-        <x:v>1</x:v>
+      <x:c r="CH113" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -29386,8 +29386,8 @@
       <x:c r="BA114" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB114" t="s">
-        <x:v>1</x:v>
+      <x:c r="BB114" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BC114" s="6" t="s">
         <x:v>97</x:v>
@@ -29404,8 +29404,8 @@
       <x:c r="BG114" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BH114" t="s">
-        <x:v>1</x:v>
+      <x:c r="BH114" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BI114" s="6" t="s">
         <x:v>97</x:v>
@@ -29482,8 +29482,8 @@
       <x:c r="CG114" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="CH114" t="s">
-        <x:v>1</x:v>
+      <x:c r="CH114" s="6" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="115">

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R79afd2ead30442d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rec98bddc357e421f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.7.23 </x:t>
+ 2026.7.25 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rec98bddc357e421f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R467fc079db6947f3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.7.25 </x:t>
+ 2026.7.26 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>
@@ -1306,19 +1306,19 @@
     <x:t>Unicode</x:t>
   </x:si>
   <x:si>
-    <x:t>Supports Unicode characters, not just ASCII</x:t>
+    <x:t>Support Unicode characters, not just ASCII</x:t>
   </x:si>
   <x:si>
     <x:t>[Unicode]</x:t>
   </x:si>
   <x:si>
-    <x:t>Supports Unicode characters inside sets</x:t>
+    <x:t>Support Unicode characters inside sets</x:t>
   </x:si>
   <x:si>
     <x:t>é=É</x:t>
   </x:si>
   <x:si>
-    <x:t>Supports Unicode case folding</x:t>
+    <x:t>Support Unicode case folding</x:t>
   </x:si>
   <x:si>
     <x:t>Surrogates</x:t>
@@ -1396,7 +1396,7 @@
     <x:t>Get all captures matched by group</x:t>
   </x:si>
   <x:si>
-    <x:t>Also supports alternative syntax</x:t>
+    <x:t>Also support alternative syntax</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R23ad4140e41a40cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R1f99d93151a244f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1315,10 +1315,16 @@
     <x:t>Any character, even newline</x:t>
   </x:si>
   <x:si>
-    <x:t>Unicode</x:t>
+    <x:t>Unicode “.”</x:t>
   </x:si>
   <x:si>
-    <x:t>Support Unicode characters, not just ASCII</x:t>
+    <x:t>“.” matches Unicode characters, not just ASCII</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unicode “\w”</x:t>
+  </x:si>
+  <x:si>
+    <x:t>“\w” matches Unicode characters, not just ASCII</x:t>
   </x:si>
   <x:si>
     <x:t>[Unicode]</x:t>
@@ -22964,8 +22970,8 @@
       <x:c r="M86" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="N86" t="s">
-        <x:v>1</x:v>
+      <x:c r="N86" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="O86" s="6" t="s">
         <x:v>101</x:v>
@@ -24847,8 +24853,8 @@
       <x:c r="M93" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="N93" t="s">
-        <x:v>1</x:v>
+      <x:c r="N93" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="O93" s="6" t="s">
         <x:v>101</x:v>
@@ -25923,8 +25929,8 @@
       <x:c r="M97" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="N97" t="s">
-        <x:v>1</x:v>
+      <x:c r="N97" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="O97" s="6" t="s">
         <x:v>101</x:v>
@@ -27007,8 +27013,8 @@
       <x:c r="M102" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="N102" t="s">
-        <x:v>1</x:v>
+      <x:c r="N102" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="O102" t="s">
         <x:v>1</x:v>
@@ -28352,8 +28358,8 @@
       <x:c r="M107" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="N107" t="s">
-        <x:v>1</x:v>
+      <x:c r="N107" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="O107" t="s">
         <x:v>1</x:v>
@@ -29428,8 +29434,8 @@
       <x:c r="M111" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="N111" t="s">
-        <x:v>1</x:v>
+      <x:c r="N111" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="O111" t="s">
         <x:v>1</x:v>
@@ -36169,8 +36175,8 @@
       <x:c r="M138" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="N138" t="s">
-        <x:v>1</x:v>
+      <x:c r="N138" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="O138" t="s">
         <x:v>1</x:v>
@@ -36262,8 +36268,8 @@
       <x:c r="AR138" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="AS138" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="AS138" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AT138" s="6" t="s">
         <x:v>101</x:v>
@@ -54743,35 +54749,35 @@
       <x:c r="D212" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="E212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="F212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="G212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="I212" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="E212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J212" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="K212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="L212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="M212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="N212" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="K212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O212" t="s">
         <x:v>1</x:v>
@@ -54794,14 +54800,14 @@
       <x:c r="U212" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="V212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="W212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="X212" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="V212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Y212" s="6" t="s">
         <x:v>101</x:v>
@@ -54809,14 +54815,14 @@
       <x:c r="Z212" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="AA212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AB212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AC212" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="AA212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD212" s="6" t="s">
         <x:v>101</x:v>
@@ -54839,29 +54845,29 @@
       <x:c r="AJ212" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="AK212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AL212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AM212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AN212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AO212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AP212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AQ212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AR212" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="AK212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AS212" s="6" t="s">
         <x:v>101</x:v>
@@ -54875,23 +54881,23 @@
       <x:c r="AV212" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="AW212" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="AW212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AX212" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="AY212" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="AY212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AZ212" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="BA212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BB212" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BA212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BC212" s="6" t="s">
         <x:v>101</x:v>
@@ -54899,8 +54905,8 @@
       <x:c r="BD212" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="BE212" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BE212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BF212" s="6" t="s">
         <x:v>101</x:v>
@@ -54911,8 +54917,8 @@
       <x:c r="BH212" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="BI212" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BI212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BJ212" s="6" t="s">
         <x:v>101</x:v>
@@ -54923,8 +54929,8 @@
       <x:c r="BL212" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="BM212" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BM212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BN212" t="s">
         <x:v>1</x:v>
@@ -54932,11 +54938,11 @@
       <x:c r="BO212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BP212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BQ212" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BP212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BR212" t="s">
         <x:v>1</x:v>
@@ -54944,17 +54950,17 @@
       <x:c r="BS212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BT212" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BT212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BU212" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="BV212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BW212" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BV212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BX212" t="s">
         <x:v>1</x:v>
@@ -54968,32 +54974,32 @@
       <x:c r="CA212" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="CB212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="CC212" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="CB212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CD212" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="CE212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="CF212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="CG212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="CH212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="CI212" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="CJ212" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="CE212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CH212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CI212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CJ212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CK212" s="6" t="s">
         <x:v>101</x:v>
@@ -55009,26 +55015,26 @@
       <x:c r="C213" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="D213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J213" t="s">
-        <x:v>1</x:v>
+      <x:c r="D213" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="E213" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F213" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G213" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H213" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="I213" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="J213" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="K213" s="6" t="s">
         <x:v>101</x:v>
@@ -55144,8 +55150,8 @@
       <x:c r="AV213" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="AW213" t="s">
-        <x:v>1</x:v>
+      <x:c r="AW213" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="AX213" s="6" t="s">
         <x:v>101</x:v>
@@ -55156,11 +55162,11 @@
       <x:c r="AZ213" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="BA213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB213" t="s">
-        <x:v>1</x:v>
+      <x:c r="BA213" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BB213" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BC213" s="6" t="s">
         <x:v>101</x:v>
@@ -55180,8 +55186,8 @@
       <x:c r="BH213" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="BI213" t="s">
-        <x:v>1</x:v>
+      <x:c r="BI213" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BJ213" s="6" t="s">
         <x:v>101</x:v>
@@ -55192,8 +55198,8 @@
       <x:c r="BL213" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="BM213" t="s">
-        <x:v>1</x:v>
+      <x:c r="BM213" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BN213" t="s">
         <x:v>1</x:v>
@@ -55201,11 +55207,11 @@
       <x:c r="BO213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BP213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ213" t="s">
-        <x:v>1</x:v>
+      <x:c r="BP213" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BQ213" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BR213" t="s">
         <x:v>1</x:v>
@@ -55219,11 +55225,11 @@
       <x:c r="BU213" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="BV213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW213" t="s">
-        <x:v>1</x:v>
+      <x:c r="BV213" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BW213" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BX213" t="s">
         <x:v>1</x:v>
@@ -55240,8 +55246,8 @@
       <x:c r="CB213" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="CC213" t="s">
-        <x:v>1</x:v>
+      <x:c r="CC213" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="CD213" s="6" t="s">
         <x:v>101</x:v>
@@ -55261,8 +55267,8 @@
       <x:c r="CI213" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="CJ213" t="s">
-        <x:v>1</x:v>
+      <x:c r="CJ213" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="CK213" s="6" t="s">
         <x:v>101</x:v>
@@ -55275,8 +55281,8 @@
       <x:c r="B214" s="5" t="s">
         <x:v>432</x:v>
       </x:c>
-      <x:c r="C214" t="s">
-        <x:v>1</x:v>
+      <x:c r="C214" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D214" t="s">
         <x:v>1</x:v>
@@ -55299,11 +55305,11 @@
       <x:c r="J214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L214" t="s">
-        <x:v>1</x:v>
+      <x:c r="K214" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="L214" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="M214" s="6" t="s">
         <x:v>101</x:v>
@@ -55314,35 +55320,35 @@
       <x:c r="O214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y214" t="s">
-        <x:v>1</x:v>
+      <x:c r="P214" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="Q214" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="R214" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="S214" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="T214" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="U214" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="V214" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="W214" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="X214" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="Y214" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="Z214" s="6" t="s">
         <x:v>101</x:v>
@@ -55377,8 +55383,8 @@
       <x:c r="AJ214" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="AK214" t="s">
-        <x:v>1</x:v>
+      <x:c r="AK214" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="AL214" s="6" t="s">
         <x:v>101</x:v>
@@ -55398,8 +55404,8 @@
       <x:c r="AQ214" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="AR214" t="s">
-        <x:v>1</x:v>
+      <x:c r="AR214" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="AS214" s="6" t="s">
         <x:v>101</x:v>
@@ -55413,8 +55419,8 @@
       <x:c r="AV214" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="AW214" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="AW214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AX214" s="6" t="s">
         <x:v>101</x:v>
@@ -55425,11 +55431,11 @@
       <x:c r="AZ214" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="BA214" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BB214" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BA214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BC214" s="6" t="s">
         <x:v>101</x:v>
@@ -55449,8 +55455,8 @@
       <x:c r="BH214" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="BI214" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BI214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BJ214" s="6" t="s">
         <x:v>101</x:v>
@@ -55461,8 +55467,8 @@
       <x:c r="BL214" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="BM214" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BM214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BN214" t="s">
         <x:v>1</x:v>
@@ -55503,14 +55509,14 @@
       <x:c r="BZ214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CA214" t="s">
-        <x:v>1</x:v>
+      <x:c r="CA214" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="CB214" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="CC214" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="CC214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CD214" s="6" t="s">
         <x:v>101</x:v>
@@ -55524,14 +55530,14 @@
       <x:c r="CG214" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="CH214" t="s">
-        <x:v>1</x:v>
+      <x:c r="CH214" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="CI214" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="CJ214" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="CJ214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CK214" s="6" t="s">
         <x:v>101</x:v>
@@ -55574,11 +55580,11 @@
       <x:c r="L215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N215" t="s">
-        <x:v>1</x:v>
+      <x:c r="M215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="N215" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="O215" t="s">
         <x:v>1</x:v>
@@ -55613,59 +55619,59 @@
       <x:c r="Y215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ215" t="s">
-        <x:v>1</x:v>
+      <x:c r="Z215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AA215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AB215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AC215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AD215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AE215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AF215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AG215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AH215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AI215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AJ215" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="AK215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AL215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ215" t="s">
-        <x:v>1</x:v>
+      <x:c r="AL215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AM215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AN215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AO215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AP215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AQ215" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="AR215" t="s">
         <x:v>1</x:v>
@@ -55673,44 +55679,44 @@
       <x:c r="AS215" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="AT215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF215" t="s">
-        <x:v>1</x:v>
+      <x:c r="AT215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AU215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AV215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AW215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AX215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AY215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AZ215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BA215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BB215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BC215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BD215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BE215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BF215" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BG215" s="6" t="s">
         <x:v>101</x:v>
@@ -55718,20 +55724,20 @@
       <x:c r="BH215" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="BI215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM215" t="s">
-        <x:v>1</x:v>
+      <x:c r="BI215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BJ215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BK215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BL215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BM215" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BN215" t="s">
         <x:v>1</x:v>
@@ -55739,11 +55745,11 @@
       <x:c r="BO215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BP215" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BQ215" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BP215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BR215" t="s">
         <x:v>1</x:v>
@@ -55751,11 +55757,11 @@
       <x:c r="BS215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BT215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU215" t="s">
-        <x:v>1</x:v>
+      <x:c r="BT215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BU215" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BV215" t="s">
         <x:v>1</x:v>
@@ -55775,35 +55781,35 @@
       <x:c r="CA215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CB215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CG215" t="s">
-        <x:v>1</x:v>
+      <x:c r="CB215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CC215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CD215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CE215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CF215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CG215" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="CH215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CI215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CJ215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CK215" t="s">
-        <x:v>1</x:v>
+      <x:c r="CI215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CJ215" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CK215" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -55843,17 +55849,17 @@
       <x:c r="L216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="N216" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="M216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P216" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="P216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q216" t="s">
         <x:v>1</x:v>
@@ -55882,38 +55888,38 @@
       <x:c r="Y216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AA216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AB216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AC216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AD216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AE216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AF216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AG216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AH216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AI216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AJ216" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="Z216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AK216" t="s">
         <x:v>1</x:v>
@@ -55927,11 +55933,11 @@
       <x:c r="AN216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AP216" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="AO216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AQ216" t="s">
         <x:v>1</x:v>
@@ -55942,41 +55948,41 @@
       <x:c r="AS216" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="AT216" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="AT216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AU216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AV216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AW216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AX216" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="AV216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AY216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ216" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="AZ216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BA216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BC216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BD216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BE216" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BB216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BF216" t="s">
         <x:v>1</x:v>
@@ -55987,26 +55993,26 @@
       <x:c r="BH216" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="BI216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BJ216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BK216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BL216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BM216" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BI216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BN216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BO216" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BO216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BP216" s="6" t="s">
         <x:v>101</x:v>
@@ -56014,20 +56020,20 @@
       <x:c r="BQ216" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="BR216" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BR216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BS216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BT216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BU216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BV216" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BT216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BW216" t="s">
         <x:v>1</x:v>
@@ -56035,32 +56041,32 @@
       <x:c r="BX216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BY216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BZ216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="CA216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="CB216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="CC216" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BY216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CD216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CE216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="CF216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="CG216" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="CE216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CH216" t="s">
         <x:v>1</x:v>
@@ -56068,11 +56074,11 @@
       <x:c r="CI216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CJ216" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="CK216" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="CJ216" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CK216" t="s">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
@@ -56085,104 +56091,104 @@
       <x:c r="C217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D217" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="E217" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="F217" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="G217" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H217" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="I217" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="D217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K217" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="L217" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="M217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O217" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="P217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q217" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="R217" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="S217" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="T217" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="U217" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="V217" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="W217" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="X217" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="Y217" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="Z217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ217" t="s">
-        <x:v>1</x:v>
+      <x:c r="K217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="N217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="O217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="Q217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AA217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AB217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AC217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AD217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AE217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AF217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AG217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AH217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AI217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AJ217" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="AK217" t="s">
         <x:v>1</x:v>
@@ -56196,11 +56202,11 @@
       <x:c r="AN217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP217" t="s">
-        <x:v>1</x:v>
+      <x:c r="AO217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AP217" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="AQ217" t="s">
         <x:v>1</x:v>
@@ -56208,128 +56214,128 @@
       <x:c r="AR217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AS217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT217" t="s">
-        <x:v>1</x:v>
+      <x:c r="AS217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AT217" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="AU217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AV217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX217" t="s">
-        <x:v>1</x:v>
+      <x:c r="AV217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AW217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AX217" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="AY217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ217" t="s">
-        <x:v>1</x:v>
+      <x:c r="AZ217" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BA217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE217" t="s">
-        <x:v>1</x:v>
+      <x:c r="BB217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BC217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BD217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BE217" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BF217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BG217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM217" t="s">
-        <x:v>1</x:v>
+      <x:c r="BG217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BH217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BI217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BJ217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BK217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BL217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BM217" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BN217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BO217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR217" t="s">
-        <x:v>1</x:v>
+      <x:c r="BO217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BP217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BQ217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BR217" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BS217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BT217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV217" t="s">
-        <x:v>1</x:v>
+      <x:c r="BT217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BU217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BV217" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BW217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BX217" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BY217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC217" t="s">
-        <x:v>1</x:v>
+      <x:c r="BX217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BZ217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CA217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CB217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CC217" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="CD217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CE217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CG217" t="s">
-        <x:v>1</x:v>
+      <x:c r="CE217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CF217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CG217" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="CH217" t="s">
         <x:v>1</x:v>
@@ -56337,11 +56343,11 @@
       <x:c r="CI217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CJ217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CK217" t="s">
-        <x:v>1</x:v>
+      <x:c r="CJ217" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CK217" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -56354,23 +56360,23 @@
       <x:c r="C218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I218" t="s">
-        <x:v>1</x:v>
+      <x:c r="D218" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="E218" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F218" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G218" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H218" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="I218" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="J218" t="s">
         <x:v>1</x:v>
@@ -56381,125 +56387,125 @@
       <x:c r="L218" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="M218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="N218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="O218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="Q218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AA218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AB218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AC218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AD218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AE218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AF218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AG218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AH218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AI218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AJ218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AK218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AL218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AM218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AN218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AO218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AP218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AQ218" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="M218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O218" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="P218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q218" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="R218" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="S218" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="T218" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="U218" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="V218" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="W218" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="X218" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="Y218" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="Z218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AR218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AS218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AT218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AU218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AV218" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="AS218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AW218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AY218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AZ218" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="AX218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BA218" t="s">
         <x:v>1</x:v>
@@ -56507,35 +56513,35 @@
       <x:c r="BB218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BD218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BE218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BF218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BG218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BH218" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BC218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BI218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BJ218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BK218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BL218" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BJ218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BM218" t="s">
         <x:v>1</x:v>
@@ -56558,11 +56564,11 @@
       <x:c r="BS218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BT218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BU218" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BT218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BV218" t="s">
         <x:v>1</x:v>
@@ -56570,8 +56576,8 @@
       <x:c r="BW218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BX218" t="s">
-        <x:v>1</x:v>
+      <x:c r="BX218" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BY218" t="s">
         <x:v>1</x:v>
@@ -56582,309 +56588,309 @@
       <x:c r="CA218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CB218" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="CB218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CC218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CD218" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="CD218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CE218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CF218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="CG218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="CH218" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="CI218" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="CF218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CH218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CI218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CJ218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CK218" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="CK218" t="s">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
-      <x:c r="A219" s="3" t="s">
+      <x:c r="A219" s="4" t="s">
         <x:v>441</x:v>
       </x:c>
-      <x:c r="CK219" t="s">
-        <x:v>1</x:v>
+      <x:c r="B219" s="5" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="C219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="L219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="M219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="N219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="O219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="Q219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AA219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AB219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AC219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AD219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AE219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AF219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AG219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AH219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AI219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AJ219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AK219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AL219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AM219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AN219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AO219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AP219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AQ219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AR219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AT219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AU219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AV219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AW219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AY219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AZ219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BA219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BD219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BE219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BF219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BG219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BH219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BI219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BK219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BL219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BM219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BU219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BV219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CC219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CE219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CG219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CH219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CI219" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CJ219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CK219" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
-      <x:c r="A220" s="4" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="B220" s="5" t="s">
+      <x:c r="A220" s="3" t="s">
         <x:v>443</x:v>
-      </x:c>
-      <x:c r="C220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU220" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AV220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CG220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CH220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CI220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CJ220" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="CK220" t="s">
         <x:v>1</x:v>
@@ -57029,8 +57035,8 @@
       <x:c r="AT221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AU221" t="s">
-        <x:v>1</x:v>
+      <x:c r="AU221" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="AV221" t="s">
         <x:v>1</x:v>
@@ -57202,8 +57208,8 @@
       <x:c r="N222" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O222" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="O222" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="P222" t="s">
         <x:v>1</x:v>
@@ -57433,7 +57439,7 @@
         <x:v>448</x:v>
       </x:c>
       <x:c r="B223" s="5" t="s">
-        <x:v>114</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="C223" t="s">
         <x:v>1</x:v>
@@ -57471,8 +57477,8 @@
       <x:c r="N223" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O223" t="s">
-        <x:v>1</x:v>
+      <x:c r="O223" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="P223" t="s">
         <x:v>1</x:v>
@@ -57627,8 +57633,8 @@
       <x:c r="BN223" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BO223" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BO223" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BP223" t="s">
         <x:v>1</x:v>
@@ -57699,10 +57705,10 @@
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="4" t="s">
-        <x:v>449</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B224" s="5" t="s">
-        <x:v>450</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C224" t="s">
         <x:v>1</x:v>
@@ -57851,8 +57857,8 @@
       <x:c r="AY224" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ224" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="AZ224" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BA224" t="s">
         <x:v>1</x:v>
@@ -57896,8 +57902,8 @@
       <x:c r="BN224" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BO224" t="s">
-        <x:v>1</x:v>
+      <x:c r="BO224" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BP224" t="s">
         <x:v>1</x:v>
@@ -57932,8 +57938,8 @@
       <x:c r="BZ224" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CA224" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="CA224" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CB224" t="s">
         <x:v>1</x:v>
@@ -58506,13 +58512,13 @@
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B227" s="5" t="s">
-        <x:v>455</x:v>
-      </x:c>
-      <x:c r="C227" s="6" t="s">
-        <x:v>101</x:v>
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="C227" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D227" t="s">
         <x:v>1</x:v>
@@ -58553,11 +58559,11 @@
       <x:c r="P227" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q227" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="R227" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="Q227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R227" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="S227" t="s">
         <x:v>1</x:v>
@@ -58577,11 +58583,11 @@
       <x:c r="X227" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Y227" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="Z227" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="Y227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z227" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AA227" t="s">
         <x:v>1</x:v>
@@ -58598,20 +58604,20 @@
       <x:c r="AE227" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AF227" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AG227" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AH227" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AI227" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AJ227" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="AF227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ227" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AK227" t="s">
         <x:v>1</x:v>
@@ -58658,8 +58664,8 @@
       <x:c r="AY227" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AZ227" t="s">
-        <x:v>1</x:v>
+      <x:c r="AZ227" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BA227" t="s">
         <x:v>1</x:v>
@@ -58679,11 +58685,11 @@
       <x:c r="BF227" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BG227" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="BH227" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BG227" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH227" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BI227" t="s">
         <x:v>1</x:v>
@@ -58739,8 +58745,8 @@
       <x:c r="BZ227" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CA227" t="s">
-        <x:v>1</x:v>
+      <x:c r="CA227" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="CB227" t="s">
         <x:v>1</x:v>
@@ -58778,10 +58784,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B228" s="5" t="s">
-        <x:v>456</x:v>
-      </x:c>
-      <x:c r="C228" t="s">
-        <x:v>1</x:v>
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="C228" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D228" t="s">
         <x:v>1</x:v>
@@ -58822,11 +58828,11 @@
       <x:c r="P228" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q228" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R228" t="s">
-        <x:v>1</x:v>
+      <x:c r="Q228" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="R228" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="S228" t="s">
         <x:v>1</x:v>
@@ -58846,11 +58852,11 @@
       <x:c r="X228" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Y228" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z228" t="s">
-        <x:v>1</x:v>
+      <x:c r="Y228" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="Z228" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="AA228" t="s">
         <x:v>1</x:v>
@@ -58867,20 +58873,20 @@
       <x:c r="AE228" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AF228" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG228" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH228" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI228" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ228" t="s">
-        <x:v>1</x:v>
+      <x:c r="AF228" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AG228" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AH228" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AI228" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AJ228" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="AK228" t="s">
         <x:v>1</x:v>
@@ -58930,8 +58936,8 @@
       <x:c r="AZ228" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BA228" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="BA228" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BB228" t="s">
         <x:v>1</x:v>
@@ -58948,11 +58954,11 @@
       <x:c r="BF228" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BG228" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH228" t="s">
-        <x:v>1</x:v>
+      <x:c r="BG228" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BH228" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BI228" t="s">
         <x:v>1</x:v>
@@ -59043,271 +59049,540 @@
       </x:c>
     </x:row>
     <x:row r="229">
-      <x:c r="A229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CG229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CH229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CI229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CJ229" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CK229" s="7" t="s">
+      <x:c r="A229" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B229" s="5" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="C229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA229" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BB229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CH229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CI229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CJ229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CK229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CH230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CI230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CJ230" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CK230" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -59359,7 +59634,7 @@
     <x:mergeCell ref="A186:CK186"/>
     <x:mergeCell ref="A193:CK193"/>
     <x:mergeCell ref="A204:CK204"/>
-    <x:mergeCell ref="A219:CK219"/>
+    <x:mergeCell ref="A220:CK220"/>
   </x:mergeCells>
 </x:worksheet>
 </file>
--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Ra69d7ef0471c436f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R05e2d5b06e1042fc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -47615,11 +47615,11 @@
       <x:c r="BA182" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB182" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC182" t="s">
-        <x:v>1</x:v>
+      <x:c r="BB182" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BC182" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BD182" s="6" t="s">
         <x:v>101</x:v>
@@ -47636,11 +47636,11 @@
       <x:c r="BH182" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="BI182" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ182" t="s">
-        <x:v>1</x:v>
+      <x:c r="BI182" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BJ182" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BK182" t="s">
         <x:v>1</x:v>
@@ -47717,11 +47717,11 @@
       <x:c r="CI182" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CJ182" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CK182" t="s">
-        <x:v>1</x:v>
+      <x:c r="CJ182" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CK182" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="183">

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R05e2d5b06e1042fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R30364a5351814b4d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.7.35 </x:t>
+ 2026.7.40 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R30364a5351814b4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R785ce283f1434f37"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +23,7 @@
   </x:si>
   <x:si>
     <x:t>.NET
- 9.0.17 </x:t>
+ 9.0.18 </x:t>
   </x:si>
   <x:si>
     <x:t>wregex
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.7.40 </x:t>
+ 2026.7.46 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R785ce283f1434f37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R16382bb51d83476f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.7.46 </x:t>
+ 2026.7.50 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R16382bb51d83476f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R39961fa6fd3041c9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.7.50 </x:t>
+ 2026.7.51 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>
@@ -6655,11 +6655,11 @@
       <x:c r="BA21" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC21" t="s">
-        <x:v>1</x:v>
+      <x:c r="BB21" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BC21" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BD21" s="6" t="s">
         <x:v>101</x:v>
@@ -6676,11 +6676,11 @@
       <x:c r="BH21" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BI21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ21" t="s">
-        <x:v>1</x:v>
+      <x:c r="BI21" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BJ21" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BK21" t="s">
         <x:v>1</x:v>
@@ -6757,11 +6757,11 @@
       <x:c r="CI21" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CJ21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CK21" t="s">
-        <x:v>1</x:v>
+      <x:c r="CJ21" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CK21" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -13665,11 +13665,11 @@
       <x:c r="BA49" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB49" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC49" t="s">
-        <x:v>1</x:v>
+      <x:c r="BB49" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BC49" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BD49" s="6" t="s">
         <x:v>101</x:v>
@@ -13686,11 +13686,11 @@
       <x:c r="BH49" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BI49" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ49" t="s">
-        <x:v>1</x:v>
+      <x:c r="BI49" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BJ49" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BK49" t="s">
         <x:v>1</x:v>
@@ -13767,11 +13767,11 @@
       <x:c r="CI49" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CJ49" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CK49" t="s">
-        <x:v>1</x:v>
+      <x:c r="CJ49" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CK49" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -19860,11 +19860,11 @@
       <x:c r="BA73" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB73" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC73" t="s">
-        <x:v>1</x:v>
+      <x:c r="BB73" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BC73" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BD73" s="6" t="s">
         <x:v>101</x:v>
@@ -19881,11 +19881,11 @@
       <x:c r="BH73" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BI73" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ73" t="s">
-        <x:v>1</x:v>
+      <x:c r="BI73" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BJ73" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BK73" t="s">
         <x:v>1</x:v>
@@ -19962,11 +19962,11 @@
       <x:c r="CI73" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CJ73" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CK73" t="s">
-        <x:v>1</x:v>
+      <x:c r="CJ73" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="CK73" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="74">

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R39961fa6fd3041c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R0439f05cf80a4dde"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -127,7 +127,7 @@
   </x:si>
   <x:si>
     <x:t>RE#
- 1.0.4 </x:t>
+ 1.0.5 </x:t>
   </x:si>
   <x:si>
     <x:t>Go
@@ -14547,8 +14547,8 @@
       <x:c r="BZ52" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CA52" t="s">
-        <x:v>1</x:v>
+      <x:c r="CA52" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="CB52" t="s">
         <x:v>1</x:v>
@@ -20742,8 +20742,8 @@
       <x:c r="BZ76" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CA76" t="s">
-        <x:v>1</x:v>
+      <x:c r="CA76" s="6" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="CB76" t="s">
         <x:v>1</x:v>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rcaa71ee6fd0f43af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R52d470949f984aab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -131,7 +131,7 @@
   </x:si>
   <x:si>
     <x:t>Go
- 1.26.4 </x:t>
+ 1.26.5 </x:t>
   </x:si>
   <x:si>
     <x:t>Dart

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R8c31f20cb5fc4f5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R5ee06e1429c34c08"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.7.51 </x:t>
+ 2026.7.55 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R5ee06e1429c34c08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R36fdc568f99a4273"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +23,7 @@
   </x:si>
   <x:si>
     <x:t>.NET
- 9.0.18 </x:t>
+ 10.0.10 </x:t>
   </x:si>
   <x:si>
     <x:t>wregex
@@ -1557,7 +1557,7 @@
   <x:cols>
     <x:col min="1" max="1" width="20" customWidth="1"/>
     <x:col min="2" max="2" width="45" customWidth="1"/>
-    <x:col min="3" max="3" width="8" customWidth="1"/>
+    <x:col min="3" max="3" width="9" customWidth="1"/>
     <x:col min="4" max="4" width="11.789" customWidth="1"/>
     <x:col min="5" max="5" width="6.198" customWidth="1"/>
     <x:col min="6" max="6" width="9.4" customWidth="1"/>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R7ae56ec95e10415b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R0aaa27c948b64736"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.7.62 </x:t>
+ 2026.7.63 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>
@@ -1354,16 +1354,28 @@
     <x:t>Support Unicode characters inside sets</x:t>
   </x:si>
   <x:si>
+    <x:t>Surrogates</x:t>
+  </x:si>
+  <x:si>
+    <x:t>“.” matches surrogate pairs as one entity (no split)</x:t>
+  </x:si>
+  <x:si>
     <x:t>é=É</x:t>
   </x:si>
   <x:si>
     <x:t>Support Unicode case folding</x:t>
   </x:si>
   <x:si>
-    <x:t>Surrogates</x:t>
+    <x:t>Σσς</x:t>
   </x:si>
   <x:si>
-    <x:t>“.” matches surrogate pairs as one entity (no split)</x:t>
+    <x:t>Match letters that have multiple uppercase and lowercase variants</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ß=SS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Match “ß ↔ ss” and “ß ↔ SS” in case-insensitive mode</x:t>
   </x:si>
   <x:si>
     <x:t>Fuzzy matching</x:t>
@@ -1382,12 +1394,6 @@
   </x:si>
   <x:si>
     <x:t>Give error on possible ReDoS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Σσς</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Match letters that have multiple uppercase and lowercase variants</x:t>
   </x:si>
   <x:si>
     <x:t>Specific extensions</x:t>
@@ -57975,8 +57981,8 @@
       <x:c r="B215" s="5" t="s">
         <x:v>439</x:v>
       </x:c>
-      <x:c r="C215" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="C215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D215" t="s">
         <x:v>1</x:v>
@@ -57999,14 +58005,14 @@
       <x:c r="J215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K215" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="L215" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="M215" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="K215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N215" s="6" t="s">
         <x:v>106</x:v>
@@ -58017,35 +58023,35 @@
       <x:c r="P215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q215" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="R215" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="S215" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="T215" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="U215" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="V215" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="W215" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="X215" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="Y215" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="Z215" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="Q215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AA215" s="6" t="s">
         <x:v>106</x:v>
@@ -58080,8 +58086,8 @@
       <x:c r="AK215" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="AL215" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="AL215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AM215" s="6" t="s">
         <x:v>106</x:v>
@@ -58101,8 +58107,8 @@
       <x:c r="AR215" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="AS215" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="AS215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AT215" s="6" t="s">
         <x:v>106</x:v>
@@ -58116,8 +58122,8 @@
       <x:c r="AW215" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="AX215" t="s">
-        <x:v>1</x:v>
+      <x:c r="AX215" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AY215" s="6" t="s">
         <x:v>106</x:v>
@@ -58128,8 +58134,8 @@
       <x:c r="BA215" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="BB215" t="s">
-        <x:v>1</x:v>
+      <x:c r="BB215" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BC215" s="6" t="s">
         <x:v>106</x:v>
@@ -58146,8 +58152,8 @@
       <x:c r="BG215" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="BH215" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="BH215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BI215" s="6" t="s">
         <x:v>106</x:v>
@@ -58158,8 +58164,8 @@
       <x:c r="BK215" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="BL215" t="s">
-        <x:v>1</x:v>
+      <x:c r="BL215" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BM215" s="6" t="s">
         <x:v>106</x:v>
@@ -58170,8 +58176,8 @@
       <x:c r="BO215" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="BP215" t="s">
-        <x:v>1</x:v>
+      <x:c r="BP215" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BQ215" t="s">
         <x:v>1</x:v>
@@ -58212,14 +58218,14 @@
       <x:c r="CC215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CD215" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="CD215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CE215" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="CF215" t="s">
-        <x:v>1</x:v>
+      <x:c r="CF215" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="CG215" s="6" t="s">
         <x:v>106</x:v>
@@ -58233,8 +58239,8 @@
       <x:c r="CJ215" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="CK215" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="CK215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CL215" s="6" t="s">
         <x:v>106</x:v>
@@ -58242,8 +58248,8 @@
       <x:c r="CM215" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="CN215" t="s">
-        <x:v>1</x:v>
+      <x:c r="CN215" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="CO215" s="6" t="s">
         <x:v>106</x:v>
@@ -58256,8 +58262,8 @@
       <x:c r="B216" s="5" t="s">
         <x:v>441</x:v>
       </x:c>
-      <x:c r="C216" t="s">
-        <x:v>1</x:v>
+      <x:c r="C216" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D216" t="s">
         <x:v>1</x:v>
@@ -58280,14 +58286,14 @@
       <x:c r="J216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M216" t="s">
-        <x:v>1</x:v>
+      <x:c r="K216" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="L216" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="M216" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="N216" s="6" t="s">
         <x:v>106</x:v>
@@ -58298,35 +58304,35 @@
       <x:c r="P216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y216" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z216" t="s">
-        <x:v>1</x:v>
+      <x:c r="Q216" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="R216" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="S216" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="T216" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="U216" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="V216" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="W216" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="X216" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="Y216" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="Z216" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AA216" s="6" t="s">
         <x:v>106</x:v>
@@ -58361,8 +58367,8 @@
       <x:c r="AK216" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="AL216" t="s">
-        <x:v>1</x:v>
+      <x:c r="AL216" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AM216" s="6" t="s">
         <x:v>106</x:v>
@@ -58382,8 +58388,8 @@
       <x:c r="AR216" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="AS216" t="s">
-        <x:v>1</x:v>
+      <x:c r="AS216" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AT216" s="6" t="s">
         <x:v>106</x:v>
@@ -58397,8 +58403,8 @@
       <x:c r="AW216" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="AX216" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="AX216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AY216" s="6" t="s">
         <x:v>106</x:v>
@@ -58409,8 +58415,8 @@
       <x:c r="BA216" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="BB216" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="BB216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BC216" s="6" t="s">
         <x:v>106</x:v>
@@ -58427,8 +58433,8 @@
       <x:c r="BG216" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="BH216" t="s">
-        <x:v>1</x:v>
+      <x:c r="BH216" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BI216" s="6" t="s">
         <x:v>106</x:v>
@@ -58439,8 +58445,8 @@
       <x:c r="BK216" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="BL216" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="BL216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BM216" s="6" t="s">
         <x:v>106</x:v>
@@ -58451,8 +58457,8 @@
       <x:c r="BO216" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="BP216" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="BP216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BQ216" t="s">
         <x:v>1</x:v>
@@ -58493,14 +58499,14 @@
       <x:c r="CC216" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CD216" t="s">
-        <x:v>1</x:v>
+      <x:c r="CD216" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="CE216" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="CF216" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="CF216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CG216" s="6" t="s">
         <x:v>106</x:v>
@@ -58514,8 +58520,8 @@
       <x:c r="CJ216" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="CK216" t="s">
-        <x:v>1</x:v>
+      <x:c r="CK216" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="CL216" s="6" t="s">
         <x:v>106</x:v>
@@ -58523,8 +58529,8 @@
       <x:c r="CM216" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="CN216" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="CN216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CO216" s="6" t="s">
         <x:v>106</x:v>
@@ -58561,26 +58567,26 @@
       <x:c r="J217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O217" t="s">
-        <x:v>1</x:v>
+      <x:c r="K217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="L217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="M217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="N217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="O217" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="P217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q217" t="s">
-        <x:v>1</x:v>
+      <x:c r="Q217" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="R217" t="s">
         <x:v>1</x:v>
@@ -58609,59 +58615,59 @@
       <x:c r="Z217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AA217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR217" t="s">
-        <x:v>1</x:v>
+      <x:c r="AA217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AB217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AC217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AD217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AE217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AF217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AG217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AH217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AI217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AJ217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AK217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AL217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AM217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AN217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AO217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AP217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AQ217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AR217" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AS217" t="s">
         <x:v>1</x:v>
@@ -58669,50 +58675,50 @@
       <x:c r="AT217" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="AU217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW217" t="s">
-        <x:v>1</x:v>
+      <x:c r="AU217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AV217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AW217" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AX217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AY217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA217" t="s">
-        <x:v>1</x:v>
+      <x:c r="AY217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AZ217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="BA217" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BB217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG217" t="s">
-        <x:v>1</x:v>
+      <x:c r="BC217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="BD217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="BE217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="BF217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="BG217" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BH217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BI217" t="s">
-        <x:v>1</x:v>
+      <x:c r="BI217" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BJ217" s="6" t="s">
         <x:v>106</x:v>
@@ -58723,14 +58729,14 @@
       <x:c r="BL217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BM217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO217" t="s">
-        <x:v>1</x:v>
+      <x:c r="BM217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="BN217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="BO217" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BP217" t="s">
         <x:v>1</x:v>
@@ -58741,11 +58747,11 @@
       <x:c r="BR217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BS217" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="BT217" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="BS217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BU217" t="s">
         <x:v>1</x:v>
@@ -58753,11 +58759,11 @@
       <x:c r="BV217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BW217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX217" t="s">
-        <x:v>1</x:v>
+      <x:c r="BW217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="BX217" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BY217" t="s">
         <x:v>1</x:v>
@@ -58777,38 +58783,38 @@
       <x:c r="CD217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CE217" t="s">
-        <x:v>1</x:v>
+      <x:c r="CE217" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="CF217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CG217" t="s">
-        <x:v>1</x:v>
+      <x:c r="CG217" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="CH217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CI217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CJ217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CK217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CL217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CM217" t="s">
-        <x:v>1</x:v>
+      <x:c r="CI217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="CJ217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="CK217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="CL217" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="CM217" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="CN217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO217" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO217" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -58848,20 +58854,20 @@
       <x:c r="L218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="N218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="O218" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="M218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="P218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q218" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="Q218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R218" t="s">
         <x:v>1</x:v>
@@ -58935,11 +58941,11 @@
       <x:c r="AO218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AP218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="AQ218" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="AP218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AR218" t="s">
         <x:v>1</x:v>
@@ -58947,50 +58953,50 @@
       <x:c r="AS218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AT218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="AU218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="AV218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="AX218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="AY218" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="AT218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV218" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AW218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AZ218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BA218" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="BA218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BB218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="BD218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="BE218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="BF218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="BG218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="BH218" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="BC218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BI218" t="s">
         <x:v>1</x:v>
@@ -59001,47 +59007,47 @@
       <x:c r="BK218" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="BL218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="BM218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="BN218" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="BL218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BO218" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="BP218" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="BP218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BQ218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BR218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="BS218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="BT218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="BU218" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="BR218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BV218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BW218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="BX218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="BY218" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="BW218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BZ218" t="s">
         <x:v>1</x:v>
@@ -59049,32 +59055,32 @@
       <x:c r="CA218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CB218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="CC218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="CD218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="CE218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="CF218" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="CB218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CG218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CH218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="CI218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="CJ218" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="CH218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CI218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CJ218" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CK218" t="s">
         <x:v>1</x:v>
@@ -59085,11 +59091,11 @@
       <x:c r="CM218" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="CN218" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="CO218" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="CN218" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CO218" t="s">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
@@ -59102,32 +59108,32 @@
       <x:c r="C219" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D219" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="E219" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="F219" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G219" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="H219" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="I219" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="D219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I219" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J219" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K219" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="L219" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="K219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L219" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M219" t="s">
         <x:v>1</x:v>
@@ -59138,38 +59144,38 @@
       <x:c r="O219" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P219" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="P219" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q219" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="R219" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="S219" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="T219" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="U219" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="V219" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="W219" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="X219" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="Y219" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="Z219" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="R219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z219" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AA219" t="s">
         <x:v>1</x:v>
@@ -59228,8 +59234,8 @@
       <x:c r="AS219" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AT219" t="s">
-        <x:v>1</x:v>
+      <x:c r="AT219" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AU219" t="s">
         <x:v>1</x:v>
@@ -59276,11 +59282,11 @@
       <x:c r="BI219" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BJ219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK219" t="s">
-        <x:v>1</x:v>
+      <x:c r="BJ219" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="BK219" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BL219" t="s">
         <x:v>1</x:v>
@@ -59303,11 +59309,11 @@
       <x:c r="BR219" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BS219" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT219" t="s">
-        <x:v>1</x:v>
+      <x:c r="BS219" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="BT219" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BU219" t="s">
         <x:v>1</x:v>
@@ -59327,8 +59333,8 @@
       <x:c r="BZ219" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CA219" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="CA219" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CB219" t="s">
         <x:v>1</x:v>
@@ -59404,11 +59410,11 @@
       <x:c r="J220" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K220" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="L220" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="K220" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L220" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M220" s="6" t="s">
         <x:v>106</x:v>
@@ -59485,17 +59491,17 @@
       <x:c r="AK220" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="AL220" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="AM220" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="AN220" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="AO220" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="AL220" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM220" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN220" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO220" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AP220" s="6" t="s">
         <x:v>106</x:v>
@@ -59503,8 +59509,8 @@
       <x:c r="AQ220" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="AR220" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="AR220" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AS220" t="s">
         <x:v>1</x:v>
@@ -59515,20 +59521,20 @@
       <x:c r="AU220" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="AV220" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="AV220" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AW220" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="AX220" t="s">
-        <x:v>1</x:v>
+      <x:c r="AX220" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AY220" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="AZ220" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="AZ220" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BA220" s="6" t="s">
         <x:v>106</x:v>
@@ -59551,11 +59557,11 @@
       <x:c r="BG220" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="BH220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI220" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="BH220" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="BI220" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BJ220" s="6" t="s">
         <x:v>106</x:v>
@@ -59563,8 +59569,8 @@
       <x:c r="BK220" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="BL220" t="s">
-        <x:v>1</x:v>
+      <x:c r="BL220" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BM220" s="6" t="s">
         <x:v>106</x:v>
@@ -59575,23 +59581,23 @@
       <x:c r="BO220" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="BP220" t="s">
-        <x:v>1</x:v>
+      <x:c r="BP220" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BQ220" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BR220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU220" t="s">
-        <x:v>1</x:v>
+      <x:c r="BR220" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="BS220" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="BT220" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="BU220" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BV220" t="s">
         <x:v>1</x:v>
@@ -59602,8 +59608,8 @@
       <x:c r="BX220" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="BY220" t="s">
-        <x:v>1</x:v>
+      <x:c r="BY220" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BZ220" t="s">
         <x:v>1</x:v>
@@ -59611,26 +59617,26 @@
       <x:c r="CA220" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CB220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD220" t="s">
-        <x:v>1</x:v>
+      <x:c r="CB220" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="CC220" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="CD220" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="CE220" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="CF220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CG220" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="CH220" t="s">
-        <x:v>1</x:v>
+      <x:c r="CF220" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="CG220" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CH220" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="CI220" s="6" t="s">
         <x:v>106</x:v>
@@ -59638,306 +59644,306 @@
       <x:c r="CJ220" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="CK220" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="CL220" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="CK220" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CL220" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CM220" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="CN220" t="s">
-        <x:v>1</x:v>
+      <x:c r="CN220" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="CO220" s="6" t="s">
         <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="221">
-      <x:c r="A221" s="3" t="s">
+      <x:c r="A221" s="4" t="s">
         <x:v>450</x:v>
+      </x:c>
+      <x:c r="B221" s="5" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="C221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="E221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="I221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="J221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="L221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="M221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="Q221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="S221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="T221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="U221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="V221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="W221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="X221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="Y221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="Z221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AA221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA221" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="CB221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CH221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CI221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CJ221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CK221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CL221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CM221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CN221" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CO221" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
-      <x:c r="A222" s="4" t="s">
-        <x:v>451</x:v>
-      </x:c>
-      <x:c r="B222" s="5" t="s">
+      <x:c r="A222" s="3" t="s">
         <x:v>452</x:v>
-      </x:c>
-      <x:c r="C222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV222" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="AW222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CG222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CH222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CI222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CJ222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CK222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CL222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CM222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CN222" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="CO222" t="s">
         <x:v>1</x:v>
@@ -60085,8 +60091,8 @@
       <x:c r="AU223" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AV223" t="s">
-        <x:v>1</x:v>
+      <x:c r="AV223" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AW223" t="s">
         <x:v>1</x:v>
@@ -60270,8 +60276,8 @@
       <x:c r="O224" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P224" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="P224" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q224" t="s">
         <x:v>1</x:v>
@@ -60510,7 +60516,7 @@
         <x:v>457</x:v>
       </x:c>
       <x:c r="B225" s="5" t="s">
-        <x:v>119</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="C225" t="s">
         <x:v>1</x:v>
@@ -60551,8 +60557,8 @@
       <x:c r="O225" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P225" t="s">
-        <x:v>1</x:v>
+      <x:c r="P225" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="Q225" t="s">
         <x:v>1</x:v>
@@ -60713,8 +60719,8 @@
       <x:c r="BQ225" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BR225" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="BR225" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BS225" t="s">
         <x:v>1</x:v>
@@ -60788,10 +60794,10 @@
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="4" t="s">
-        <x:v>458</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B226" s="5" t="s">
-        <x:v>459</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C226" t="s">
         <x:v>1</x:v>
@@ -60943,8 +60949,8 @@
       <x:c r="AZ226" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BA226" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="BA226" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BB226" t="s">
         <x:v>1</x:v>
@@ -60994,8 +61000,8 @@
       <x:c r="BQ226" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BR226" t="s">
-        <x:v>1</x:v>
+      <x:c r="BR226" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BS226" t="s">
         <x:v>1</x:v>
@@ -61030,8 +61036,8 @@
       <x:c r="CC226" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CD226" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="CD226" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CE226" t="s">
         <x:v>1</x:v>
@@ -61631,13 +61637,13 @@
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B229" s="5" t="s">
-        <x:v>464</x:v>
-      </x:c>
-      <x:c r="C229" s="6" t="s">
-        <x:v>106</x:v>
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="C229" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D229" t="s">
         <x:v>1</x:v>
@@ -61681,11 +61687,11 @@
       <x:c r="Q229" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="R229" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="S229" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="R229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S229" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T229" t="s">
         <x:v>1</x:v>
@@ -61705,11 +61711,11 @@
       <x:c r="Y229" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z229" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="AA229" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="Z229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA229" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AB229" t="s">
         <x:v>1</x:v>
@@ -61726,20 +61732,20 @@
       <x:c r="AF229" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AG229" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="AH229" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="AI229" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="AJ229" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="AK229" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="AG229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK229" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL229" t="s">
         <x:v>1</x:v>
@@ -61786,8 +61792,8 @@
       <x:c r="AZ229" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BA229" t="s">
-        <x:v>1</x:v>
+      <x:c r="BA229" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BB229" t="s">
         <x:v>1</x:v>
@@ -61813,11 +61819,11 @@
       <x:c r="BI229" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BJ229" s="6" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="BK229" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="BJ229" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK229" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BL229" t="s">
         <x:v>1</x:v>
@@ -61873,8 +61879,8 @@
       <x:c r="CC229" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CD229" t="s">
-        <x:v>1</x:v>
+      <x:c r="CD229" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="CE229" t="s">
         <x:v>1</x:v>
@@ -61915,10 +61921,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B230" s="5" t="s">
-        <x:v>465</x:v>
-      </x:c>
-      <x:c r="C230" t="s">
-        <x:v>1</x:v>
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="C230" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D230" t="s">
         <x:v>1</x:v>
@@ -61962,11 +61968,11 @@
       <x:c r="Q230" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="R230" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S230" t="s">
-        <x:v>1</x:v>
+      <x:c r="R230" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="S230" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="T230" t="s">
         <x:v>1</x:v>
@@ -61986,11 +61992,11 @@
       <x:c r="Y230" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z230" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA230" t="s">
-        <x:v>1</x:v>
+      <x:c r="Z230" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AA230" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AB230" t="s">
         <x:v>1</x:v>
@@ -62007,20 +62013,20 @@
       <x:c r="AF230" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AG230" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH230" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI230" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ230" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK230" t="s">
-        <x:v>1</x:v>
+      <x:c r="AG230" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AH230" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AI230" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AJ230" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AK230" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AL230" t="s">
         <x:v>1</x:v>
@@ -62070,8 +62076,8 @@
       <x:c r="BA230" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB230" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="BB230" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BC230" t="s">
         <x:v>1</x:v>
@@ -62094,11 +62100,11 @@
       <x:c r="BI230" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BJ230" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK230" t="s">
-        <x:v>1</x:v>
+      <x:c r="BJ230" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="BK230" s="6" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BL230" t="s">
         <x:v>1</x:v>
@@ -62192,283 +62198,564 @@
       </x:c>
     </x:row>
     <x:row r="231">
-      <x:c r="A231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CG231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CH231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CI231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CJ231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CK231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CL231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CM231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CN231" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CO231" s="7" t="s">
+      <x:c r="A231" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B231" s="5" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="C231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB231" s="6" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="BC231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CH231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CI231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CJ231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CK231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CL231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CM231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CN231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CO231" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CH232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CI232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CJ232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CK232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CL232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CM232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CN232" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CO232" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -62520,7 +62807,7 @@
     <x:mergeCell ref="A187:CO187"/>
     <x:mergeCell ref="A194:CO194"/>
     <x:mergeCell ref="A205:CO205"/>
-    <x:mergeCell ref="A221:CO221"/>
+    <x:mergeCell ref="A222:CO222"/>
   </x:mergeCells>
 </x:worksheet>
 </file>
--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R0aaa27c948b64736"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rb7da85c239e2471c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.7.63 </x:t>
+ 2026.8.2 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rb7da85c239e2471c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rfeecdc97b9a34188"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -67,7 +67,7 @@
   </x:si>
   <x:si>
     <x:t>ICU
- 77.1 </x:t>
+ 78.3 </x:t>
   </x:si>
   <x:si>
     <x:t>Rust

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R515d815e187944dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R70f1fdd5a495426c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.8.8 </x:t>
+ 2026.8.9 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>
@@ -4416,8 +4416,8 @@
       <x:c r="BD12" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE12" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE12" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF12" s="6" t="s">
         <x:v>107</x:v>
@@ -6404,8 +6404,8 @@
       <x:c r="BD19" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE19" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE19" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF19" s="6" t="s">
         <x:v>107</x:v>
@@ -6972,8 +6972,8 @@
       <x:c r="BD21" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE21" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE21" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF21" s="6" t="s">
         <x:v>107</x:v>
@@ -7256,8 +7256,8 @@
       <x:c r="BD22" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE22" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE22" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF22" s="6" t="s">
         <x:v>107</x:v>
@@ -10680,8 +10680,8 @@
       <x:c r="BD36" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE36" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE36" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF36" s="6" t="s">
         <x:v>107</x:v>
@@ -11248,8 +11248,8 @@
       <x:c r="BD38" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE38" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE38" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF38" s="6" t="s">
         <x:v>107</x:v>
@@ -17220,8 +17220,8 @@
       <x:c r="BD60" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE60" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE60" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF60" s="6" t="s">
         <x:v>107</x:v>
@@ -17788,8 +17788,8 @@
       <x:c r="BD62" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE62" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE62" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF62" s="6" t="s">
         <x:v>107</x:v>
@@ -28020,8 +28020,8 @@
       <x:c r="BD99" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE99" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE99" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF99" s="6" t="s">
         <x:v>107</x:v>
@@ -58472,8 +58472,8 @@
       <x:c r="BD214" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE214" s="6" t="s">
-        <x:v>107</x:v>
+      <x:c r="BE214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BF214" s="6" t="s">
         <x:v>107</x:v>
@@ -59040,8 +59040,8 @@
       <x:c r="BD216" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE216" s="6" t="s">
-        <x:v>107</x:v>
+      <x:c r="BE216" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BF216" s="6" t="s">
         <x:v>107</x:v>
@@ -59324,8 +59324,8 @@
       <x:c r="BD217" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE217" s="6" t="s">
-        <x:v>107</x:v>
+      <x:c r="BE217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BF217" s="6" t="s">
         <x:v>107</x:v>
@@ -60744,8 +60744,8 @@
       <x:c r="BD222" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE222" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE222" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF222" s="6" t="s">
         <x:v>107</x:v>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R70f1fdd5a495426c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R1fb02e5d43dd48c4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7059,8 +7059,8 @@
       <x:c r="CG21" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CH21" t="s">
-        <x:v>1</x:v>
+      <x:c r="CH21" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="CI21" t="s">
         <x:v>1</x:v>
@@ -7343,8 +7343,8 @@
       <x:c r="CG22" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CH22" t="s">
-        <x:v>1</x:v>
+      <x:c r="CH22" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="CI22" t="s">
         <x:v>1</x:v>
@@ -10475,8 +10475,8 @@
       <x:c r="CG34" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CH34" t="s">
-        <x:v>1</x:v>
+      <x:c r="CH34" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="CI34" t="s">
         <x:v>1</x:v>
@@ -26403,8 +26403,8 @@
       <x:c r="CG93" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CH93" t="s">
-        <x:v>1</x:v>
+      <x:c r="CH93" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="CI93" t="s">
         <x:v>1</x:v>
@@ -28107,8 +28107,8 @@
       <x:c r="CG99" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CH99" t="s">
-        <x:v>1</x:v>
+      <x:c r="CH99" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="CI99" t="s">
         <x:v>1</x:v>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R1fb02e5d43dd48c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R658cbb8358d84bce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.8.9 </x:t>
+ 2026.8.11 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>
@@ -4700,8 +4700,8 @@
       <x:c r="BD13" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE13" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE13" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF13" t="s">
         <x:v>1</x:v>
@@ -14372,8 +14372,8 @@
       <x:c r="BD49" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE49" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE49" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF49" s="6" t="s">
         <x:v>107</x:v>
@@ -15792,8 +15792,8 @@
       <x:c r="BD54" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE54" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE54" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF54" s="6" t="s">
         <x:v>107</x:v>
@@ -17504,8 +17504,8 @@
       <x:c r="BD61" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE61" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE61" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF61" t="s">
         <x:v>1</x:v>
@@ -20912,8 +20912,8 @@
       <x:c r="BD73" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE73" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE73" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF73" s="6" t="s">
         <x:v>107</x:v>
@@ -22332,8 +22332,8 @@
       <x:c r="BD78" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE78" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE78" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF78" s="6" t="s">
         <x:v>107</x:v>
@@ -25180,8 +25180,8 @@
       <x:c r="BD89" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE89" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE89" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF89" s="6" t="s">
         <x:v>107</x:v>
@@ -25748,8 +25748,8 @@
       <x:c r="BD91" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE91" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE91" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF91" t="s">
         <x:v>1</x:v>
@@ -26316,8 +26316,8 @@
       <x:c r="BD93" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE93" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE93" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF93" s="6" t="s">
         <x:v>107</x:v>
@@ -29448,8 +29448,8 @@
       <x:c r="BD105" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE105" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE105" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF105" s="6" t="s">
         <x:v>107</x:v>
@@ -32572,8 +32572,8 @@
       <x:c r="BD116" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE116" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE116" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF116" t="s">
         <x:v>1</x:v>
@@ -33432,8 +33432,8 @@
       <x:c r="BD120" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE120" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE120" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF120" s="6" t="s">
         <x:v>107</x:v>
@@ -35704,8 +35704,8 @@
       <x:c r="BD128" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE128" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE128" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF128" s="6" t="s">
         <x:v>107</x:v>
@@ -36272,8 +36272,8 @@
       <x:c r="BD130" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE130" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE130" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF130" t="s">
         <x:v>1</x:v>
@@ -36556,8 +36556,8 @@
       <x:c r="BD131" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE131" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE131" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF131" t="s">
         <x:v>1</x:v>
@@ -41400,8 +41400,8 @@
       <x:c r="BD150" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE150" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE150" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF150" t="s">
         <x:v>1</x:v>
@@ -43388,8 +43388,8 @@
       <x:c r="BD157" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE157" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE157" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF157" t="s">
         <x:v>1</x:v>
@@ -43672,8 +43672,8 @@
       <x:c r="BD158" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE158" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE158" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF158" s="6" t="s">
         <x:v>107</x:v>
@@ -43956,8 +43956,8 @@
       <x:c r="BD159" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE159" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE159" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF159" t="s">
         <x:v>1</x:v>
@@ -47648,8 +47648,8 @@
       <x:c r="BD172" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE172" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE172" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF172" t="s">
         <x:v>1</x:v>
@@ -58472,8 +58472,8 @@
       <x:c r="BD214" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE214" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE214" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF214" s="6" t="s">
         <x:v>107</x:v>
@@ -58756,8 +58756,8 @@
       <x:c r="BD215" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE215" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE215" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF215" s="6" t="s">
         <x:v>107</x:v>
@@ -59040,8 +59040,8 @@
       <x:c r="BD216" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE216" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE216" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF216" s="6" t="s">
         <x:v>107</x:v>
@@ -59324,8 +59324,8 @@
       <x:c r="BD217" s="6" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="BE217" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE217" s="6" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BF217" s="6" t="s">
         <x:v>107</x:v>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R658cbb8358d84bce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R864bd3a6973d424a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.8.11 </x:t>
+ 2026.8.14 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R864bd3a6973d424a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Ra5deac12fd9a4d6a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.8.14 </x:t>
+ 2026.8.16 </x:t>
   </x:si>
   <x:si>
     <x:t>ECMAScript</x:t>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R74aae3860d32421d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Reb2729751cd94b1c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -135,7 +135,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.8.17 </x:t>
+ 2026.8.19 </x:t>
   </x:si>
   <x:si>
     <x:t>Regex</x:t>
@@ -15809,8 +15809,8 @@
       <x:c r="BE52" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BF52" t="s">
-        <x:v>1</x:v>
+      <x:c r="BF52" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BG52" t="s">
         <x:v>1</x:v>
@@ -15842,11 +15842,11 @@
       <x:c r="BP52" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BQ52" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR52" t="s">
-        <x:v>1</x:v>
+      <x:c r="BQ52" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BR52" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BS52" t="s">
         <x:v>1</x:v>
@@ -15926,11 +15926,11 @@
       <x:c r="CR52" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CS52" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CT52" t="s">
-        <x:v>1</x:v>
+      <x:c r="CS52" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CT52" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -22625,8 +22625,8 @@
       <x:c r="BE76" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BF76" t="s">
-        <x:v>1</x:v>
+      <x:c r="BF76" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BG76" t="s">
         <x:v>1</x:v>
@@ -22658,11 +22658,11 @@
       <x:c r="BP76" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BQ76" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR76" t="s">
-        <x:v>1</x:v>
+      <x:c r="BQ76" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BR76" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BS76" t="s">
         <x:v>1</x:v>
@@ -22742,11 +22742,11 @@
       <x:c r="CR76" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CS76" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CT76" t="s">
-        <x:v>1</x:v>
+      <x:c r="CS76" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CT76" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="77">

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Reb2729751cd94b1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rf1d7c01466074b3e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5573,8 +5573,8 @@
       <x:c r="E16" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="F16" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="F16" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G16" t="s">
         <x:v>1</x:v>
@@ -43812,8 +43812,8 @@
       <x:c r="B153" s="5" t="s">
         <x:v>342</x:v>
       </x:c>
-      <x:c r="C153" t="s">
-        <x:v>1</x:v>
+      <x:c r="C153" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D153" t="s">
         <x:v>1</x:v>
@@ -43821,8 +43821,8 @@
       <x:c r="E153" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F153" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="F153" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G153" t="s">
         <x:v>1</x:v>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R8c7589d7656f4b2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R276e8a5dbaab4a2c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -71,7 +71,7 @@
   </x:si>
   <x:si>
     <x:t>Rust
- 1.97.1 </x:t>
+ 1.98.0 </x:t>
   </x:si>
   <x:si>
     <x:t>Java

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rbed83f87198e4a1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R957cdd86f644428a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -127,7 +127,7 @@
   </x:si>
   <x:si>
     <x:t>Go
- 1.26.5 </x:t>
+ 1.27.0 </x:t>
   </x:si>
   <x:si>
     <x:t>Dart
@@ -348,7 +348,7 @@
     <x:t>coregex</x:t>
   </x:si>
   <x:si>
-    <x:t>coregex (posix)</x:t>
+    <x:t>onigmo</x:t>
   </x:si>
   <x:si>
     <x:t>RegExp</x:t>
@@ -1685,7 +1685,7 @@
     <x:col min="90" max="90" width="8.498000000000001" customWidth="1"/>
     <x:col min="91" max="91" width="5.498" customWidth="1"/>
     <x:col min="92" max="92" width="8.398" customWidth="1"/>
-    <x:col min="93" max="93" width="14.292" customWidth="1"/>
+    <x:col min="93" max="93" width="7.897" customWidth="1"/>
     <x:col min="94" max="94" width="8.396" customWidth="1"/>
     <x:col min="95" max="95" width="16.391" customWidth="1"/>
     <x:col min="96" max="96" width="10.996" customWidth="1"/>
@@ -4650,8 +4650,8 @@
       <x:c r="CN12" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO12" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO12" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP12" t="s">
         <x:v>1</x:v>
@@ -6722,8 +6722,8 @@
       <x:c r="CN19" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO19" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO19" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP19" t="s">
         <x:v>1</x:v>
@@ -7314,8 +7314,8 @@
       <x:c r="CN21" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CO21" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CO21" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CP21" t="s">
         <x:v>1</x:v>
@@ -10874,8 +10874,8 @@
       <x:c r="CN34" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO34" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO34" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP34" t="s">
         <x:v>1</x:v>
@@ -11770,8 +11770,8 @@
       <x:c r="CN38" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO38" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO38" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP38" t="s">
         <x:v>1</x:v>
@@ -13842,8 +13842,8 @@
       <x:c r="CN45" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CO45" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CO45" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CP45" s="6" t="s">
         <x:v>112</x:v>
@@ -15026,8 +15026,8 @@
       <x:c r="CN49" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CO49" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CO49" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CP49" t="s">
         <x:v>1</x:v>
@@ -18290,8 +18290,8 @@
       <x:c r="CN61" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO61" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO61" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP61" s="6" t="s">
         <x:v>112</x:v>
@@ -18586,8 +18586,8 @@
       <x:c r="CN62" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO62" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO62" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP62" t="s">
         <x:v>1</x:v>
@@ -20658,8 +20658,8 @@
       <x:c r="CN69" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CO69" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CO69" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CP69" s="6" t="s">
         <x:v>112</x:v>
@@ -21842,8 +21842,8 @@
       <x:c r="CN73" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CO73" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CO73" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CP73" t="s">
         <x:v>1</x:v>
@@ -25994,8 +25994,8 @@
       <x:c r="CN88" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO88" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO88" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP88" t="s">
         <x:v>1</x:v>
@@ -27474,8 +27474,8 @@
       <x:c r="CN93" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO93" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO93" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP93" t="s">
         <x:v>1</x:v>
@@ -29546,8 +29546,8 @@
       <x:c r="CN100" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CO100" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CO100" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CP100" t="s">
         <x:v>1</x:v>
@@ -30442,8 +30442,8 @@
       <x:c r="CN104" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO104" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO104" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP104" t="s">
         <x:v>1</x:v>
@@ -33402,8 +33402,8 @@
       <x:c r="CN114" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CO114" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CO114" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CP114" t="s">
         <x:v>1</x:v>
@@ -39338,8 +39338,8 @@
       <x:c r="CN136" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO136" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO136" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP136" t="s">
         <x:v>1</x:v>
@@ -40226,8 +40226,8 @@
       <x:c r="CN139" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO139" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO139" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP139" t="s">
         <x:v>1</x:v>
@@ -43194,8 +43194,8 @@
       <x:c r="CN150" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO150" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO150" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP150" t="s">
         <x:v>1</x:v>
@@ -43786,8 +43786,8 @@
       <x:c r="CN152" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CO152" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CO152" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CP152" t="s">
         <x:v>1</x:v>
@@ -44378,8 +44378,8 @@
       <x:c r="CN154" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CO154" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CO154" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CP154" s="6" t="s">
         <x:v>112</x:v>
@@ -44674,8 +44674,8 @@
       <x:c r="CN155" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO155" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO155" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP155" s="6" t="s">
         <x:v>112</x:v>
@@ -44970,8 +44970,8 @@
       <x:c r="CN156" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO156" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO156" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP156" s="6" t="s">
         <x:v>112</x:v>
@@ -45266,8 +45266,8 @@
       <x:c r="CN157" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO157" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO157" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP157" t="s">
         <x:v>1</x:v>
@@ -45562,8 +45562,8 @@
       <x:c r="CN158" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO158" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO158" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP158" s="6" t="s">
         <x:v>112</x:v>
@@ -47042,8 +47042,8 @@
       <x:c r="CN163" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO163" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO163" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP163" t="s">
         <x:v>1</x:v>
@@ -47634,8 +47634,8 @@
       <x:c r="CN165" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO165" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO165" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP165" t="s">
         <x:v>1</x:v>
@@ -50306,8 +50306,8 @@
       <x:c r="CN175" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO175" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO175" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP175" s="6" t="s">
         <x:v>112</x:v>
@@ -50602,8 +50602,8 @@
       <x:c r="CN176" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO176" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO176" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP176" s="6" t="s">
         <x:v>112</x:v>
@@ -50898,8 +50898,8 @@
       <x:c r="CN177" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO177" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO177" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP177" s="6" t="s">
         <x:v>112</x:v>
@@ -51786,8 +51786,8 @@
       <x:c r="CN180" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO180" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO180" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP180" s="6" t="s">
         <x:v>112</x:v>
@@ -52674,8 +52674,8 @@
       <x:c r="CN183" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO183" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO183" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP183" s="6" t="s">
         <x:v>112</x:v>
@@ -52970,8 +52970,8 @@
       <x:c r="CN184" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO184" t="s">
-        <x:v>1</x:v>
+      <x:c r="CO184" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CP184" t="s">
         <x:v>1</x:v>
@@ -60098,8 +60098,8 @@
       <x:c r="CN211" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CO211" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CO211" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CP211" t="s">
         <x:v>1</x:v>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R957cdd86f644428a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R37607ab1a532417f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -657,7 +657,7 @@
     <x:t>Generic escape</x:t>
   </x:si>
   <x:si>
-    <x:t>Escapes inside […] sets</x:t>
+    <x:t>Escapes inside sets</x:t>
   </x:si>
   <x:si>
     <x:t>[\a]</x:t>
@@ -837,7 +837,7 @@
     <x:t>Unicode property</x:t>
   </x:si>
   <x:si>
-    <x:t>Classes inside […] sets</x:t>
+    <x:t>Classes inside sets</x:t>
   </x:si>
   <x:si>
     <x:t>[\d], [\D]</x:t>
@@ -894,7 +894,7 @@
     <x:t>Collating symbol</x:t>
   </x:si>
   <x:si>
-    <x:t>Operators inside […] sets</x:t>
+    <x:t>Operators inside sets</x:t>
   </x:si>
   <x:si>
     <x:t>[[…] op […]]</x:t>
@@ -1326,6 +1326,12 @@
     <x:t>Miscellaneous</x:t>
   </x:si>
   <x:si>
+    <x:t>Get all captures matched by group</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Differentiate between empty groups and failed groups</x:t>
+  </x:si>
+  <x:si>
     <x:t>(*verb)</x:t>
   </x:si>
   <x:si>
@@ -1464,10 +1470,7 @@
     <x:t>Complement (pattern must not match)</x:t>
   </x:si>
   <x:si>
-    <x:t>Get all captures matched by group</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Also support alternative syntax</x:t>
+    <x:t>Support alternative syntax</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -58935,13 +58938,13 @@
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B208" s="5" t="s">
         <x:v>429</x:v>
       </x:c>
-      <x:c r="B208" s="5" t="s">
-        <x:v>430</x:v>
-      </x:c>
-      <x:c r="C208" t="s">
-        <x:v>1</x:v>
+      <x:c r="C208" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D208" t="s">
         <x:v>1</x:v>
@@ -58991,8 +58994,8 @@
       <x:c r="S208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="T208" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="T208" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U208" s="6" t="s">
         <x:v>112</x:v>
@@ -59018,8 +59021,8 @@
       <x:c r="AB208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AC208" t="s">
-        <x:v>1</x:v>
+      <x:c r="AC208" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AD208" s="6" t="s">
         <x:v>112</x:v>
@@ -59039,8 +59042,8 @@
       <x:c r="AI208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AJ208" t="s">
-        <x:v>1</x:v>
+      <x:c r="AJ208" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AK208" s="6" t="s">
         <x:v>112</x:v>
@@ -59048,8 +59051,8 @@
       <x:c r="AL208" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="AM208" t="s">
-        <x:v>1</x:v>
+      <x:c r="AM208" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AN208" s="6" t="s">
         <x:v>112</x:v>
@@ -59078,11 +59081,11 @@
       <x:c r="AV208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AW208" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AX208" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="AW208" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX208" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AY208" t="s">
         <x:v>1</x:v>
@@ -59093,8 +59096,8 @@
       <x:c r="BA208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB208" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BB208" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BC208" t="s">
         <x:v>1</x:v>
@@ -59147,8 +59150,8 @@
       <x:c r="BS208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BT208" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BT208" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BU208" t="s">
         <x:v>1</x:v>
@@ -59171,11 +59174,11 @@
       <x:c r="CA208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CB208" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CC208" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CB208" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC208" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CD208" t="s">
         <x:v>1</x:v>
@@ -59219,8 +59222,8 @@
       <x:c r="CQ208" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CR208" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CR208" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CS208" t="s">
         <x:v>1</x:v>
@@ -59231,58 +59234,58 @@
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="4" t="s">
-        <x:v>431</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B209" s="5" t="s">
-        <x:v>432</x:v>
-      </x:c>
-      <x:c r="C209" t="s">
-        <x:v>1</x:v>
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="C209" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D209" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E209" t="s">
-        <x:v>1</x:v>
+      <x:c r="E209" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F209" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R209" t="s">
-        <x:v>1</x:v>
+      <x:c r="G209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="I209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="J209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="K209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="L209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="M209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="N209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="O209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="P209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="Q209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="R209" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="S209" t="s">
         <x:v>1</x:v>
@@ -59290,86 +59293,86 @@
       <x:c r="T209" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="U209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU209" t="s">
-        <x:v>1</x:v>
+      <x:c r="U209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="V209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="W209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="X209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="Y209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="Z209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AA209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AB209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AC209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AD209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AE209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AF209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AG209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AH209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AI209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AJ209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AK209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AL209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AM209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AN209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AO209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AP209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AQ209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AR209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AS209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AT209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AU209" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AV209" t="s">
         <x:v>1</x:v>
@@ -59377,23 +59380,23 @@
       <x:c r="AW209" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AX209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC209" t="s">
-        <x:v>1</x:v>
+      <x:c r="AX209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AY209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AZ209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BA209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BB209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BC209" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BD209" t="s">
         <x:v>1</x:v>
@@ -59401,44 +59404,44 @@
       <x:c r="BE209" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BF209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR209" t="s">
-        <x:v>1</x:v>
+      <x:c r="BF209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BG209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BH209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BI209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BJ209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BK209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BL209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BM209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BN209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BO209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BP209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BQ209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BR209" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BS209" t="s">
         <x:v>1</x:v>
@@ -59455,17 +59458,17 @@
       <x:c r="BW209" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BX209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY209" t="s">
-        <x:v>1</x:v>
+      <x:c r="BX209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BY209" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BZ209" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CA209" t="s">
-        <x:v>1</x:v>
+      <x:c r="CA209" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CB209" t="s">
         <x:v>1</x:v>
@@ -59473,14 +59476,14 @@
       <x:c r="CC209" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CD209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF209" t="s">
-        <x:v>1</x:v>
+      <x:c r="CD209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CE209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CF209" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CG209" t="s">
         <x:v>1</x:v>
@@ -59488,49 +59491,49 @@
       <x:c r="CH209" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CI209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CJ209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CK209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CL209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CM209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CN209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CO209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CP209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CQ209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CR209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CS209" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CT209" t="s">
-        <x:v>1</x:v>
+      <x:c r="CI209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CJ209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CK209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CL209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CM209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CN209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CO209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CP209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CQ209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CR209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CS209" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CT209" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="4" t="s">
-        <x:v>433</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B210" s="5" t="s">
-        <x:v>434</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="C210" t="s">
         <x:v>1</x:v>
@@ -59586,11 +59589,11 @@
       <x:c r="T210" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="U210" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V210" t="s">
-        <x:v>1</x:v>
+      <x:c r="U210" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="V210" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="W210" t="s">
         <x:v>1</x:v>
@@ -59670,11 +59673,11 @@
       <x:c r="AV210" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AW210" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX210" t="s">
-        <x:v>1</x:v>
+      <x:c r="AW210" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AX210" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AY210" t="s">
         <x:v>1</x:v>
@@ -59685,8 +59688,8 @@
       <x:c r="BA210" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB210" t="s">
-        <x:v>1</x:v>
+      <x:c r="BB210" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BC210" t="s">
         <x:v>1</x:v>
@@ -59727,11 +59730,11 @@
       <x:c r="BO210" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BP210" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ210" t="s">
-        <x:v>1</x:v>
+      <x:c r="BP210" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BQ210" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BR210" t="s">
         <x:v>1</x:v>
@@ -59739,8 +59742,8 @@
       <x:c r="BS210" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BT210" t="s">
-        <x:v>1</x:v>
+      <x:c r="BT210" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BU210" t="s">
         <x:v>1</x:v>
@@ -59763,11 +59766,11 @@
       <x:c r="CA210" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CB210" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC210" t="s">
-        <x:v>1</x:v>
+      <x:c r="CB210" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CC210" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CD210" t="s">
         <x:v>1</x:v>
@@ -59811,8 +59814,8 @@
       <x:c r="CQ210" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CR210" t="s">
-        <x:v>1</x:v>
+      <x:c r="CR210" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CS210" t="s">
         <x:v>1</x:v>
@@ -59823,10 +59826,10 @@
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="4" t="s">
-        <x:v>435</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B211" s="5" t="s">
-        <x:v>436</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="C211" t="s">
         <x:v>1</x:v>
@@ -59870,8 +59873,8 @@
       <x:c r="P211" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q211" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="Q211" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R211" t="s">
         <x:v>1</x:v>
@@ -59957,8 +59960,8 @@
       <x:c r="AS211" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AT211" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="AT211" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AU211" t="s">
         <x:v>1</x:v>
@@ -59966,11 +59969,11 @@
       <x:c r="AV211" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AW211" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AX211" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="AW211" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX211" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AY211" t="s">
         <x:v>1</x:v>
@@ -59996,8 +59999,8 @@
       <x:c r="BF211" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BG211" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BG211" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BH211" t="s">
         <x:v>1</x:v>
@@ -60005,14 +60008,14 @@
       <x:c r="BI211" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BJ211" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BK211" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BL211" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BJ211" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK211" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL211" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BM211" t="s">
         <x:v>1</x:v>
@@ -60023,11 +60026,11 @@
       <x:c r="BO211" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BP211" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BQ211" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BP211" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ211" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BR211" t="s">
         <x:v>1</x:v>
@@ -60050,8 +60053,8 @@
       <x:c r="BX211" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BY211" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BY211" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BZ211" t="s">
         <x:v>1</x:v>
@@ -60059,8 +60062,8 @@
       <x:c r="CA211" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CB211" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CB211" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CC211" s="6" t="s">
         <x:v>112</x:v>
@@ -60068,14 +60071,14 @@
       <x:c r="CD211" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CE211" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CE211" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CF211" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CG211" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CG211" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CH211" t="s">
         <x:v>1</x:v>
@@ -60083,8 +60086,8 @@
       <x:c r="CI211" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CJ211" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CJ211" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CK211" t="s">
         <x:v>1</x:v>
@@ -60095,8 +60098,8 @@
       <x:c r="CM211" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CN211" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CN211" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CO211" t="s">
         <x:v>1</x:v>
@@ -60107,8 +60110,8 @@
       <x:c r="CQ211" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CR211" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CR211" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CS211" t="s">
         <x:v>1</x:v>
@@ -60119,10 +60122,10 @@
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="4" t="s">
-        <x:v>437</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B212" s="5" t="s">
-        <x:v>438</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="C212" t="s">
         <x:v>1</x:v>
@@ -60136,8 +60139,8 @@
       <x:c r="F212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G212" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="G212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H212" t="s">
         <x:v>1</x:v>
@@ -60154,17 +60157,17 @@
       <x:c r="L212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M212" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="N212" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="O212" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="P212" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="M212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q212" t="s">
         <x:v>1</x:v>
@@ -60205,8 +60208,8 @@
       <x:c r="AC212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AD212" t="s">
-        <x:v>1</x:v>
+      <x:c r="AD212" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AE212" t="s">
         <x:v>1</x:v>
@@ -60226,38 +60229,38 @@
       <x:c r="AJ212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AK212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL212" t="s">
-        <x:v>1</x:v>
+      <x:c r="AK212" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AL212" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AM212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AN212" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO212" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AP212" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AQ212" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AR212" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AS212" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="AN212" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AO212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AT212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AU212" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="AU212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AV212" t="s">
         <x:v>1</x:v>
@@ -60280,14 +60283,14 @@
       <x:c r="BB212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC212" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BC212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE212" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BE212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BF212" t="s">
         <x:v>1</x:v>
@@ -60310,8 +60313,8 @@
       <x:c r="BL212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BM212" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BM212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BN212" t="s">
         <x:v>1</x:v>
@@ -60337,8 +60340,8 @@
       <x:c r="BU212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BV212" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BV212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BW212" t="s">
         <x:v>1</x:v>
@@ -60349,8 +60352,8 @@
       <x:c r="BY212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BZ212" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BZ212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CA212" t="s">
         <x:v>1</x:v>
@@ -60367,11 +60370,11 @@
       <x:c r="CE212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CF212" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CG212" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CF212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CH212" t="s">
         <x:v>1</x:v>
@@ -60388,8 +60391,8 @@
       <x:c r="CL212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CM212" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CM212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CN212" t="s">
         <x:v>1</x:v>
@@ -60397,11 +60400,11 @@
       <x:c r="CO212" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CP212" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CQ212" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CP212" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CQ212" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CR212" t="s">
         <x:v>1</x:v>
@@ -60415,10 +60418,10 @@
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="4" t="s">
-        <x:v>439</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B213" s="5" t="s">
-        <x:v>440</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="C213" t="s">
         <x:v>1</x:v>
@@ -60432,8 +60435,8 @@
       <x:c r="F213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G213" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="G213" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H213" t="s">
         <x:v>1</x:v>
@@ -60450,20 +60453,20 @@
       <x:c r="L213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M213" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="N213" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="O213" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="P213" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="Q213" t="s">
-        <x:v>1</x:v>
+      <x:c r="M213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q213" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="R213" t="s">
         <x:v>1</x:v>
@@ -60534,35 +60537,35 @@
       <x:c r="AN213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO213" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AP213" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AQ213" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AR213" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AS213" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AT213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU213" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="AO213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT213" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AU213" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AV213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AW213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX213" t="s">
-        <x:v>1</x:v>
+      <x:c r="AW213" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AX213" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AY213" t="s">
         <x:v>1</x:v>
@@ -60576,38 +60579,38 @@
       <x:c r="BB213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BC213" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BC213" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BE213" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BE213" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BF213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BG213" t="s">
-        <x:v>1</x:v>
+      <x:c r="BG213" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BH213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BI213" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BJ213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM213" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BI213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ213" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BK213" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BL213" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BM213" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BN213" t="s">
         <x:v>1</x:v>
@@ -60615,11 +60618,11 @@
       <x:c r="BO213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BP213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ213" t="s">
-        <x:v>1</x:v>
+      <x:c r="BP213" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BQ213" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BR213" t="s">
         <x:v>1</x:v>
@@ -60627,14 +60630,14 @@
       <x:c r="BS213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BT213" t="s">
-        <x:v>1</x:v>
+      <x:c r="BT213" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BU213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BV213" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BV213" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BW213" t="s">
         <x:v>1</x:v>
@@ -60642,29 +60645,29 @@
       <x:c r="BX213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BY213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ213" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BY213" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BZ213" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CA213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CB213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD213" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CE213" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF213" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CB213" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CC213" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CD213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE213" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CF213" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CG213" s="6" t="s">
         <x:v>112</x:v>
@@ -60675,8 +60678,8 @@
       <x:c r="CI213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CJ213" t="s">
-        <x:v>1</x:v>
+      <x:c r="CJ213" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CK213" t="s">
         <x:v>1</x:v>
@@ -60684,23 +60687,23 @@
       <x:c r="CL213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CM213" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CN213" t="s">
-        <x:v>1</x:v>
+      <x:c r="CM213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CN213" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CO213" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CP213" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CQ213" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CR213" t="s">
-        <x:v>1</x:v>
+      <x:c r="CP213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CQ213" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CR213" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CS213" t="s">
         <x:v>1</x:v>
@@ -60711,40 +60714,40 @@
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="4" t="s">
-        <x:v>441</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="B214" s="5" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="C214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="E214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="F214" s="6" t="s">
-        <x:v>112</x:v>
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="C214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G214" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="I214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="J214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="K214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="L214" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="H214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M214" s="6" t="s">
         <x:v>112</x:v>
@@ -60758,11 +60761,11 @@
       <x:c r="P214" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="Q214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="R214" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="Q214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="S214" t="s">
         <x:v>1</x:v>
@@ -60770,65 +60773,65 @@
       <x:c r="T214" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="U214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="V214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="W214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="X214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="Y214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="Z214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AA214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AB214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AC214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AD214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AE214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AF214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AG214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AH214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AI214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AJ214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AK214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AL214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AM214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AN214" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="U214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AO214" s="6" t="s">
         <x:v>112</x:v>
@@ -60845,149 +60848,149 @@
       <x:c r="AS214" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="AT214" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="AT214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AU214" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="AV214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AW214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AX214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AY214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AZ214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BA214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BB214" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="AV214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BC214" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BD214" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BD214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BE214" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BF214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BG214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BH214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BI214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BJ214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BK214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BL214" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BF214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BM214" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BN214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BO214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BP214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BQ214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BR214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BS214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BT214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BU214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BV214" t="s">
-        <x:v>1</x:v>
+      <x:c r="BN214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV214" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BW214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BX214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BY214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BZ214" t="s">
-        <x:v>1</x:v>
+      <x:c r="BX214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ214" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CA214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CB214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CC214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CD214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CE214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CF214" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CG214" t="s">
-        <x:v>1</x:v>
+      <x:c r="CB214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF214" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CG214" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CH214" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CI214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CJ214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CK214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CL214" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CI214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CJ214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CK214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CL214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CM214" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CN214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CO214" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CN214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CO214" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CP214" s="6" t="s">
         <x:v>112</x:v>
@@ -60995,34 +60998,34 @@
       <x:c r="CQ214" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CR214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CS214" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CT214" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CR214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CS214" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CT214" t="s">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="4" t="s">
-        <x:v>443</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B215" s="5" t="s">
-        <x:v>444</x:v>
-      </x:c>
-      <x:c r="C215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="E215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="F215" s="6" t="s">
-        <x:v>112</x:v>
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="C215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G215" s="6" t="s">
         <x:v>112</x:v>
@@ -61045,14 +61048,14 @@
       <x:c r="M215" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="N215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P215" t="s">
-        <x:v>1</x:v>
+      <x:c r="N215" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="O215" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="P215" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="Q215" t="s">
         <x:v>1</x:v>
@@ -61066,20 +61069,20 @@
       <x:c r="T215" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="U215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="V215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="W215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="X215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="Y215" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="U215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Z215" t="s">
         <x:v>1</x:v>
@@ -61090,11 +61093,11 @@
       <x:c r="AB215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AC215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AD215" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="AC215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AE215" t="s">
         <x:v>1</x:v>
@@ -61105,128 +61108,128 @@
       <x:c r="AG215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AI215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AJ215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AK215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AL215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AM215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AN215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AO215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS215" t="s">
-        <x:v>1</x:v>
+      <x:c r="AH215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO215" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AP215" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AQ215" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AR215" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AS215" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AT215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AU215" t="s">
-        <x:v>1</x:v>
+      <x:c r="AU215" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AV215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AW215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AX215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AY215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AZ215" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="AW215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BA215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BC215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BE215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BG215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BH215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BI215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ215" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BB215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC215" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BD215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE215" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BF215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI215" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BJ215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BK215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BL215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BM215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BO215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BP215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BQ215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BR215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BS215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BT215" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BL215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM215" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BN215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BU215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BV215" t="s">
-        <x:v>1</x:v>
+      <x:c r="BV215" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BW215" t="s">
         <x:v>1</x:v>
@@ -61237,8 +61240,8 @@
       <x:c r="BY215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BZ215" t="s">
-        <x:v>1</x:v>
+      <x:c r="BZ215" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CA215" t="s">
         <x:v>1</x:v>
@@ -61246,26 +61249,26 @@
       <x:c r="CB215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CC215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CD215" t="s">
-        <x:v>1</x:v>
+      <x:c r="CC215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD215" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CE215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CF215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CG215" t="s">
-        <x:v>1</x:v>
+      <x:c r="CF215" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CG215" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CH215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CI215" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CI215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CJ215" t="s">
         <x:v>1</x:v>
@@ -61273,11 +61276,11 @@
       <x:c r="CK215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CL215" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CM215" t="s">
-        <x:v>1</x:v>
+      <x:c r="CL215" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CM215" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CN215" t="s">
         <x:v>1</x:v>
@@ -61285,28 +61288,28 @@
       <x:c r="CO215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CP215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CQ215" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CR215" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CP215" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CQ215" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CR215" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CS215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CT215" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CT215" t="s">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="4" t="s">
-        <x:v>445</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B216" s="5" t="s">
-        <x:v>446</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="C216" s="6" t="s">
         <x:v>112</x:v>
@@ -61599,25 +61602,25 @@
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="4" t="s">
-        <x:v>447</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B217" s="5" t="s">
-        <x:v>448</x:v>
-      </x:c>
-      <x:c r="C217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D217" t="s">
-        <x:v>1</x:v>
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="C217" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D217" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E217" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="F217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G217" t="s">
-        <x:v>1</x:v>
+      <x:c r="F217" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G217" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H217" t="s">
         <x:v>1</x:v>
@@ -61634,8 +61637,8 @@
       <x:c r="L217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M217" t="s">
-        <x:v>1</x:v>
+      <x:c r="M217" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="N217" t="s">
         <x:v>1</x:v>
@@ -61646,32 +61649,32 @@
       <x:c r="P217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q217" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="R217" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="Q217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="S217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="T217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X217" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y217" t="s">
-        <x:v>1</x:v>
+      <x:c r="T217" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="U217" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="V217" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="W217" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="X217" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="Y217" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="Z217" t="s">
         <x:v>1</x:v>
@@ -61682,20 +61685,20 @@
       <x:c r="AB217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AC217" t="s">
-        <x:v>1</x:v>
+      <x:c r="AC217" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AD217" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="AE217" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AF217" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AG217" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="AE217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AH217" s="6" t="s">
         <x:v>112</x:v>
@@ -61721,23 +61724,23 @@
       <x:c r="AO217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AP217" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AQ217" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AR217" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AS217" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AT217" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AU217" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="AP217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AV217" t="s">
         <x:v>1</x:v>
@@ -61754,20 +61757,20 @@
       <x:c r="AZ217" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BA217" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BA217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BB217" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BC217" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BC217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD217" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BE217" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BE217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BF217" s="6" t="s">
         <x:v>112</x:v>
@@ -61778,14 +61781,14 @@
       <x:c r="BH217" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BI217" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BI217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BJ217" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BK217" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BK217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BL217" s="6" t="s">
         <x:v>112</x:v>
@@ -61814,8 +61817,8 @@
       <x:c r="BT217" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BU217" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BU217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BV217" t="s">
         <x:v>1</x:v>
@@ -61835,8 +61838,8 @@
       <x:c r="CA217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CB217" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CB217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CC217" s="6" t="s">
         <x:v>112</x:v>
@@ -61859,35 +61862,35 @@
       <x:c r="CI217" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CJ217" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CK217" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CJ217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CK217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CL217" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CM217" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CN217" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CO217" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CM217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CN217" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CO217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CP217" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CQ217" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CQ217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CR217" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CS217" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CS217" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CT217" s="6" t="s">
         <x:v>112</x:v>
@@ -61895,10 +61898,10 @@
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="4" t="s">
-        <x:v>449</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B218" s="5" t="s">
-        <x:v>450</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="C218" s="6" t="s">
         <x:v>112</x:v>
@@ -61912,26 +61915,26 @@
       <x:c r="F218" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M218" t="s">
-        <x:v>1</x:v>
+      <x:c r="G218" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H218" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="I218" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="J218" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="K218" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="L218" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="M218" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="N218" s="6" t="s">
         <x:v>112</x:v>
@@ -62050,8 +62053,8 @@
       <x:c r="AZ218" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BA218" t="s">
-        <x:v>1</x:v>
+      <x:c r="BA218" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BB218" s="6" t="s">
         <x:v>112</x:v>
@@ -62062,8 +62065,8 @@
       <x:c r="BD218" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BE218" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE218" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BF218" s="6" t="s">
         <x:v>112</x:v>
@@ -62074,8 +62077,8 @@
       <x:c r="BH218" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BI218" t="s">
-        <x:v>1</x:v>
+      <x:c r="BI218" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BJ218" s="6" t="s">
         <x:v>112</x:v>
@@ -62110,8 +62113,8 @@
       <x:c r="BT218" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BU218" t="s">
-        <x:v>1</x:v>
+      <x:c r="BU218" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BV218" t="s">
         <x:v>1</x:v>
@@ -62119,11 +62122,11 @@
       <x:c r="BW218" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BX218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY218" t="s">
-        <x:v>1</x:v>
+      <x:c r="BX218" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BY218" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BZ218" t="s">
         <x:v>1</x:v>
@@ -62137,11 +62140,11 @@
       <x:c r="CC218" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CD218" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE218" t="s">
-        <x:v>1</x:v>
+      <x:c r="CD218" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CE218" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CF218" t="s">
         <x:v>1</x:v>
@@ -62158,8 +62161,8 @@
       <x:c r="CJ218" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CK218" t="s">
-        <x:v>1</x:v>
+      <x:c r="CK218" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CL218" s="6" t="s">
         <x:v>112</x:v>
@@ -62182,8 +62185,8 @@
       <x:c r="CR218" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CS218" t="s">
-        <x:v>1</x:v>
+      <x:c r="CS218" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CT218" s="6" t="s">
         <x:v>112</x:v>
@@ -62191,10 +62194,10 @@
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="4" t="s">
-        <x:v>451</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B219" s="5" t="s">
-        <x:v>452</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C219" t="s">
         <x:v>1</x:v>
@@ -62229,14 +62232,14 @@
       <x:c r="M219" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N219" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="O219" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="P219" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="N219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O219" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P219" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q219" s="6" t="s">
         <x:v>112</x:v>
@@ -62247,8 +62250,8 @@
       <x:c r="S219" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="T219" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="T219" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U219" t="s">
         <x:v>1</x:v>
@@ -62310,8 +62313,8 @@
       <x:c r="AN219" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="AO219" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="AO219" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AP219" s="6" t="s">
         <x:v>112</x:v>
@@ -62346,8 +62349,8 @@
       <x:c r="AZ219" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BA219" t="s">
-        <x:v>1</x:v>
+      <x:c r="BA219" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BB219" s="6" t="s">
         <x:v>112</x:v>
@@ -62358,8 +62361,8 @@
       <x:c r="BD219" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BE219" t="s">
-        <x:v>1</x:v>
+      <x:c r="BE219" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BF219" s="6" t="s">
         <x:v>112</x:v>
@@ -62370,8 +62373,8 @@
       <x:c r="BH219" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BI219" t="s">
-        <x:v>1</x:v>
+      <x:c r="BI219" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BJ219" s="6" t="s">
         <x:v>112</x:v>
@@ -62406,8 +62409,8 @@
       <x:c r="BT219" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BU219" t="s">
-        <x:v>1</x:v>
+      <x:c r="BU219" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BV219" t="s">
         <x:v>1</x:v>
@@ -62454,14 +62457,14 @@
       <x:c r="CJ219" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CK219" t="s">
-        <x:v>1</x:v>
+      <x:c r="CK219" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CL219" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CM219" t="s">
-        <x:v>1</x:v>
+      <x:c r="CM219" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CN219" s="6" t="s">
         <x:v>112</x:v>
@@ -62469,8 +62472,8 @@
       <x:c r="CO219" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CP219" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CP219" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CQ219" s="6" t="s">
         <x:v>112</x:v>
@@ -62478,8 +62481,8 @@
       <x:c r="CR219" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CS219" t="s">
-        <x:v>1</x:v>
+      <x:c r="CS219" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CT219" s="6" t="s">
         <x:v>112</x:v>
@@ -62487,22 +62490,22 @@
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="4" t="s">
-        <x:v>453</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B220" s="5" t="s">
-        <x:v>454</x:v>
-      </x:c>
-      <x:c r="C220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F220" t="s">
-        <x:v>1</x:v>
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="C220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="E220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F220" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G220" t="s">
         <x:v>1</x:v>
@@ -62525,53 +62528,53 @@
       <x:c r="M220" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R220" t="s">
-        <x:v>1</x:v>
+      <x:c r="N220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="O220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="P220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="Q220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="R220" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="S220" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="T220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC220" t="s">
-        <x:v>1</x:v>
+      <x:c r="T220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="U220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="V220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="W220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="X220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="Y220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="Z220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AA220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AB220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AC220" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AD220" s="6" t="s">
         <x:v>112</x:v>
@@ -62606,86 +62609,86 @@
       <x:c r="AN220" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="AO220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX220" t="s">
-        <x:v>1</x:v>
+      <x:c r="AO220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AP220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AQ220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AR220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AS220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AT220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AU220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AV220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AW220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AX220" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AY220" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="AZ220" t="s">
-        <x:v>1</x:v>
+      <x:c r="AZ220" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BA220" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD220" t="s">
-        <x:v>1</x:v>
+      <x:c r="BB220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BC220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BD220" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BE220" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BF220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM220" t="s">
-        <x:v>1</x:v>
+      <x:c r="BF220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BG220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BH220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BI220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BJ220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BK220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BL220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BM220" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BN220" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BO220" t="s">
-        <x:v>1</x:v>
+      <x:c r="BO220" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BP220" s="6" t="s">
         <x:v>112</x:v>
@@ -62693,11 +62696,11 @@
       <x:c r="BQ220" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BR220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS220" t="s">
-        <x:v>1</x:v>
+      <x:c r="BR220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BS220" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BT220" s="6" t="s">
         <x:v>112</x:v>
@@ -62723,11 +62726,11 @@
       <x:c r="CA220" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CB220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC220" t="s">
-        <x:v>1</x:v>
+      <x:c r="CB220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CC220" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CD220" t="s">
         <x:v>1</x:v>
@@ -62747,29 +62750,29 @@
       <x:c r="CI220" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CJ220" t="s">
-        <x:v>1</x:v>
+      <x:c r="CJ220" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CK220" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CL220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CM220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CN220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CO220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CP220" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CQ220" t="s">
-        <x:v>1</x:v>
+      <x:c r="CL220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CM220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CN220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CO220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CP220" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CQ220" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CR220" s="6" t="s">
         <x:v>112</x:v>
@@ -62777,16 +62780,16 @@
       <x:c r="CS220" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CT220" t="s">
-        <x:v>1</x:v>
+      <x:c r="CT220" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="4" t="s">
-        <x:v>455</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B221" s="5" t="s">
-        <x:v>456</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="C221" t="s">
         <x:v>1</x:v>
@@ -62794,8 +62797,8 @@
       <x:c r="D221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E221" t="s">
-        <x:v>1</x:v>
+      <x:c r="E221" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F221" t="s">
         <x:v>1</x:v>
@@ -62821,26 +62824,26 @@
       <x:c r="M221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R221" t="s">
-        <x:v>1</x:v>
+      <x:c r="N221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="O221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="P221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="Q221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="R221" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="S221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="T221" t="s">
-        <x:v>1</x:v>
+      <x:c r="T221" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="U221" t="s">
         <x:v>1</x:v>
@@ -62869,59 +62872,59 @@
       <x:c r="AC221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AD221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU221" t="s">
-        <x:v>1</x:v>
+      <x:c r="AD221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AE221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AF221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AG221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AH221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AI221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AJ221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AK221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AL221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AM221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AN221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AO221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AP221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AQ221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AR221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AS221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AT221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AU221" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AV221" t="s">
         <x:v>1</x:v>
@@ -62929,59 +62932,59 @@
       <x:c r="AW221" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="AX221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ221" t="s">
-        <x:v>1</x:v>
+      <x:c r="AX221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AY221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AZ221" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BA221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BB221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD221" t="s">
-        <x:v>1</x:v>
+      <x:c r="BB221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BC221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BD221" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BE221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BF221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH221" t="s">
-        <x:v>1</x:v>
+      <x:c r="BF221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BG221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BH221" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BI221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BJ221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL221" t="s">
-        <x:v>1</x:v>
+      <x:c r="BJ221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BK221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BL221" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BM221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BN221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO221" t="s">
-        <x:v>1</x:v>
+      <x:c r="BN221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BO221" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BP221" s="6" t="s">
         <x:v>112</x:v>
@@ -62989,14 +62992,14 @@
       <x:c r="BQ221" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BR221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT221" t="s">
-        <x:v>1</x:v>
+      <x:c r="BR221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BS221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BT221" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BU221" t="s">
         <x:v>1</x:v>
@@ -63007,11 +63010,11 @@
       <x:c r="BW221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BX221" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BY221" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BX221" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY221" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BZ221" t="s">
         <x:v>1</x:v>
@@ -63019,11 +63022,11 @@
       <x:c r="CA221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CB221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC221" t="s">
-        <x:v>1</x:v>
+      <x:c r="CB221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CC221" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CD221" t="s">
         <x:v>1</x:v>
@@ -63040,58 +63043,58 @@
       <x:c r="CH221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CI221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CJ221" t="s">
-        <x:v>1</x:v>
+      <x:c r="CI221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CJ221" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CK221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CL221" t="s">
-        <x:v>1</x:v>
+      <x:c r="CL221" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CM221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CN221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CO221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CP221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CQ221" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CR221" t="s">
-        <x:v>1</x:v>
+      <x:c r="CN221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CO221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CP221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CQ221" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CR221" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CS221" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CT221" t="s">
-        <x:v>1</x:v>
+      <x:c r="CT221" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="4" t="s">
-        <x:v>457</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B222" s="5" t="s">
-        <x:v>458</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="C222" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="E222" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="D222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E222" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F222" t="s">
         <x:v>1</x:v>
@@ -63123,20 +63126,20 @@
       <x:c r="O222" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="Q222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="R222" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="P222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R222" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="S222" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="T222" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="T222" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U222" t="s">
         <x:v>1</x:v>
@@ -63210,11 +63213,11 @@
       <x:c r="AR222" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AS222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AT222" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="AS222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT222" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AU222" t="s">
         <x:v>1</x:v>
@@ -63222,56 +63225,56 @@
       <x:c r="AV222" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AW222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AX222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AY222" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BA222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BB222" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="AW222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY222" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AZ222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB222" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BC222" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BD222" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BD222" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BE222" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BF222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BG222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BH222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BI222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BJ222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BK222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BL222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BM222" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BF222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM222" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BN222" s="6" t="s">
         <x:v>112</x:v>
@@ -63285,44 +63288,44 @@
       <x:c r="BQ222" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BR222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BS222" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BR222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS222" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BT222" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BU222" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BU222" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BV222" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BW222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BX222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BY222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BZ222" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BW222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ222" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CA222" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CB222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CC222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CD222" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CB222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD222" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CE222" t="s">
         <x:v>1</x:v>
@@ -63330,32 +63333,32 @@
       <x:c r="CF222" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CG222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CH222" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CG222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CH222" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CI222" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CJ222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CK222" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CJ222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CK222" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CL222" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CM222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CN222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CO222" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CM222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CN222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CO222" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CP222" t="s">
         <x:v>1</x:v>
@@ -63366,19 +63369,19 @@
       <x:c r="CR222" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="CS222" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="CT222" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CS222" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CT222" t="s">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="4" t="s">
-        <x:v>459</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B223" s="5" t="s">
-        <x:v>460</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="C223" t="s">
         <x:v>1</x:v>
@@ -63392,32 +63395,32 @@
       <x:c r="F223" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G223" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="H223" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="I223" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="J223" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="K223" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="L223" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="G223" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H223" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I223" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J223" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K223" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L223" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M223" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N223" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="O223" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="N223" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O223" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="P223" t="s">
         <x:v>1</x:v>
@@ -63428,38 +63431,38 @@
       <x:c r="R223" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="S223" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="S223" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T223" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="U223" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="V223" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="W223" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="X223" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="Y223" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="Z223" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AA223" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AB223" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AC223" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="U223" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V223" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W223" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X223" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y223" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z223" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA223" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB223" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC223" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD223" t="s">
         <x:v>1</x:v>
@@ -63518,8 +63521,8 @@
       <x:c r="AV223" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AW223" t="s">
-        <x:v>1</x:v>
+      <x:c r="AW223" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AX223" t="s">
         <x:v>1</x:v>
@@ -63575,11 +63578,11 @@
       <x:c r="BO223" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BP223" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ223" t="s">
-        <x:v>1</x:v>
+      <x:c r="BP223" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BQ223" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BR223" t="s">
         <x:v>1</x:v>
@@ -63599,11 +63602,11 @@
       <x:c r="BW223" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BX223" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY223" t="s">
-        <x:v>1</x:v>
+      <x:c r="BX223" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BY223" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BZ223" t="s">
         <x:v>1</x:v>
@@ -63623,8 +63626,8 @@
       <x:c r="CE223" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CF223" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="CF223" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CG223" t="s">
         <x:v>1</x:v>
@@ -63670,20 +63673,308 @@
       </x:c>
     </x:row>
     <x:row r="224">
-      <x:c r="A224" s="3" t="s">
-        <x:v>461</x:v>
-      </x:c>
-      <x:c r="CT224" t="s">
-        <x:v>1</x:v>
+      <x:c r="A224" s="4" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="B224" s="5" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="C224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="E224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="Q224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="R224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="S224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="U224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AE224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AF224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AG224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AH224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AI224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AJ224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AK224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AL224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AM224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AN224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AO224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AT224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AU224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AX224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AY224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BA224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BB224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BC224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BE224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BG224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BH224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BI224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BJ224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BK224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BL224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BM224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BN224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BO224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BQ224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BR224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BS224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BT224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BU224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BV224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BX224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BY224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BZ224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CA224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CC224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CD224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CE224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CH224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CI224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CJ224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CK224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CL224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CM224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CN224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CO224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CP224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CQ224" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CR224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CS224" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="CT224" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="4" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="B225" s="5" t="s">
         <x:v>462</x:v>
       </x:c>
-      <x:c r="B225" s="5" t="s">
-        <x:v>463</x:v>
-      </x:c>
       <x:c r="C225" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -63696,32 +63987,32 @@
       <x:c r="F225" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G225" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H225" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I225" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J225" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K225" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L225" t="s">
-        <x:v>1</x:v>
+      <x:c r="G225" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H225" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="I225" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="J225" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="K225" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="L225" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="M225" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N225" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O225" t="s">
-        <x:v>1</x:v>
+      <x:c r="N225" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="O225" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="P225" t="s">
         <x:v>1</x:v>
@@ -63732,38 +64023,38 @@
       <x:c r="R225" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="S225" t="s">
-        <x:v>1</x:v>
+      <x:c r="S225" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="T225" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="U225" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V225" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W225" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X225" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y225" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z225" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA225" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB225" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC225" t="s">
-        <x:v>1</x:v>
+      <x:c r="U225" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="V225" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="W225" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="X225" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="Y225" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="Z225" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AA225" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AB225" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="AC225" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AD225" t="s">
         <x:v>1</x:v>
@@ -63828,8 +64119,8 @@
       <x:c r="AX225" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AY225" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="AY225" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AZ225" t="s">
         <x:v>1</x:v>
@@ -63927,8 +64218,8 @@
       <x:c r="CE225" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CF225" t="s">
-        <x:v>1</x:v>
+      <x:c r="CF225" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="CG225" t="s">
         <x:v>1</x:v>
@@ -63974,296 +64265,8 @@
       </x:c>
     </x:row>
     <x:row r="226">
-      <x:c r="A226" s="4" t="s">
-        <x:v>464</x:v>
-      </x:c>
-      <x:c r="B226" s="5" t="s">
-        <x:v>465</x:v>
-      </x:c>
-      <x:c r="C226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CG226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CH226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CI226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CJ226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CK226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CL226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CM226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CN226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CO226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CP226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CQ226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CR226" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CS226" t="s">
-        <x:v>1</x:v>
+      <x:c r="A226" s="3" t="s">
+        <x:v>463</x:v>
       </x:c>
       <x:c r="CT226" t="s">
         <x:v>1</x:v>
@@ -64271,10 +64274,10 @@
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="4" t="s">
-        <x:v>466</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B227" s="5" t="s">
-        <x:v>467</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C227" t="s">
         <x:v>1</x:v>
@@ -64324,8 +64327,8 @@
       <x:c r="R227" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="S227" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="S227" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T227" t="s">
         <x:v>1</x:v>
@@ -64420,8 +64423,8 @@
       <x:c r="AX227" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AY227" t="s">
-        <x:v>1</x:v>
+      <x:c r="AY227" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AZ227" t="s">
         <x:v>1</x:v>
@@ -64567,10 +64570,10 @@
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="4" t="s">
-        <x:v>468</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B228" s="5" t="s">
-        <x:v>125</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="C228" t="s">
         <x:v>1</x:v>
@@ -64788,8 +64791,8 @@
       <x:c r="BV228" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BW228" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BW228" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BX228" t="s">
         <x:v>1</x:v>
@@ -64863,16 +64866,16 @@
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="4" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B229" s="5" t="s">
         <x:v>469</x:v>
       </x:c>
-      <x:c r="B229" s="5" t="s">
-        <x:v>470</x:v>
-      </x:c>
       <x:c r="C229" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D229" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="D229" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E229" t="s">
         <x:v>1</x:v>
@@ -64916,8 +64919,8 @@
       <x:c r="R229" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="S229" t="s">
-        <x:v>1</x:v>
+      <x:c r="S229" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="T229" t="s">
         <x:v>1</x:v>
@@ -65027,8 +65030,8 @@
       <x:c r="BC229" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BD229" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BD229" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BE229" t="s">
         <x:v>1</x:v>
@@ -65159,16 +65162,16 @@
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="4" t="s">
-        <x:v>471</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B230" s="5" t="s">
-        <x:v>472</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C230" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D230" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="D230" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E230" t="s">
         <x:v>1</x:v>
@@ -65323,8 +65326,8 @@
       <x:c r="BC230" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BD230" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BD230" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BE230" t="s">
         <x:v>1</x:v>
@@ -65380,8 +65383,8 @@
       <x:c r="BV230" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BW230" t="s">
-        <x:v>1</x:v>
+      <x:c r="BW230" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BX230" t="s">
         <x:v>1</x:v>
@@ -65455,10 +65458,10 @@
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="4" t="s">
-        <x:v>473</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B231" s="5" t="s">
-        <x:v>474</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C231" t="s">
         <x:v>1</x:v>
@@ -65751,16 +65754,16 @@
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B232" s="5" t="s">
-        <x:v>475</x:v>
-      </x:c>
-      <x:c r="C232" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D232" t="s">
-        <x:v>1</x:v>
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="C232" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D232" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E232" t="s">
         <x:v>1</x:v>
@@ -65810,11 +65813,11 @@
       <x:c r="T232" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="U232" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="V232" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="U232" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V232" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="W232" t="s">
         <x:v>1</x:v>
@@ -65834,11 +65837,11 @@
       <x:c r="AB232" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AC232" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AD232" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="AC232" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD232" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AE232" t="s">
         <x:v>1</x:v>
@@ -65855,20 +65858,20 @@
       <x:c r="AI232" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AJ232" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AK232" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AL232" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AM232" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="AN232" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="AJ232" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK232" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL232" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM232" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN232" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AO232" t="s">
         <x:v>1</x:v>
@@ -65915,8 +65918,8 @@
       <x:c r="BC232" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BD232" t="s">
-        <x:v>1</x:v>
+      <x:c r="BD232" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BE232" t="s">
         <x:v>1</x:v>
@@ -65951,11 +65954,11 @@
       <x:c r="BO232" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BP232" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="BQ232" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BP232" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ232" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BR232" t="s">
         <x:v>1</x:v>
@@ -66047,7 +66050,7 @@
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B233" s="5" t="s">
         <x:v>476</x:v>
@@ -66055,8 +66058,8 @@
       <x:c r="C233" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D233" t="s">
-        <x:v>1</x:v>
+      <x:c r="D233" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E233" t="s">
         <x:v>1</x:v>
@@ -66211,11 +66214,11 @@
       <x:c r="BC233" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BD233" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE233" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BD233" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BE233" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BF233" t="s">
         <x:v>1</x:v>
@@ -66342,298 +66345,594 @@
       </x:c>
     </x:row>
     <x:row r="234">
-      <x:c r="A234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BA234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CG234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CH234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CI234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CJ234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CK234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CL234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CM234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CN234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CO234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CP234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CQ234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CR234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CS234" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CT234" s="7" t="s">
+      <x:c r="A234" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B234" s="5" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="C234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE234" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BF234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CH234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CI234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CJ234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CK234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CL234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CM234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CN234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CO234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CP234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CQ234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CR234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CS234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CT234" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CH235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CI235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CJ235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CK235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CL235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CM235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CN235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CO235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CP235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CQ235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CR235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CS235" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CT235" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -66684,7 +66983,7 @@
     <x:mergeCell ref="A189:CT189"/>
     <x:mergeCell ref="A196:CT196"/>
     <x:mergeCell ref="A207:CT207"/>
-    <x:mergeCell ref="A224:CT224"/>
+    <x:mergeCell ref="A226:CT226"/>
   </x:mergeCells>
 </x:worksheet>
 </file>
--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R37607ab1a532417f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R1860a50d809f4942"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -44581,8 +44581,8 @@
       <x:c r="BH155" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BI155" t="s">
-        <x:v>1</x:v>
+      <x:c r="BI155" s="6" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BJ155" s="6" t="s">
         <x:v>112</x:v>
@@ -63853,8 +63853,8 @@
       <x:c r="BH224" s="6" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="BI224" s="6" t="s">
-        <x:v>112</x:v>
+      <x:c r="BI224" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BJ224" s="6" t="s">
         <x:v>112</x:v>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R1860a50d809f4942"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rd78a55beea8e485d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -79,7 +79,7 @@
   </x:si>
   <x:si>
     <x:t>Python
- 3.14.6 </x:t>
+ 3.14.7 </x:t>
   </x:si>
   <x:si>
     <x:t>D
@@ -135,7 +135,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.8.20 </x:t>
+ 2026.9.2 </x:t>
   </x:si>
   <x:si>
     <x:t>Regex</x:t>

--- a/RegexFeatureMatrix.xlsx
+++ b/RegexFeatureMatrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="Rd78a55beea8e485d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" r:id="R445d27dd1bcb490f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -127,7 +127,7 @@
   </x:si>
   <x:si>
     <x:t>Go
- 1.27.0 </x:t>
+ 1.27.1 </x:t>
   </x:si>
   <x:si>
     <x:t>Dart
@@ -135,7 +135,7 @@
   </x:si>
   <x:si>
     <x:t>REAL
- 2026.9.2 </x:t>
+ 2026.9.5 </x:t>
   </x:si>
   <x:si>
     <x:t>Regex</x:t>
